--- a/projection_1.5m_buy.xlsx
+++ b/projection_1.5m_buy.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J409"/>
+  <dimension ref="A1:H409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -478,8 +478,6 @@
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -523,16 +521,6 @@
           <t>CashAfterTrade</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>EntryDate</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>EntryPrice</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="19" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -563,14 +551,6 @@
       <c r="H2" s="4" t="n">
         <v>192568.7372864</v>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>2012-03-01</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="n">
-        <v>675.5693375999999</v>
-      </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -601,14 +581,6 @@
       <c r="H3" s="7" t="n">
         <v>193202.3669168</v>
       </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>2012-03-14</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="n">
-        <v>759.4487519999999</v>
-      </c>
     </row>
     <row r="4" ht="19" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -639,14 +611,6 @@
       <c r="H4" s="4" t="n">
         <v>192632.2136</v>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2012-03-20</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>753.781224</v>
-      </c>
     </row>
     <row r="5" ht="19" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -677,14 +641,6 @@
       <c r="H5" s="7" t="n">
         <v>185087.6003264</v>
       </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>2012-03-25</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="n">
-        <v>117.8845824</v>
-      </c>
     </row>
     <row r="6" ht="19" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -715,14 +671,6 @@
       <c r="H6" s="4" t="n">
         <v>193303.2489152</v>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2012-04-02</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>170.02584</v>
-      </c>
     </row>
     <row r="7" ht="19" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -753,14 +701,6 @@
       <c r="H7" s="7" t="n">
         <v>195323.1558944</v>
       </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>2012-05-22</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="n">
-        <v>87.27993119999999</v>
-      </c>
     </row>
     <row r="8" ht="19" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -791,14 +731,6 @@
       <c r="H8" s="4" t="n">
         <v>196895.3281616</v>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2012-06-25</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="n">
-        <v>255.03876</v>
-      </c>
     </row>
     <row r="9" ht="19" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
@@ -829,14 +761,6 @@
       <c r="H9" s="7" t="n">
         <v>189912.9336656</v>
       </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>2012-06-25</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="n">
-        <v>634.7631359999999</v>
-      </c>
     </row>
     <row r="10" ht="19" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -867,14 +791,6 @@
       <c r="H10" s="4" t="n">
         <v>182556.4823216</v>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2012-06-28</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>668.7683039999999</v>
-      </c>
     </row>
     <row r="11" ht="19" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
@@ -905,14 +821,6 @@
       <c r="H11" s="7" t="n">
         <v>175152.4237424</v>
       </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>2012-07-01</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="n">
-        <v>160.9577952</v>
-      </c>
     </row>
     <row r="12" ht="19" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -943,14 +851,6 @@
       <c r="H12" s="4" t="n">
         <v>182699.3040272</v>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2012-07-03</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>204.031008</v>
-      </c>
     </row>
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
@@ -981,14 +881,6 @@
       <c r="H13" s="7" t="n">
         <v>198796.2170528</v>
       </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>2012-10-11</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="n">
-        <v>102.015504</v>
-      </c>
     </row>
     <row r="14" ht="19" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1019,14 +911,6 @@
       <c r="H14" s="4" t="n">
         <v>198963.9758816</v>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2012-10-17</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="n">
-        <v>100.8819984</v>
-      </c>
     </row>
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -1057,14 +941,6 @@
       <c r="H15" s="7" t="n">
         <v>191419.362608</v>
       </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>2012-11-05</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="n">
-        <v>290.1774336</v>
-      </c>
     </row>
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -1095,14 +971,6 @@
       <c r="H16" s="4" t="n">
         <v>183892.885424</v>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2012-11-12</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="n">
-        <v>376.3238592</v>
-      </c>
     </row>
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
@@ -1133,14 +1001,6 @@
       <c r="H17" s="7" t="n">
         <v>200256.1722656</v>
       </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>2012-11-29</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="n">
-        <v>328.716624</v>
-      </c>
     </row>
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -1171,14 +1031,6 @@
       <c r="H18" s="4" t="n">
         <v>200342.3186912</v>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>2012-12-24</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="n">
-        <v>367.2558144</v>
-      </c>
     </row>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
@@ -1209,14 +1061,6 @@
       <c r="H19" s="7" t="n">
         <v>200375.2475546008</v>
       </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>2013-01-15</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="n">
-        <v>219.1035910895715</v>
-      </c>
     </row>
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -1247,14 +1091,6 @@
       <c r="H20" s="4" t="n">
         <v>200631.0794933296</v>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2013-02-03</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="n">
-        <v>94.98710596368706</v>
-      </c>
     </row>
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
@@ -1285,14 +1121,6 @@
       <c r="H21" s="7" t="n">
         <v>192576.172907609</v>
       </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>2013-02-04</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="n">
-        <v>402.7453292860331</v>
-      </c>
     </row>
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -1323,14 +1151,6 @@
       <c r="H22" s="4" t="n">
         <v>192823.1393831146</v>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2013-02-12</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="n">
-        <v>335.6211077383609</v>
-      </c>
     </row>
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
@@ -1361,14 +1181,6 @@
       <c r="H23" s="7" t="n">
         <v>185173.5111161723</v>
       </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>2013-02-12</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="n">
-        <v>956.2035333677829</v>
-      </c>
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -1399,14 +1211,6 @@
       <c r="H24" s="4" t="n">
         <v>196243.9416925535</v>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>2013-02-26</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="n">
-        <v>981.5334282914329</v>
-      </c>
     </row>
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
@@ -1437,14 +1241,6 @@
       <c r="H25" s="7" t="n">
         <v>204329.2441521825</v>
       </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>2013-04-08</t>
-        </is>
-      </c>
-      <c r="J25" s="7" t="n">
-        <v>455.9381086256979</v>
-      </c>
     </row>
     <row r="26" ht="19" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -1475,14 +1271,6 @@
       <c r="H26" s="4" t="n">
         <v>196628.9560953929</v>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>2013-04-09</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="n">
-        <v>962.5360070986954</v>
-      </c>
     </row>
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
@@ -1513,14 +1301,6 @@
       <c r="H27" s="7" t="n">
         <v>197129.221520135</v>
       </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>2013-04-15</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="n">
-        <v>1460.268442348416</v>
-      </c>
     </row>
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -1551,14 +1331,6 @@
       <c r="H28" s="4" t="n">
         <v>204709.1925760373</v>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>2013-05-06</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="n">
-        <v>164.6443170037242</v>
-      </c>
     </row>
     <row r="29" ht="19" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
@@ -1589,14 +1361,6 @@
       <c r="H29" s="7" t="n">
         <v>196304.7334403702</v>
       </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>2013-05-07</t>
-        </is>
-      </c>
-      <c r="J29" s="7" t="n">
-        <v>400.2123397936681</v>
-      </c>
     </row>
     <row r="30" ht="19" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -1627,14 +1391,6 @@
       <c r="H30" s="4" t="n">
         <v>187945.8681155657</v>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>2013-05-13</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="n">
-        <v>94.98710596368706</v>
-      </c>
     </row>
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
@@ -1665,14 +1421,6 @@
       <c r="H31" s="7" t="n">
         <v>180536.8738503981</v>
       </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>2013-05-13</t>
-        </is>
-      </c>
-      <c r="J31" s="7" t="n">
-        <v>1234.832377527932</v>
-      </c>
     </row>
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -1703,14 +1451,6 @@
       <c r="H32" s="4" t="n">
         <v>189860.8081717937</v>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>2013-05-15</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="n">
-        <v>1941.536445897763</v>
-      </c>
     </row>
     <row r="33" ht="19" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
@@ -1741,14 +1481,6 @@
       <c r="H33" s="7" t="n">
         <v>181501.9428469892</v>
       </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>2013-05-16</t>
-        </is>
-      </c>
-      <c r="J33" s="7" t="n">
-        <v>1044.858165600558</v>
-      </c>
     </row>
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -1779,14 +1511,6 @@
       <c r="H34" s="4" t="n">
         <v>173143.0775221847</v>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>2013-05-19</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="n">
-        <v>278.6288441601487</v>
-      </c>
     </row>
     <row r="35" ht="19" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
@@ -1817,14 +1541,6 @@
       <c r="H35" s="7" t="n">
         <v>198941.5755019221</v>
       </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>2013-06-03</t>
-        </is>
-      </c>
-      <c r="J35" s="7" t="n">
-        <v>91.18762172513956</v>
-      </c>
     </row>
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -1855,14 +1571,6 @@
       <c r="H36" s="4" t="n">
         <v>198384.3178136018</v>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>2013-06-20</t>
-        </is>
-      </c>
-      <c r="J36" s="4" t="n">
-        <v>174.7762749731842</v>
-      </c>
     </row>
     <row r="37" ht="19" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
@@ -1893,14 +1601,6 @@
       <c r="H37" s="7" t="n">
         <v>208409.8902243825</v>
       </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>2013-06-26</t>
-        </is>
-      </c>
-      <c r="J37" s="7" t="n">
-        <v>1937.736961659216</v>
-      </c>
     </row>
     <row r="38" ht="19" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -1931,14 +1631,6 @@
       <c r="H38" s="4" t="n">
         <v>201836.7824916953</v>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>2013-06-26</t>
-        </is>
-      </c>
-      <c r="J38" s="4" t="n">
-        <v>2191.035910895715</v>
-      </c>
     </row>
     <row r="39" ht="19" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
@@ -1969,14 +1661,6 @@
       <c r="H39" s="7" t="n">
         <v>201824.1175442335</v>
       </c>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>2013-07-10</t>
-        </is>
-      </c>
-      <c r="J39" s="7" t="n">
-        <v>873.8813748659209</v>
-      </c>
     </row>
     <row r="40" ht="19" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -2007,14 +1691,6 @@
       <c r="H40" s="4" t="n">
         <v>201152.8753287568</v>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>2013-07-23</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="n">
-        <v>1494.463800495343</v>
-      </c>
     </row>
     <row r="41" ht="19" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
@@ -2045,14 +1721,6 @@
       <c r="H41" s="7" t="n">
         <v>210783.3013787284</v>
       </c>
-      <c r="I41" s="5" t="inlineStr">
-        <is>
-          <t>2013-08-20</t>
-        </is>
-      </c>
-      <c r="J41" s="7" t="n">
-        <v>395.1463608089381</v>
-      </c>
     </row>
     <row r="42" ht="19" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
@@ -2083,14 +1751,6 @@
       <c r="H42" s="4" t="n">
         <v>211767.3677965122</v>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>2013-09-15</t>
-        </is>
-      </c>
-      <c r="J42" s="4" t="n">
-        <v>1063.855586793295</v>
-      </c>
     </row>
     <row r="43" ht="19" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
@@ -2121,14 +1781,6 @@
       <c r="H43" s="7" t="n">
         <v>203370.5076293223</v>
       </c>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>2013-09-17</t>
-        </is>
-      </c>
-      <c r="J43" s="7" t="n">
-        <v>64.5912320553072</v>
-      </c>
     </row>
     <row r="44" ht="19" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -2159,14 +1811,6 @@
       <c r="H44" s="4" t="n">
         <v>211244.3054663388</v>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>2013-10-08</t>
-        </is>
-      </c>
-      <c r="J44" s="4" t="n">
-        <v>98.78659020223454</v>
-      </c>
     </row>
     <row r="45" ht="19" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
@@ -2197,14 +1841,6 @@
       <c r="H45" s="7" t="n">
         <v>203645.3369892439</v>
       </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>2013-10-10</t>
-        </is>
-      </c>
-      <c r="J45" s="7" t="n">
-        <v>949.8710596368705</v>
-      </c>
     </row>
     <row r="46" ht="19" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
@@ -2235,14 +1871,6 @@
       <c r="H46" s="4" t="n">
         <v>211621.7209007012</v>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>2013-10-28</t>
-        </is>
-      </c>
-      <c r="J46" s="4" t="n">
-        <v>401.4788345398506</v>
-      </c>
     </row>
     <row r="47" ht="19" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
@@ -2273,14 +1901,6 @@
       <c r="H47" s="7" t="n">
         <v>213142.7810908664</v>
       </c>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>2013-10-31</t>
-        </is>
-      </c>
-      <c r="J47" s="7" t="n">
-        <v>943.538585905958</v>
-      </c>
     </row>
     <row r="48" ht="19" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
@@ -2311,14 +1931,6 @@
       <c r="H48" s="4" t="n">
         <v>213019.3320433674</v>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>2014-02-26</t>
-        </is>
-      </c>
-      <c r="J48" s="4" t="n">
-        <v>948.1082402389745</v>
-      </c>
     </row>
     <row r="49" ht="19" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
@@ -2349,14 +1961,6 @@
       <c r="H49" s="7" t="n">
         <v>212832.5405691711</v>
       </c>
-      <c r="I49" s="5" t="inlineStr">
-        <is>
-          <t>2014-03-24</t>
-        </is>
-      </c>
-      <c r="J49" s="7" t="n">
-        <v>683.4869851274996</v>
-      </c>
     </row>
     <row r="50" ht="19" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
@@ -2387,14 +1991,6 @@
       <c r="H50" s="4" t="n">
         <v>203719.3807674711</v>
       </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>2014-03-27</t>
-        </is>
-      </c>
-      <c r="J50" s="4" t="n">
-        <v>650.9399858357139</v>
-      </c>
     </row>
     <row r="51" ht="19" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
@@ -2425,14 +2021,6 @@
       <c r="H51" s="7" t="n">
         <v>196813.7565699096</v>
       </c>
-      <c r="I51" s="5" t="inlineStr">
-        <is>
-          <t>2014-03-31</t>
-        </is>
-      </c>
-      <c r="J51" s="7" t="n">
-        <v>3452.812098780743</v>
-      </c>
     </row>
     <row r="52" ht="19" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
@@ -2463,14 +2051,6 @@
       <c r="H52" s="4" t="n">
         <v>187601.5406834085</v>
       </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>2014-04-01</t>
-        </is>
-      </c>
-      <c r="J52" s="4" t="n">
-        <v>614.1477257667387</v>
-      </c>
     </row>
     <row r="53" ht="19" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
@@ -2501,14 +2081,6 @@
       <c r="H53" s="7" t="n">
         <v>214823.567873673</v>
       </c>
-      <c r="I53" s="5" t="inlineStr">
-        <is>
-          <t>2014-04-22</t>
-        </is>
-      </c>
-      <c r="J53" s="7" t="n">
-        <v>926.8819363530273</v>
-      </c>
     </row>
     <row r="54" ht="19" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
@@ -2539,14 +2111,6 @@
       <c r="H54" s="4" t="n">
         <v>215332.9991669357</v>
       </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>2014-04-27</t>
-        </is>
-      </c>
-      <c r="J54" s="4" t="n">
-        <v>679.2417243503101</v>
-      </c>
     </row>
     <row r="55" ht="19" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
@@ -2577,14 +2141,6 @@
       <c r="H55" s="7" t="n">
         <v>215061.3024771956</v>
       </c>
-      <c r="I55" s="5" t="inlineStr">
-        <is>
-          <t>2014-04-30</t>
-        </is>
-      </c>
-      <c r="J55" s="7" t="n">
-        <v>658.0154204643629</v>
-      </c>
     </row>
     <row r="56" ht="19" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
@@ -2615,14 +2171,6 @@
       <c r="H56" s="4" t="n">
         <v>206783.0439616762</v>
       </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>2014-05-05</t>
-        </is>
-      </c>
-      <c r="J56" s="4" t="n">
-        <v>1379.709752586567</v>
-      </c>
     </row>
     <row r="57" ht="19" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
@@ -2653,14 +2201,6 @@
       <c r="H57" s="7" t="n">
         <v>215582.0544658641</v>
       </c>
-      <c r="I57" s="5" t="inlineStr">
-        <is>
-          <t>2014-05-21</t>
-        </is>
-      </c>
-      <c r="J57" s="7" t="n">
-        <v>665.0908550930119</v>
-      </c>
     </row>
     <row r="58" ht="19" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
@@ -2691,14 +2231,6 @@
       <c r="H58" s="4" t="n">
         <v>215808.4683739809</v>
       </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>2014-05-28</t>
-        </is>
-      </c>
-      <c r="J58" s="4" t="n">
-        <v>625.4684211725772</v>
-      </c>
     </row>
     <row r="59" ht="19" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
@@ -2729,14 +2261,6 @@
       <c r="H59" s="7" t="n">
         <v>207530.2098584615</v>
       </c>
-      <c r="I59" s="5" t="inlineStr">
-        <is>
-          <t>2014-05-28</t>
-        </is>
-      </c>
-      <c r="J59" s="7" t="n">
-        <v>2759.419505173135</v>
-      </c>
     </row>
     <row r="60" ht="19" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
@@ -2767,14 +2291,6 @@
       <c r="H60" s="4" t="n">
         <v>208315.5831022415</v>
       </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>2014-06-03</t>
-        </is>
-      </c>
-      <c r="J60" s="4" t="n">
-        <v>591.5063349550617</v>
-      </c>
     </row>
     <row r="61" ht="19" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
@@ -2805,14 +2321,6 @@
       <c r="H61" s="7" t="n">
         <v>199145.8198235123</v>
       </c>
-      <c r="I61" s="5" t="inlineStr">
-        <is>
-          <t>2014-06-03</t>
-        </is>
-      </c>
-      <c r="J61" s="7" t="n">
-        <v>611.3175519152791</v>
-      </c>
     </row>
     <row r="62" ht="19" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
@@ -2843,14 +2351,6 @@
       <c r="H62" s="4" t="n">
         <v>199435.912643287</v>
       </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>2014-06-15</t>
-        </is>
-      </c>
-      <c r="J62" s="4" t="n">
-        <v>1259.427363899533</v>
-      </c>
     </row>
     <row r="63" ht="19" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
@@ -2881,14 +2381,6 @@
       <c r="H63" s="7" t="n">
         <v>220350.8974055736</v>
       </c>
-      <c r="I63" s="5" t="inlineStr">
-        <is>
-          <t>2014-07-06</t>
-        </is>
-      </c>
-      <c r="J63" s="7" t="n">
-        <v>849.0521554378876</v>
-      </c>
     </row>
     <row r="64" ht="19" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
@@ -2919,14 +2411,6 @@
       <c r="H64" s="4" t="n">
         <v>221074.0068246215</v>
       </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>2014-09-15</t>
-        </is>
-      </c>
-      <c r="J64" s="4" t="n">
-        <v>641.0343773556051</v>
-      </c>
     </row>
     <row r="65" ht="19" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
@@ -2957,14 +2441,6 @@
       <c r="H65" s="7" t="n">
         <v>211931.1301974812</v>
       </c>
-      <c r="I65" s="5" t="inlineStr">
-        <is>
-          <t>2014-09-16</t>
-        </is>
-      </c>
-      <c r="J65" s="7" t="n">
-        <v>703.2982020877168</v>
-      </c>
     </row>
     <row r="66" ht="19" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
@@ -2995,14 +2471,6 @@
       <c r="H66" s="4" t="n">
         <v>222544.2821404548</v>
       </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>2014-10-26</t>
-        </is>
-      </c>
-      <c r="J66" s="4" t="n">
-        <v>870.2784593238348</v>
-      </c>
     </row>
     <row r="67" ht="19" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
@@ -3033,14 +2501,6 @@
       <c r="H67" s="7" t="n">
         <v>221907.4930238764</v>
       </c>
-      <c r="I67" s="5" t="inlineStr">
-        <is>
-          <t>2014-11-20</t>
-        </is>
-      </c>
-      <c r="J67" s="7" t="n">
-        <v>495.2804240054344</v>
-      </c>
     </row>
     <row r="68" ht="19" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
@@ -3071,14 +2531,6 @@
       <c r="H68" s="4" t="n">
         <v>222487.6786634256</v>
       </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>2014-11-23</t>
-        </is>
-      </c>
-      <c r="J68" s="4" t="n">
-        <v>615.5628126924685</v>
-      </c>
     </row>
     <row r="69" ht="19" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
@@ -3109,14 +2561,6 @@
       <c r="H69" s="7" t="n">
         <v>223230.5992994338</v>
       </c>
-      <c r="I69" s="5" t="inlineStr">
-        <is>
-          <t>2014-12-10</t>
-        </is>
-      </c>
-      <c r="J69" s="7" t="n">
-        <v>601.4119434351704</v>
-      </c>
     </row>
     <row r="70" ht="19" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
@@ -3147,14 +2591,6 @@
       <c r="H70" s="4" t="n">
         <v>223747.1060273251</v>
       </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>2014-12-14</t>
-        </is>
-      </c>
-      <c r="J70" s="4" t="n">
-        <v>884.4293285811329</v>
-      </c>
     </row>
     <row r="71" ht="19" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
@@ -3185,14 +2621,6 @@
       <c r="H71" s="7" t="n">
         <v>214725.9268757976</v>
       </c>
-      <c r="I71" s="5" t="inlineStr">
-        <is>
-          <t>2014-12-15</t>
-        </is>
-      </c>
-      <c r="J71" s="7" t="n">
-        <v>601.4119434351704</v>
-      </c>
     </row>
     <row r="72" ht="19" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
@@ -3223,14 +2651,6 @@
       <c r="H72" s="4" t="n">
         <v>224143.3303665295</v>
       </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>2014-12-18</t>
-        </is>
-      </c>
-      <c r="J72" s="4" t="n">
-        <v>376.4131222441302</v>
-      </c>
     </row>
     <row r="73" ht="19" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
@@ -3261,14 +2681,6 @@
       <c r="H73" s="7" t="n">
         <v>225057.476520551</v>
       </c>
-      <c r="I73" s="5" t="inlineStr">
-        <is>
-          <t>2014-12-28</t>
-        </is>
-      </c>
-      <c r="J73" s="7" t="n">
-        <v>499.5256847826238</v>
-      </c>
     </row>
     <row r="74" ht="19" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
@@ -3299,14 +2711,6 @@
       <c r="H74" s="4" t="n">
         <v>224994.2320104517</v>
       </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>2015-01-04</t>
-        </is>
-      </c>
-      <c r="J74" s="4" t="n">
-        <v>235.5858001196998</v>
-      </c>
     </row>
     <row r="75" ht="19" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
@@ -3337,14 +2741,6 @@
       <c r="H75" s="7" t="n">
         <v>225579.2437288698</v>
       </c>
-      <c r="I75" s="5" t="inlineStr">
-        <is>
-          <t>2015-01-07</t>
-        </is>
-      </c>
-      <c r="J75" s="7" t="n">
-        <v>407.9270901401513</v>
-      </c>
     </row>
     <row r="76" ht="19" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
@@ -3375,14 +2771,6 @@
       <c r="H76" s="4" t="n">
         <v>215064.8439248698</v>
       </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>2015-01-14</t>
-        </is>
-      </c>
-      <c r="J76" s="4" t="n">
-        <v>751.0285574285732</v>
-      </c>
     </row>
     <row r="77" ht="19" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
@@ -3413,14 +2801,6 @@
       <c r="H77" s="7" t="n">
         <v>215264.0641316824</v>
       </c>
-      <c r="I77" s="5" t="inlineStr">
-        <is>
-          <t>2015-01-19</t>
-        </is>
-      </c>
-      <c r="J77" s="7" t="n">
-        <v>751.0285574285732</v>
-      </c>
     </row>
     <row r="78" ht="19" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
@@ -3451,14 +2831,6 @@
       <c r="H78" s="4" t="n">
         <v>226973.7851765582</v>
       </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>2015-03-19</t>
-        </is>
-      </c>
-      <c r="J78" s="4" t="n">
-        <v>543.9027868535351</v>
-      </c>
     </row>
     <row r="79" ht="19" customHeight="1">
       <c r="A79" s="5" t="inlineStr">
@@ -3489,14 +2861,6 @@
       <c r="H79" s="7" t="n">
         <v>216797.7435015892</v>
       </c>
-      <c r="I79" s="5" t="inlineStr">
-        <is>
-          <t>2015-03-19</t>
-        </is>
-      </c>
-      <c r="J79" s="7" t="n">
-        <v>2544.010418742262</v>
-      </c>
     </row>
     <row r="80" ht="19" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
@@ -3527,14 +2891,6 @@
       <c r="H80" s="4" t="n">
         <v>227868.6949944626</v>
       </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>2015-03-22</t>
-        </is>
-      </c>
-      <c r="J80" s="4" t="n">
-        <v>999.2632595681226</v>
-      </c>
     </row>
     <row r="81" ht="19" customHeight="1">
       <c r="A81" s="5" t="inlineStr">
@@ -3565,14 +2921,6 @@
       <c r="H81" s="7" t="n">
         <v>227870.276107215</v>
       </c>
-      <c r="I81" s="5" t="inlineStr">
-        <is>
-          <t>2015-04-13</t>
-        </is>
-      </c>
-      <c r="J81" s="7" t="n">
-        <v>1139.98229453895</v>
-      </c>
     </row>
     <row r="82" ht="19" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
@@ -3603,14 +2951,6 @@
       <c r="H82" s="4" t="n">
         <v>217513.9875784631</v>
       </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>2015-04-13</t>
-        </is>
-      </c>
-      <c r="J82" s="4" t="n">
-        <v>414.2515411500762</v>
-      </c>
     </row>
     <row r="83" ht="19" customHeight="1">
       <c r="A83" s="5" t="inlineStr">
@@ -3641,14 +2981,6 @@
       <c r="H83" s="7" t="n">
         <v>228210.2153489985</v>
       </c>
-      <c r="I83" s="5" t="inlineStr">
-        <is>
-          <t>2015-04-19</t>
-        </is>
-      </c>
-      <c r="J83" s="7" t="n">
-        <v>1130.495618024063</v>
-      </c>
     </row>
     <row r="84" ht="19" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
@@ -3679,14 +3011,6 @@
       <c r="H84" s="4" t="n">
         <v>229177.856353517</v>
       </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>2015-06-03</t>
-        </is>
-      </c>
-      <c r="J84" s="4" t="n">
-        <v>2333.722422662261</v>
-      </c>
     </row>
     <row r="85" ht="19" customHeight="1">
       <c r="A85" s="5" t="inlineStr">
@@ -3717,14 +3041,6 @@
       <c r="H85" s="7" t="n">
         <v>218979.6791000132</v>
       </c>
-      <c r="I85" s="5" t="inlineStr">
-        <is>
-          <t>2015-06-03</t>
-        </is>
-      </c>
-      <c r="J85" s="7" t="n">
-        <v>3399.392417834595</v>
-      </c>
     </row>
     <row r="86" ht="19" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
@@ -3755,14 +3071,6 @@
       <c r="H86" s="4" t="n">
         <v>208509.5504530826</v>
       </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>2015-06-10</t>
-        </is>
-      </c>
-      <c r="J86" s="4" t="n">
-        <v>951.8298769936864</v>
-      </c>
     </row>
     <row r="87" ht="19" customHeight="1">
       <c r="A87" s="5" t="inlineStr">
@@ -3793,14 +3101,6 @@
       <c r="H87" s="7" t="n">
         <v>219185.2237578357</v>
       </c>
-      <c r="I87" s="5" t="inlineStr">
-        <is>
-          <t>2015-06-28</t>
-        </is>
-      </c>
-      <c r="J87" s="7" t="n">
-        <v>186.5713047927824</v>
-      </c>
     </row>
     <row r="88" ht="19" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
@@ -3831,14 +3131,6 @@
       <c r="H88" s="4" t="n">
         <v>232774.8878654117</v>
       </c>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>2015-07-08</t>
-        </is>
-      </c>
-      <c r="J88" s="4" t="n">
-        <v>498.0505170315801</v>
-      </c>
     </row>
     <row r="89" ht="19" customHeight="1">
       <c r="A89" s="5" t="inlineStr">
@@ -3869,14 +3161,6 @@
       <c r="H89" s="7" t="n">
         <v>233026.2847930563</v>
       </c>
-      <c r="I89" s="5" t="inlineStr">
-        <is>
-          <t>2015-07-26</t>
-        </is>
-      </c>
-      <c r="J89" s="7" t="n">
-        <v>958.1543280036113</v>
-      </c>
     </row>
     <row r="90" ht="19" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
@@ -3907,14 +3191,6 @@
       <c r="H90" s="4" t="n">
         <v>233513.2675208205</v>
       </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>2015-08-02</t>
-        </is>
-      </c>
-      <c r="J90" s="4" t="n">
-        <v>189.7335302977448</v>
-      </c>
     </row>
     <row r="91" ht="19" customHeight="1">
       <c r="A91" s="5" t="inlineStr">
@@ -3945,14 +3221,6 @@
       <c r="H91" s="7" t="n">
         <v>235039.0413269648</v>
       </c>
-      <c r="I91" s="5" t="inlineStr">
-        <is>
-          <t>2015-08-10</t>
-        </is>
-      </c>
-      <c r="J91" s="7" t="n">
-        <v>2292.61349109775</v>
-      </c>
     </row>
     <row r="92" ht="19" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
@@ -3983,14 +3251,6 @@
       <c r="H92" s="4" t="n">
         <v>234971.0534786081</v>
       </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>2015-08-16</t>
-        </is>
-      </c>
-      <c r="J92" s="4" t="n">
-        <v>937.5998622213556</v>
-      </c>
     </row>
     <row r="93" ht="19" customHeight="1">
       <c r="A93" s="5" t="inlineStr">
@@ -4021,14 +3281,6 @@
       <c r="H93" s="7" t="n">
         <v>224899.3652453028</v>
       </c>
-      <c r="I93" s="5" t="inlineStr">
-        <is>
-          <t>2015-08-18</t>
-        </is>
-      </c>
-      <c r="J93" s="7" t="n">
-        <v>774.7452487157913</v>
-      </c>
     </row>
     <row r="94" ht="19" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
@@ -4059,14 +3311,6 @@
       <c r="H94" s="4" t="n">
         <v>239050.3243800097</v>
       </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>2015-10-08</t>
-        </is>
-      </c>
-      <c r="J94" s="4" t="n">
-        <v>711.500738616543</v>
-      </c>
     </row>
     <row r="95" ht="19" customHeight="1">
       <c r="A95" s="5" t="inlineStr">
@@ -4097,14 +3341,6 @@
       <c r="H95" s="7" t="n">
         <v>239809.2585012006</v>
       </c>
-      <c r="I95" s="5" t="inlineStr">
-        <is>
-          <t>2015-11-02</t>
-        </is>
-      </c>
-      <c r="J95" s="7" t="n">
-        <v>433.2248941798507</v>
-      </c>
     </row>
     <row r="96" ht="19" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
@@ -4135,14 +3371,6 @@
       <c r="H96" s="4" t="n">
         <v>240512.8536760548</v>
       </c>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t>2015-11-08</t>
-        </is>
-      </c>
-      <c r="J96" s="4" t="n">
-        <v>1984.296504363914</v>
-      </c>
     </row>
     <row r="97" ht="19" customHeight="1">
       <c r="A97" s="5" t="inlineStr">
@@ -4173,14 +3401,6 @@
       <c r="H97" s="7" t="n">
         <v>240647.2482600157</v>
       </c>
-      <c r="I97" s="5" t="inlineStr">
-        <is>
-          <t>2015-12-01</t>
-        </is>
-      </c>
-      <c r="J97" s="7" t="n">
-        <v>1021.39883810286</v>
-      </c>
     </row>
     <row r="98" ht="19" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
@@ -4211,14 +3431,6 @@
       <c r="H98" s="4" t="n">
         <v>230477.5310360566</v>
       </c>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>2015-12-02</t>
-        </is>
-      </c>
-      <c r="J98" s="4" t="n">
-        <v>423.7382176649634</v>
-      </c>
     </row>
     <row r="99" ht="19" customHeight="1">
       <c r="A99" s="5" t="inlineStr">
@@ -4249,14 +3461,6 @@
       <c r="H99" s="7" t="n">
         <v>240501.7858867874</v>
       </c>
-      <c r="I99" s="5" t="inlineStr">
-        <is>
-          <t>2015-12-04</t>
-        </is>
-      </c>
-      <c r="J99" s="7" t="n">
-        <v>877.5175776270697</v>
-      </c>
     </row>
     <row r="100" ht="19" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
@@ -4287,14 +3491,6 @@
       <c r="H100" s="4" t="n">
         <v>230105.9695392235</v>
       </c>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>2015-12-13</t>
-        </is>
-      </c>
-      <c r="J100" s="4" t="n">
-        <v>415.8326539025574</v>
-      </c>
     </row>
     <row r="101" ht="19" customHeight="1">
       <c r="A101" s="5" t="inlineStr">
@@ -4325,14 +3521,6 @@
       <c r="H101" s="7" t="n">
         <v>242440.2301213294</v>
       </c>
-      <c r="I101" s="5" t="inlineStr">
-        <is>
-          <t>2015-12-31</t>
-        </is>
-      </c>
-      <c r="J101" s="7" t="n">
-        <v>2608.836041593991</v>
-      </c>
     </row>
     <row r="102" ht="19" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
@@ -4363,14 +3551,6 @@
       <c r="H102" s="4" t="n">
         <v>248608.2593763361</v>
       </c>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>2016-02-29</t>
-        </is>
-      </c>
-      <c r="J102" s="4" t="n">
-        <v>6168.029255006671</v>
-      </c>
     </row>
     <row r="103" ht="19" customHeight="1">
       <c r="A103" s="5" t="inlineStr">
@@ -4401,14 +3581,6 @@
       <c r="H103" s="7" t="n">
         <v>243200.1878805423</v>
       </c>
-      <c r="I103" s="5" t="inlineStr">
-        <is>
-          <t>2016-03-10</t>
-        </is>
-      </c>
-      <c r="J103" s="7" t="n">
-        <v>362.3054433456641</v>
-      </c>
     </row>
     <row r="104" ht="19" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
@@ -4439,14 +3611,6 @@
       <c r="H104" s="4" t="n">
         <v>231447.3527671341</v>
       </c>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t>2016-03-30</t>
-        </is>
-      </c>
-      <c r="J104" s="4" t="n">
-        <v>2350.567022681625</v>
-      </c>
     </row>
     <row r="105" ht="19" customHeight="1">
       <c r="A105" s="5" t="inlineStr">
@@ -4477,14 +3641,6 @@
       <c r="H105" s="7" t="n">
         <v>244361.3326428745</v>
       </c>
-      <c r="I105" s="5" t="inlineStr">
-        <is>
-          <t>2016-05-03</t>
-        </is>
-      </c>
-      <c r="J105" s="7" t="n">
-        <v>542.5744932054579</v>
-      </c>
     </row>
     <row r="106" ht="19" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
@@ -4515,14 +3671,6 @@
       <c r="H106" s="4" t="n">
         <v>245077.1068114354</v>
       </c>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>2016-05-18</t>
-        </is>
-      </c>
-      <c r="J106" s="4" t="n">
-        <v>397.6523158671922</v>
-      </c>
     </row>
     <row r="107" ht="19" customHeight="1">
       <c r="A107" s="5" t="inlineStr">
@@ -4553,14 +3701,6 @@
       <c r="H107" s="7" t="n">
         <v>245738.093327588</v>
       </c>
-      <c r="I107" s="5" t="inlineStr">
-        <is>
-          <t>2016-05-26</t>
-        </is>
-      </c>
-      <c r="J107" s="7" t="n">
-        <v>314.587165441601</v>
-      </c>
     </row>
     <row r="108" ht="19" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
@@ -4591,14 +3731,6 @@
       <c r="H108" s="4" t="n">
         <v>250379.1376896646</v>
       </c>
-      <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t>2016-06-12</t>
-        </is>
-      </c>
-      <c r="J108" s="4" t="n">
-        <v>3957.082378785082</v>
-      </c>
     </row>
     <row r="109" ht="19" customHeight="1">
       <c r="A109" s="5" t="inlineStr">
@@ -4629,14 +3761,6 @@
       <c r="H109" s="7" t="n">
         <v>238997.4447377326</v>
       </c>
-      <c r="I109" s="5" t="inlineStr">
-        <is>
-          <t>2016-06-19</t>
-        </is>
-      </c>
-      <c r="J109" s="7" t="n">
-        <v>406.4890339975743</v>
-      </c>
     </row>
     <row r="110" ht="19" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
@@ -4667,14 +3791,6 @@
       <c r="H110" s="4" t="n">
         <v>253634.5846488974</v>
       </c>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>2016-07-18</t>
-        </is>
-      </c>
-      <c r="J110" s="4" t="n">
-        <v>6344.763617614311</v>
-      </c>
     </row>
     <row r="111" ht="19" customHeight="1">
       <c r="A111" s="5" t="inlineStr">
@@ -4705,14 +3821,6 @@
       <c r="H111" s="7" t="n">
         <v>248827.4099859696</v>
       </c>
-      <c r="I111" s="5" t="inlineStr">
-        <is>
-          <t>2016-07-26</t>
-        </is>
-      </c>
-      <c r="J111" s="7" t="n">
-        <v>945.5288399508793</v>
-      </c>
     </row>
     <row r="112" ht="19" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
@@ -4743,14 +3851,6 @@
       <c r="H112" s="4" t="n">
         <v>249555.555559913</v>
       </c>
-      <c r="I112" s="2" t="inlineStr">
-        <is>
-          <t>2016-08-28</t>
-        </is>
-      </c>
-      <c r="J112" s="4" t="n">
-        <v>5839.303340556458</v>
-      </c>
     </row>
     <row r="113" ht="19" customHeight="1">
       <c r="A113" s="5" t="inlineStr">
@@ -4781,14 +3881,6 @@
       <c r="H113" s="7" t="n">
         <v>238894.9388074201</v>
       </c>
-      <c r="I113" s="5" t="inlineStr">
-        <is>
-          <t>2016-08-29</t>
-        </is>
-      </c>
-      <c r="J113" s="7" t="n">
-        <v>1332.577094061613</v>
-      </c>
     </row>
     <row r="114" ht="19" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
@@ -4819,14 +3911,6 @@
       <c r="H114" s="4" t="n">
         <v>230464.7097110357</v>
       </c>
-      <c r="I114" s="2" t="inlineStr">
-        <is>
-          <t>2016-08-31</t>
-        </is>
-      </c>
-      <c r="J114" s="4" t="n">
-        <v>8430.229096384475</v>
-      </c>
     </row>
     <row r="115" ht="19" customHeight="1">
       <c r="A115" s="5" t="inlineStr">
@@ -4857,14 +3941,6 @@
       <c r="H115" s="7" t="n">
         <v>218800.2417789313</v>
       </c>
-      <c r="I115" s="5" t="inlineStr">
-        <is>
-          <t>2016-08-31</t>
-        </is>
-      </c>
-      <c r="J115" s="7" t="n">
-        <v>2916.116983026076</v>
-      </c>
     </row>
     <row r="116" ht="19" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
@@ -4895,14 +3971,6 @@
       <c r="H116" s="4" t="n">
         <v>207330.1816456954</v>
       </c>
-      <c r="I116" s="2" t="inlineStr">
-        <is>
-          <t>2016-08-31</t>
-        </is>
-      </c>
-      <c r="J116" s="4" t="n">
-        <v>1042.732739385082</v>
-      </c>
     </row>
     <row r="117" ht="19" customHeight="1">
       <c r="A117" s="5" t="inlineStr">
@@ -4933,14 +4001,6 @@
       <c r="H117" s="7" t="n">
         <v>196049.2272804497</v>
       </c>
-      <c r="I117" s="5" t="inlineStr">
-        <is>
-          <t>2016-09-05</t>
-        </is>
-      </c>
-      <c r="J117" s="7" t="n">
-        <v>867.7657204035173</v>
-      </c>
     </row>
     <row r="118" ht="19" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
@@ -4971,14 +4031,6 @@
       <c r="H118" s="4" t="n">
         <v>249820.6571038245</v>
       </c>
-      <c r="I118" s="2" t="inlineStr">
-        <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="J118" s="4" t="n">
-        <v>303.9831036851425</v>
-      </c>
     </row>
     <row r="119" ht="19" customHeight="1">
       <c r="A119" s="5" t="inlineStr">
@@ -5009,14 +4061,6 @@
       <c r="H119" s="7" t="n">
         <v>264919.0737013952</v>
       </c>
-      <c r="I119" s="5" t="inlineStr">
-        <is>
-          <t>2016-11-16</t>
-        </is>
-      </c>
-      <c r="J119" s="7" t="n">
-        <v>3048.667754981807</v>
-      </c>
     </row>
     <row r="120" ht="19" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
@@ -5047,14 +4091,6 @@
       <c r="H120" s="4" t="n">
         <v>262665.7105781478</v>
       </c>
-      <c r="I120" s="2" t="inlineStr">
-        <is>
-          <t>2016-11-30</t>
-        </is>
-      </c>
-      <c r="J120" s="4" t="n">
-        <v>503.6929334317769</v>
-      </c>
     </row>
     <row r="121" ht="19" customHeight="1">
       <c r="A121" s="5" t="inlineStr">
@@ -5085,14 +4121,6 @@
       <c r="H121" s="7" t="n">
         <v>251876.0777409514</v>
       </c>
-      <c r="I121" s="5" t="inlineStr">
-        <is>
-          <t>2016-11-30</t>
-        </is>
-      </c>
-      <c r="J121" s="7" t="n">
-        <v>2157.926567439296</v>
-      </c>
     </row>
     <row r="122" ht="19" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
@@ -5123,14 +4151,6 @@
       <c r="H122" s="4" t="n">
         <v>240656.9804026183</v>
       </c>
-      <c r="I122" s="2" t="inlineStr">
-        <is>
-          <t>2016-11-30</t>
-        </is>
-      </c>
-      <c r="J122" s="4" t="n">
-        <v>2804.774334583263</v>
-      </c>
     </row>
     <row r="123" ht="19" customHeight="1">
       <c r="A123" s="5" t="inlineStr">
@@ -5161,14 +4181,6 @@
       <c r="H123" s="7" t="n">
         <v>261727.3755680503</v>
       </c>
-      <c r="I123" s="5" t="inlineStr">
-        <is>
-          <t>2017-01-02</t>
-        </is>
-      </c>
-      <c r="J123" s="7" t="n">
-        <v>934.0322167135914</v>
-      </c>
     </row>
     <row r="124" ht="19" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
@@ -5199,14 +4211,6 @@
       <c r="H124" s="4" t="n">
         <v>264432.7120096943</v>
       </c>
-      <c r="I124" s="2" t="inlineStr">
-        <is>
-          <t>2017-02-01</t>
-        </is>
-      </c>
-      <c r="J124" s="4" t="n">
-        <v>2744.830404295755</v>
-      </c>
     </row>
     <row r="125" ht="19" customHeight="1">
       <c r="A125" s="5" t="inlineStr">
@@ -5237,14 +4241,6 @@
       <c r="H125" s="7" t="n">
         <v>260216.7314966214</v>
       </c>
-      <c r="I125" s="5" t="inlineStr">
-        <is>
-          <t>2017-02-15</t>
-        </is>
-      </c>
-      <c r="J125" s="7" t="n">
-        <v>483.8010424837841</v>
-      </c>
     </row>
     <row r="126" ht="19" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
@@ -5275,14 +4271,6 @@
       <c r="H126" s="4" t="n">
         <v>247248.8888599233</v>
       </c>
-      <c r="I126" s="2" t="inlineStr">
-        <is>
-          <t>2017-02-15</t>
-        </is>
-      </c>
-      <c r="J126" s="4" t="n">
-        <v>392.9649283847879</v>
-      </c>
     </row>
     <row r="127" ht="19" customHeight="1">
       <c r="A127" s="5" t="inlineStr">
@@ -5313,14 +4301,6 @@
       <c r="H127" s="7" t="n">
         <v>236170.832336111</v>
       </c>
-      <c r="I127" s="5" t="inlineStr">
-        <is>
-          <t>2017-02-16</t>
-        </is>
-      </c>
-      <c r="J127" s="7" t="n">
-        <v>2215.611304762473</v>
-      </c>
     </row>
     <row r="128" ht="19" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
@@ -5351,14 +4331,6 @@
       <c r="H128" s="4" t="n">
         <v>223777.6268559958</v>
       </c>
-      <c r="I128" s="2" t="inlineStr">
-        <is>
-          <t>2017-02-16</t>
-        </is>
-      </c>
-      <c r="J128" s="4" t="n">
-        <v>1032.767123342935</v>
-      </c>
     </row>
     <row r="129" ht="19" customHeight="1">
       <c r="A129" s="5" t="inlineStr">
@@ -5389,14 +4361,6 @@
       <c r="H129" s="7" t="n">
         <v>212458.6571600078</v>
       </c>
-      <c r="I129" s="5" t="inlineStr">
-        <is>
-          <t>2017-02-16</t>
-        </is>
-      </c>
-      <c r="J129" s="7" t="n">
-        <v>2829.742423996991</v>
-      </c>
     </row>
     <row r="130" ht="19" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
@@ -5427,14 +4391,6 @@
       <c r="H130" s="4" t="n">
         <v>212960.2304856848</v>
       </c>
-      <c r="I130" s="2" t="inlineStr">
-        <is>
-          <t>2017-02-19</t>
-        </is>
-      </c>
-      <c r="J130" s="4" t="n">
-        <v>6200.552136322784</v>
-      </c>
     </row>
     <row r="131" ht="19" customHeight="1">
       <c r="A131" s="5" t="inlineStr">
@@ -5465,14 +4421,6 @@
       <c r="H131" s="7" t="n">
         <v>262742.3704082</v>
       </c>
-      <c r="I131" s="5" t="inlineStr">
-        <is>
-          <t>2017-03-19</t>
-        </is>
-      </c>
-      <c r="J131" s="7" t="n">
-        <v>898.4876503270276</v>
-      </c>
     </row>
     <row r="132" ht="19" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
@@ -5503,14 +4451,6 @@
       <c r="H132" s="4" t="n">
         <v>249788.3506584301</v>
       </c>
-      <c r="I132" s="2" t="inlineStr">
-        <is>
-          <t>2017-03-22</t>
-        </is>
-      </c>
-      <c r="J132" s="4" t="n">
-        <v>809.6262343606184</v>
-      </c>
     </row>
     <row r="133" ht="19" customHeight="1">
       <c r="A133" s="5" t="inlineStr">
@@ -5541,14 +4481,6 @@
       <c r="H133" s="7" t="n">
         <v>267896.3325342517</v>
       </c>
-      <c r="I133" s="5" t="inlineStr">
-        <is>
-          <t>2017-05-15</t>
-        </is>
-      </c>
-      <c r="J133" s="7" t="n">
-        <v>928.1081223158308</v>
-      </c>
     </row>
     <row r="134" ht="19" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
@@ -5579,14 +4511,6 @@
       <c r="H134" s="4" t="n">
         <v>268990.3152997048</v>
       </c>
-      <c r="I134" s="2" t="inlineStr">
-        <is>
-          <t>2017-07-06</t>
-        </is>
-      </c>
-      <c r="J134" s="4" t="n">
-        <v>2912.679745565639</v>
-      </c>
     </row>
     <row r="135" ht="19" customHeight="1">
       <c r="A135" s="5" t="inlineStr">
@@ -5617,14 +4541,6 @@
       <c r="H135" s="7" t="n">
         <v>267844.9903828045</v>
       </c>
-      <c r="I135" s="5" t="inlineStr">
-        <is>
-          <t>2017-07-09</t>
-        </is>
-      </c>
-      <c r="J135" s="7" t="n">
-        <v>1072.261085994673</v>
-      </c>
     </row>
     <row r="136" ht="19" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
@@ -5655,14 +4571,6 @@
       <c r="H136" s="4" t="n">
         <v>254851.4766703828</v>
       </c>
-      <c r="I136" s="2" t="inlineStr">
-        <is>
-          <t>2017-07-10</t>
-        </is>
-      </c>
-      <c r="J136" s="4" t="n">
-        <v>1856.216244631662</v>
-      </c>
     </row>
     <row r="137" ht="19" customHeight="1">
       <c r="A137" s="5" t="inlineStr">
@@ -5693,14 +4601,6 @@
       <c r="H137" s="7" t="n">
         <v>268405.8046524591</v>
       </c>
-      <c r="I137" s="5" t="inlineStr">
-        <is>
-          <t>2017-07-18</t>
-        </is>
-      </c>
-      <c r="J137" s="7" t="n">
-        <v>270.5336441644017</v>
-      </c>
     </row>
     <row r="138" ht="19" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
@@ -5731,14 +4631,6 @@
       <c r="H138" s="4" t="n">
         <v>269890.7776481644</v>
       </c>
-      <c r="I138" s="2" t="inlineStr">
-        <is>
-          <t>2017-09-18</t>
-        </is>
-      </c>
-      <c r="J138" s="4" t="n">
-        <v>1520.517562091893</v>
-      </c>
     </row>
     <row r="139" ht="19" customHeight="1">
       <c r="A139" s="5" t="inlineStr">
@@ -5769,14 +4661,6 @@
       <c r="H139" s="7" t="n">
         <v>257264.5577884039</v>
       </c>
-      <c r="I139" s="5" t="inlineStr">
-        <is>
-          <t>2017-09-24</t>
-        </is>
-      </c>
-      <c r="J139" s="7" t="n">
-        <v>548.966080859151</v>
-      </c>
     </row>
     <row r="140" ht="19" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
@@ -5807,14 +4691,6 @@
       <c r="H140" s="4" t="n">
         <v>270633.2641460171</v>
       </c>
-      <c r="I140" s="2" t="inlineStr">
-        <is>
-          <t>2017-10-16</t>
-        </is>
-      </c>
-      <c r="J140" s="4" t="n">
-        <v>1721.936771615754</v>
-      </c>
     </row>
     <row r="141" ht="19" customHeight="1">
       <c r="A141" s="5" t="inlineStr">
@@ -5845,14 +4721,6 @@
       <c r="H141" s="7" t="n">
         <v>275708.2383467653</v>
       </c>
-      <c r="I141" s="5" t="inlineStr">
-        <is>
-          <t>2017-11-06</t>
-        </is>
-      </c>
-      <c r="J141" s="7" t="n">
-        <v>7227.395165267959</v>
-      </c>
     </row>
     <row r="142" ht="19" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
@@ -5883,14 +4751,6 @@
       <c r="H142" s="4" t="n">
         <v>270554.2762207136</v>
       </c>
-      <c r="I142" s="2" t="inlineStr">
-        <is>
-          <t>2017-11-13</t>
-        </is>
-      </c>
-      <c r="J142" s="4" t="n">
-        <v>1569.885015406565</v>
-      </c>
     </row>
     <row r="143" ht="19" customHeight="1">
       <c r="A143" s="5" t="inlineStr">
@@ -5921,14 +4781,6 @@
       <c r="H143" s="7" t="n">
         <v>258291.4008173491</v>
       </c>
-      <c r="I143" s="5" t="inlineStr">
-        <is>
-          <t>2017-11-14</t>
-        </is>
-      </c>
-      <c r="J143" s="7" t="n">
-        <v>1226.287540336449</v>
-      </c>
     </row>
     <row r="144" ht="19" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
@@ -5959,14 +4811,6 @@
       <c r="H144" s="4" t="n">
         <v>257777.9793028765</v>
       </c>
-      <c r="I144" s="2" t="inlineStr">
-        <is>
-          <t>2017-11-22</t>
-        </is>
-      </c>
-      <c r="J144" s="4" t="n">
-        <v>552.9154771243248</v>
-      </c>
     </row>
     <row r="145" ht="19" customHeight="1">
       <c r="A145" s="5" t="inlineStr">
@@ -5997,14 +4841,6 @@
       <c r="H145" s="7" t="n">
         <v>244618.5909473175</v>
       </c>
-      <c r="I145" s="5" t="inlineStr">
-        <is>
-          <t>2017-11-23</t>
-        </is>
-      </c>
-      <c r="J145" s="7" t="n">
-        <v>469.978155555676</v>
-      </c>
     </row>
     <row r="146" ht="19" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
@@ -6035,14 +4871,6 @@
       <c r="H146" s="4" t="n">
         <v>231715.9133489949</v>
       </c>
-      <c r="I146" s="2" t="inlineStr">
-        <is>
-          <t>2017-11-26</t>
-        </is>
-      </c>
-      <c r="J146" s="4" t="n">
-        <v>586.4853453783015</v>
-      </c>
     </row>
     <row r="147" ht="19" customHeight="1">
       <c r="A147" s="5" t="inlineStr">
@@ -6073,14 +4901,6 @@
       <c r="H147" s="7" t="n">
         <v>219188.4283958638</v>
       </c>
-      <c r="I147" s="5" t="inlineStr">
-        <is>
-          <t>2017-11-26</t>
-        </is>
-      </c>
-      <c r="J147" s="7" t="n">
-        <v>963.6526887023945</v>
-      </c>
     </row>
     <row r="148" ht="19" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
@@ -6111,14 +4931,6 @@
       <c r="H148" s="4" t="n">
         <v>206139.6231357297</v>
       </c>
-      <c r="I148" s="2" t="inlineStr">
-        <is>
-          <t>2017-11-26</t>
-        </is>
-      </c>
-      <c r="J148" s="4" t="n">
-        <v>932.0575185810045</v>
-      </c>
     </row>
     <row r="149" ht="19" customHeight="1">
       <c r="A149" s="5" t="inlineStr">
@@ -6149,14 +4961,6 @@
       <c r="H149" s="7" t="n">
         <v>280765.0479356897</v>
       </c>
-      <c r="I149" s="5" t="inlineStr">
-        <is>
-          <t>2018-01-08</t>
-        </is>
-      </c>
-      <c r="J149" s="7" t="n">
-        <v>7920.906538436422</v>
-      </c>
     </row>
     <row r="150" ht="19" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
@@ -6187,14 +4991,6 @@
       <c r="H150" s="4" t="n">
         <v>266185.2845914034</v>
       </c>
-      <c r="I150" s="2" t="inlineStr">
-        <is>
-          <t>2018-01-08</t>
-        </is>
-      </c>
-      <c r="J150" s="4" t="n">
-        <v>260.3529168622557</v>
-      </c>
     </row>
     <row r="151" ht="19" customHeight="1">
       <c r="A151" s="5" t="inlineStr">
@@ -6225,14 +5021,6 @@
       <c r="H151" s="7" t="n">
         <v>275988.2338254628</v>
       </c>
-      <c r="I151" s="5" t="inlineStr">
-        <is>
-          <t>2018-02-01</t>
-        </is>
-      </c>
-      <c r="J151" s="7" t="n">
-        <v>4247.282753896967</v>
-      </c>
     </row>
     <row r="152" ht="19" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
@@ -6263,14 +5051,6 @@
       <c r="H152" s="4" t="n">
         <v>261532.0277976535</v>
       </c>
-      <c r="I152" s="2" t="inlineStr">
-        <is>
-          <t>2018-02-04</t>
-        </is>
-      </c>
-      <c r="J152" s="4" t="n">
-        <v>688.390763229015</v>
-      </c>
     </row>
     <row r="153" ht="19" customHeight="1">
       <c r="A153" s="5" t="inlineStr">
@@ -6301,14 +5081,6 @@
       <c r="H153" s="7" t="n">
         <v>274922.5519708486</v>
       </c>
-      <c r="I153" s="5" t="inlineStr">
-        <is>
-          <t>2018-02-14</t>
-        </is>
-      </c>
-      <c r="J153" s="7" t="n">
-        <v>1416.496378182781</v>
-      </c>
     </row>
     <row r="154" ht="19" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
@@ -6339,14 +5111,6 @@
       <c r="H154" s="4" t="n">
         <v>261562.9171267727</v>
       </c>
-      <c r="I154" s="2" t="inlineStr">
-        <is>
-          <t>2018-02-15</t>
-        </is>
-      </c>
-      <c r="J154" s="4" t="n">
-        <v>1908.519263439416</v>
-      </c>
     </row>
     <row r="155" ht="19" customHeight="1">
       <c r="A155" s="5" t="inlineStr">
@@ -6377,14 +5141,6 @@
       <c r="H155" s="7" t="n">
         <v>253844.9976082628</v>
       </c>
-      <c r="I155" s="5" t="inlineStr">
-        <is>
-          <t>2018-02-15</t>
-        </is>
-      </c>
-      <c r="J155" s="7" t="n">
-        <v>7717.919518509918</v>
-      </c>
     </row>
     <row r="156" ht="19" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
@@ -6415,14 +5171,6 @@
       <c r="H156" s="4" t="n">
         <v>277448.857816673</v>
       </c>
-      <c r="I156" s="2" t="inlineStr">
-        <is>
-          <t>2018-05-16</t>
-        </is>
-      </c>
-      <c r="J156" s="4" t="n">
-        <v>3925.15117879621</v>
-      </c>
     </row>
     <row r="157" ht="19" customHeight="1">
       <c r="A157" s="5" t="inlineStr">
@@ -6453,14 +5201,6 @@
       <c r="H157" s="7" t="n">
         <v>274761.4861832982</v>
       </c>
-      <c r="I157" s="5" t="inlineStr">
-        <is>
-          <t>2018-07-02</t>
-        </is>
-      </c>
-      <c r="J157" s="7" t="n">
-        <v>401.5612785502587</v>
-      </c>
     </row>
     <row r="158" ht="19" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
@@ -6491,14 +5231,6 @@
       <c r="H158" s="4" t="n">
         <v>275352.7961978667</v>
       </c>
-      <c r="I158" s="2" t="inlineStr">
-        <is>
-          <t>2018-07-05</t>
-        </is>
-      </c>
-      <c r="J158" s="4" t="n">
-        <v>1643.753585274411</v>
-      </c>
     </row>
     <row r="159" ht="19" customHeight="1">
       <c r="A159" s="5" t="inlineStr">
@@ -6529,14 +5261,6 @@
       <c r="H159" s="7" t="n">
         <v>264365.020554019</v>
       </c>
-      <c r="I159" s="5" t="inlineStr">
-        <is>
-          <t>2018-07-05</t>
-        </is>
-      </c>
-      <c r="J159" s="7" t="n">
-        <v>5493.88782192387</v>
-      </c>
     </row>
     <row r="160" ht="19" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
@@ -6567,14 +5291,6 @@
       <c r="H160" s="4" t="n">
         <v>250094.1505009251</v>
       </c>
-      <c r="I160" s="2" t="inlineStr">
-        <is>
-          <t>2018-07-05</t>
-        </is>
-      </c>
-      <c r="J160" s="4" t="n">
-        <v>509.6739304676361</v>
-      </c>
     </row>
     <row r="161" ht="19" customHeight="1">
       <c r="A161" s="5" t="inlineStr">
@@ -6605,14 +5321,6 @@
       <c r="H161" s="7" t="n">
         <v>235598.2296213911</v>
       </c>
-      <c r="I161" s="5" t="inlineStr">
-        <is>
-          <t>2018-07-05</t>
-        </is>
-      </c>
-      <c r="J161" s="7" t="n">
-        <v>1610.657875503785</v>
-      </c>
     </row>
     <row r="162" ht="19" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
@@ -6643,14 +5351,6 @@
       <c r="H162" s="4" t="n">
         <v>221186.1512066093</v>
       </c>
-      <c r="I162" s="2" t="inlineStr">
-        <is>
-          <t>2018-07-05</t>
-        </is>
-      </c>
-      <c r="J162" s="4" t="n">
-        <v>626.6121049905136</v>
-      </c>
     </row>
     <row r="163" ht="19" customHeight="1">
       <c r="A163" s="5" t="inlineStr">
@@ -6681,14 +5381,6 @@
       <c r="H163" s="7" t="n">
         <v>206800.5493596439</v>
       </c>
-      <c r="I163" s="5" t="inlineStr">
-        <is>
-          <t>2018-07-05</t>
-        </is>
-      </c>
-      <c r="J163" s="7" t="n">
-        <v>719.2800923482656</v>
-      </c>
     </row>
     <row r="164" ht="19" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
@@ -6719,14 +5411,6 @@
       <c r="H164" s="4" t="n">
         <v>275939.6934511324</v>
       </c>
-      <c r="I164" s="2" t="inlineStr">
-        <is>
-          <t>2018-07-16</t>
-        </is>
-      </c>
-      <c r="J164" s="4" t="n">
-        <v>589.1036339171378</v>
-      </c>
     </row>
     <row r="165" ht="19" customHeight="1">
       <c r="A165" s="5" t="inlineStr">
@@ -6757,14 +5441,6 @@
       <c r="H165" s="7" t="n">
         <v>275516.0683660684</v>
       </c>
-      <c r="I165" s="5" t="inlineStr">
-        <is>
-          <t>2018-07-30</t>
-        </is>
-      </c>
-      <c r="J165" s="7" t="n">
-        <v>611.1674404308883</v>
-      </c>
     </row>
     <row r="166" ht="19" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
@@ -6795,14 +5471,6 @@
       <c r="H166" s="4" t="n">
         <v>279368.4089833692</v>
       </c>
-      <c r="I166" s="2" t="inlineStr">
-        <is>
-          <t>2018-08-14</t>
-        </is>
-      </c>
-      <c r="J166" s="4" t="n">
-        <v>3746.434346034831</v>
-      </c>
     </row>
     <row r="167" ht="19" customHeight="1">
       <c r="A167" s="5" t="inlineStr">
@@ -6833,14 +5501,6 @@
       <c r="H167" s="7" t="n">
         <v>264773.2009745233</v>
       </c>
-      <c r="I167" s="5" t="inlineStr">
-        <is>
-          <t>2018-08-14</t>
-        </is>
-      </c>
-      <c r="J167" s="7" t="n">
-        <v>695.0099051831401</v>
-      </c>
     </row>
     <row r="168" ht="19" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
@@ -6871,14 +5531,6 @@
       <c r="H168" s="4" t="n">
         <v>251314.2790011355</v>
       </c>
-      <c r="I168" s="2" t="inlineStr">
-        <is>
-          <t>2018-08-15</t>
-        </is>
-      </c>
-      <c r="J168" s="4" t="n">
-        <v>1345.892197338779</v>
-      </c>
     </row>
     <row r="169" ht="19" customHeight="1">
       <c r="A169" s="5" t="inlineStr">
@@ -6909,14 +5561,6 @@
       <c r="H169" s="7" t="n">
         <v>236672.7369986106</v>
       </c>
-      <c r="I169" s="5" t="inlineStr">
-        <is>
-          <t>2018-08-15</t>
-        </is>
-      </c>
-      <c r="J169" s="7" t="n">
-        <v>174.3040714586288</v>
-      </c>
     </row>
     <row r="170" ht="19" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
@@ -6947,14 +5591,6 @@
       <c r="H170" s="4" t="n">
         <v>263142.685673157</v>
       </c>
-      <c r="I170" s="2" t="inlineStr">
-        <is>
-          <t>2018-08-19</t>
-        </is>
-      </c>
-      <c r="J170" s="4" t="n">
-        <v>595.7227758712629</v>
-      </c>
     </row>
     <row r="171" ht="19" customHeight="1">
       <c r="A171" s="5" t="inlineStr">
@@ -6985,14 +5621,6 @@
       <c r="H171" s="7" t="n">
         <v>277612.1299848746</v>
       </c>
-      <c r="I171" s="5" t="inlineStr">
-        <is>
-          <t>2018-09-02</t>
-        </is>
-      </c>
-      <c r="J171" s="7" t="n">
-        <v>174.3040714586288</v>
-      </c>
     </row>
     <row r="172" ht="19" customHeight="1">
       <c r="A172" s="2" t="inlineStr">
@@ -7023,14 +5651,6 @@
       <c r="H172" s="4" t="n">
         <v>267021.5028582743</v>
       </c>
-      <c r="I172" s="2" t="inlineStr">
-        <is>
-          <t>2018-09-05</t>
-        </is>
-      </c>
-      <c r="J172" s="4" t="n">
-        <v>5295.313563300115</v>
-      </c>
     </row>
     <row r="173" ht="19" customHeight="1">
       <c r="A173" s="5" t="inlineStr">
@@ -7061,14 +5681,6 @@
       <c r="H173" s="7" t="n">
         <v>252724.156237364</v>
       </c>
-      <c r="I173" s="5" t="inlineStr">
-        <is>
-          <t>2018-09-05</t>
-        </is>
-      </c>
-      <c r="J173" s="7" t="n">
-        <v>1191.445551742526</v>
-      </c>
     </row>
     <row r="174" ht="19" customHeight="1">
       <c r="A174" s="2" t="inlineStr">
@@ -7099,14 +5711,6 @@
       <c r="H174" s="4" t="n">
         <v>279566.9832419928</v>
       </c>
-      <c r="I174" s="2" t="inlineStr">
-        <is>
-          <t>2018-10-15</t>
-        </is>
-      </c>
-      <c r="J174" s="4" t="n">
-        <v>286.8294846787562</v>
-      </c>
     </row>
     <row r="175" ht="19" customHeight="1">
       <c r="A175" s="5" t="inlineStr">
@@ -7137,14 +5741,6 @@
       <c r="H175" s="7" t="n">
         <v>279897.940339699</v>
       </c>
-      <c r="I175" s="5" t="inlineStr">
-        <is>
-          <t>2018-11-01</t>
-        </is>
-      </c>
-      <c r="J175" s="7" t="n">
-        <v>1191.445551742526</v>
-      </c>
     </row>
     <row r="176" ht="19" customHeight="1">
       <c r="A176" s="2" t="inlineStr">
@@ -7175,14 +5771,6 @@
       <c r="H176" s="4" t="n">
         <v>279712.6043649836</v>
       </c>
-      <c r="I176" s="2" t="inlineStr">
-        <is>
-          <t>2018-11-28</t>
-        </is>
-      </c>
-      <c r="J176" s="4" t="n">
-        <v>317.7188137980069</v>
-      </c>
     </row>
     <row r="177" ht="19" customHeight="1">
       <c r="A177" s="5" t="inlineStr">
@@ -7213,14 +5801,6 @@
       <c r="H177" s="7" t="n">
         <v>280902.6378331092</v>
       </c>
-      <c r="I177" s="5" t="inlineStr">
-        <is>
-          <t>2018-12-04</t>
-        </is>
-      </c>
-      <c r="J177" s="7" t="n">
-        <v>1705.532243512912</v>
-      </c>
     </row>
     <row r="178" ht="19" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
@@ -7251,14 +5831,6 @@
       <c r="H178" s="4" t="n">
         <v>280143.6428890362</v>
       </c>
-      <c r="I178" s="2" t="inlineStr">
-        <is>
-          <t>2018-12-10</t>
-        </is>
-      </c>
-      <c r="J178" s="4" t="n">
-        <v>595.7227758712629</v>
-      </c>
     </row>
     <row r="179" ht="19" customHeight="1">
       <c r="A179" s="5" t="inlineStr">
@@ -7289,14 +5861,6 @@
       <c r="H179" s="7" t="n">
         <v>281555.7265059162</v>
       </c>
-      <c r="I179" s="5" t="inlineStr">
-        <is>
-          <t>2018-12-12</t>
-        </is>
-      </c>
-      <c r="J179" s="7" t="n">
-        <v>1341.479436036029</v>
-      </c>
     </row>
     <row r="180" ht="19" customHeight="1">
       <c r="A180" s="2" t="inlineStr">
@@ -7327,14 +5891,6 @@
       <c r="H180" s="4" t="n">
         <v>267434.8903371159</v>
       </c>
-      <c r="I180" s="2" t="inlineStr">
-        <is>
-          <t>2018-12-16</t>
-        </is>
-      </c>
-      <c r="J180" s="4" t="n">
-        <v>706.0418084400153</v>
-      </c>
     </row>
     <row r="181" ht="19" customHeight="1">
       <c r="A181" s="5" t="inlineStr">
@@ -7365,14 +5921,6 @@
       <c r="H181" s="7" t="n">
         <v>253737.6792533796</v>
       </c>
-      <c r="I181" s="5" t="inlineStr">
-        <is>
-          <t>2018-12-18</t>
-        </is>
-      </c>
-      <c r="J181" s="7" t="n">
-        <v>1712.151385467037</v>
-      </c>
     </row>
     <row r="182" ht="19" customHeight="1">
       <c r="A182" s="2" t="inlineStr">
@@ -7403,14 +5951,6 @@
       <c r="H182" s="4" t="n">
         <v>280159.3055137739</v>
       </c>
-      <c r="I182" s="2" t="inlineStr">
-        <is>
-          <t>2019-01-06</t>
-        </is>
-      </c>
-      <c r="J182" s="4" t="n">
-        <v>335.2733751157606</v>
-      </c>
     </row>
     <row r="183" ht="19" customHeight="1">
       <c r="A183" s="5" t="inlineStr">
@@ -7441,14 +5981,6 @@
       <c r="H183" s="7" t="n">
         <v>263967.5736920069</v>
       </c>
-      <c r="I183" s="5" t="inlineStr">
-        <is>
-          <t>2019-01-10</t>
-        </is>
-      </c>
-      <c r="J183" s="7" t="n">
-        <v>2023.966477720878</v>
-      </c>
     </row>
     <row r="184" ht="19" customHeight="1">
       <c r="A184" s="2" t="inlineStr">
@@ -7479,14 +6011,6 @@
       <c r="H184" s="4" t="n">
         <v>248059.3450918451</v>
       </c>
-      <c r="I184" s="2" t="inlineStr">
-        <is>
-          <t>2019-01-10</t>
-        </is>
-      </c>
-      <c r="J184" s="4" t="n">
-        <v>589.1936518578441</v>
-      </c>
     </row>
     <row r="185" ht="19" customHeight="1">
       <c r="A185" s="5" t="inlineStr">
@@ -7517,14 +6041,6 @@
       <c r="H185" s="7" t="n">
         <v>286009.3328604629</v>
       </c>
-      <c r="I185" s="5" t="inlineStr">
-        <is>
-          <t>2019-01-20</t>
-        </is>
-      </c>
-      <c r="J185" s="7" t="n">
-        <v>4311.714213804892</v>
-      </c>
     </row>
     <row r="186" ht="19" customHeight="1">
       <c r="A186" s="2" t="inlineStr">
@@ -7555,14 +6071,6 @@
       <c r="H186" s="4" t="n">
         <v>282767.5351525422</v>
       </c>
-      <c r="I186" s="2" t="inlineStr">
-        <is>
-          <t>2019-01-23</t>
-        </is>
-      </c>
-      <c r="J186" s="4" t="n">
-        <v>167.6366875578803</v>
-      </c>
     </row>
     <row r="187" ht="19" customHeight="1">
       <c r="A187" s="5" t="inlineStr">
@@ -7593,14 +6101,6 @@
       <c r="H187" s="7" t="n">
         <v>284424.1800648788</v>
       </c>
-      <c r="I187" s="5" t="inlineStr">
-        <is>
-          <t>2019-03-03</t>
-        </is>
-      </c>
-      <c r="J187" s="7" t="n">
-        <v>2502.22408634189</v>
-      </c>
     </row>
     <row r="188" ht="19" customHeight="1">
       <c r="A188" s="2" t="inlineStr">
@@ -7631,14 +6131,6 @@
       <c r="H188" s="4" t="n">
         <v>268538.1386733644</v>
       </c>
-      <c r="I188" s="2" t="inlineStr">
-        <is>
-          <t>2019-03-06</t>
-        </is>
-      </c>
-      <c r="J188" s="4" t="n">
-        <v>882.5578550841346</v>
-      </c>
     </row>
     <row r="189" ht="19" customHeight="1">
       <c r="A189" s="5" t="inlineStr">
@@ -7669,14 +6161,6 @@
       <c r="H189" s="7" t="n">
         <v>252119.6042743132</v>
       </c>
-      <c r="I189" s="5" t="inlineStr">
-        <is>
-          <t>2019-03-06</t>
-        </is>
-      </c>
-      <c r="J189" s="7" t="n">
-        <v>443.7441729473302</v>
-      </c>
     </row>
     <row r="190" ht="19" customHeight="1">
       <c r="A190" s="2" t="inlineStr">
@@ -7707,14 +6191,6 @@
       <c r="H190" s="4" t="n">
         <v>268972.0218646907</v>
       </c>
-      <c r="I190" s="2" t="inlineStr">
-        <is>
-          <t>2019-03-09</t>
-        </is>
-      </c>
-      <c r="J190" s="4" t="n">
-        <v>332.8081297104977</v>
-      </c>
     </row>
     <row r="191" ht="19" customHeight="1">
       <c r="A191" s="5" t="inlineStr">
@@ -7745,14 +6221,6 @@
       <c r="H191" s="7" t="n">
         <v>285622.2893318366</v>
       </c>
-      <c r="I191" s="5" t="inlineStr">
-        <is>
-          <t>2019-04-24</t>
-        </is>
-      </c>
-      <c r="J191" s="7" t="n">
-        <v>337.7386205210236</v>
-      </c>
     </row>
     <row r="192" ht="19" customHeight="1">
       <c r="A192" s="2" t="inlineStr">
@@ -7783,14 +6251,6 @@
       <c r="H192" s="4" t="n">
         <v>285794.856510205</v>
       </c>
-      <c r="I192" s="2" t="inlineStr">
-        <is>
-          <t>2019-05-22</t>
-        </is>
-      </c>
-      <c r="J192" s="4" t="n">
-        <v>172.5671783684062</v>
-      </c>
     </row>
     <row r="193" ht="19" customHeight="1">
       <c r="A193" s="5" t="inlineStr">
@@ -7821,14 +6281,6 @@
       <c r="H193" s="7" t="n">
         <v>285770.2040561524</v>
       </c>
-      <c r="I193" s="5" t="inlineStr">
-        <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="J193" s="7" t="n">
-        <v>273.642239984187</v>
-      </c>
     </row>
     <row r="194" ht="19" customHeight="1">
       <c r="A194" s="2" t="inlineStr">
@@ -7859,14 +6311,6 @@
       <c r="H194" s="4" t="n">
         <v>270204.6445673222</v>
       </c>
-      <c r="I194" s="2" t="inlineStr">
-        <is>
-          <t>2019-07-16</t>
-        </is>
-      </c>
-      <c r="J194" s="4" t="n">
-        <v>1415.050862620931</v>
-      </c>
     </row>
     <row r="195" ht="19" customHeight="1">
       <c r="A195" s="5" t="inlineStr">
@@ -7897,14 +6341,6 @@
       <c r="H195" s="7" t="n">
         <v>253860.0675304288</v>
       </c>
-      <c r="I195" s="5" t="inlineStr">
-        <is>
-          <t>2019-07-17</t>
-        </is>
-      </c>
-      <c r="J195" s="7" t="n">
-        <v>160.2409513420915</v>
-      </c>
     </row>
     <row r="196" ht="19" customHeight="1">
       <c r="A196" s="2" t="inlineStr">
@@ -7935,14 +6371,6 @@
       <c r="H196" s="4" t="n">
         <v>253613.5429899025</v>
       </c>
-      <c r="I196" s="2" t="inlineStr">
-        <is>
-          <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="J196" s="4" t="n">
-        <v>579.3326702367923</v>
-      </c>
     </row>
     <row r="197" ht="19" customHeight="1">
       <c r="A197" s="5" t="inlineStr">
@@ -7973,14 +6401,6 @@
       <c r="H197" s="7" t="n">
         <v>286352.0019717945</v>
       </c>
-      <c r="I197" s="5" t="inlineStr">
-        <is>
-          <t>2019-08-12</t>
-        </is>
-      </c>
-      <c r="J197" s="7" t="n">
-        <v>1508.730188020923</v>
-      </c>
     </row>
     <row r="198" ht="19" customHeight="1">
       <c r="A198" s="2" t="inlineStr">
@@ -8011,14 +6431,6 @@
       <c r="H198" s="4" t="n">
         <v>285020.7694529525</v>
       </c>
-      <c r="I198" s="2" t="inlineStr">
-        <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
-      <c r="J198" s="4" t="n">
-        <v>1343.558745868306</v>
-      </c>
     </row>
     <row r="199" ht="19" customHeight="1">
       <c r="A199" s="5" t="inlineStr">
@@ -8049,14 +6461,6 @@
       <c r="H199" s="7" t="n">
         <v>285427.5349448209</v>
       </c>
-      <c r="I199" s="5" t="inlineStr">
-        <is>
-          <t>2019-08-22</t>
-        </is>
-      </c>
-      <c r="J199" s="7" t="n">
-        <v>391.9740194368084</v>
-      </c>
     </row>
     <row r="200" ht="19" customHeight="1">
       <c r="A200" s="2" t="inlineStr">
@@ -8087,14 +6491,6 @@
       <c r="H200" s="4" t="n">
         <v>269502.0496268222</v>
       </c>
-      <c r="I200" s="2" t="inlineStr">
-        <is>
-          <t>2019-09-03</t>
-        </is>
-      </c>
-      <c r="J200" s="4" t="n">
-        <v>936.7932539999194</v>
-      </c>
     </row>
     <row r="201" ht="19" customHeight="1">
       <c r="A201" s="5" t="inlineStr">
@@ -8125,14 +6521,6 @@
       <c r="H201" s="7" t="n">
         <v>269134.7280614381</v>
       </c>
-      <c r="I201" s="5" t="inlineStr">
-        <is>
-          <t>2019-09-04</t>
-        </is>
-      </c>
-      <c r="J201" s="7" t="n">
-        <v>1094.568959936748</v>
-      </c>
     </row>
     <row r="202" ht="19" customHeight="1">
       <c r="A202" s="2" t="inlineStr">
@@ -8163,14 +6551,6 @@
       <c r="H202" s="4" t="n">
         <v>253081.0499823658</v>
       </c>
-      <c r="I202" s="2" t="inlineStr">
-        <is>
-          <t>2019-09-04</t>
-        </is>
-      </c>
-      <c r="J202" s="4" t="n">
-        <v>729.7126399578319</v>
-      </c>
     </row>
     <row r="203" ht="19" customHeight="1">
       <c r="A203" s="5" t="inlineStr">
@@ -8201,14 +6581,6 @@
       <c r="H203" s="7" t="n">
         <v>285767.7388107472</v>
       </c>
-      <c r="I203" s="5" t="inlineStr">
-        <is>
-          <t>2019-09-18</t>
-        </is>
-      </c>
-      <c r="J203" s="7" t="n">
-        <v>1797.163900436688</v>
-      </c>
     </row>
     <row r="204" ht="19" customHeight="1">
       <c r="A204" s="2" t="inlineStr">
@@ -8239,14 +6611,6 @@
       <c r="H204" s="4" t="n">
         <v>269664.7558235696</v>
       </c>
-      <c r="I204" s="2" t="inlineStr">
-        <is>
-          <t>2019-09-18</t>
-        </is>
-      </c>
-      <c r="J204" s="4" t="n">
-        <v>700.1296950946765</v>
-      </c>
     </row>
     <row r="205" ht="19" customHeight="1">
       <c r="A205" s="5" t="inlineStr">
@@ -8277,14 +6641,6 @@
       <c r="H205" s="7" t="n">
         <v>286169.573811805</v>
       </c>
-      <c r="I205" s="5" t="inlineStr">
-        <is>
-          <t>2019-10-03</t>
-        </is>
-      </c>
-      <c r="J205" s="7" t="n">
-        <v>384.5782832210195</v>
-      </c>
     </row>
     <row r="206" ht="19" customHeight="1">
       <c r="A206" s="2" t="inlineStr">
@@ -8315,14 +6671,6 @@
       <c r="H206" s="4" t="n">
         <v>286672.4838744787</v>
       </c>
-      <c r="I206" s="2" t="inlineStr">
-        <is>
-          <t>2019-10-21</t>
-        </is>
-      </c>
-      <c r="J206" s="4" t="n">
-        <v>613.8461059104735</v>
-      </c>
     </row>
     <row r="207" ht="19" customHeight="1">
       <c r="A207" s="5" t="inlineStr">
@@ -8353,14 +6701,6 @@
       <c r="H207" s="7" t="n">
         <v>286667.5533836681</v>
       </c>
-      <c r="I207" s="5" t="inlineStr">
-        <is>
-          <t>2019-11-11</t>
-        </is>
-      </c>
-      <c r="J207" s="7" t="n">
-        <v>231.7330680947169</v>
-      </c>
     </row>
     <row r="208" ht="19" customHeight="1">
       <c r="A208" s="2" t="inlineStr">
@@ -8391,14 +6731,6 @@
       <c r="H208" s="4" t="n">
         <v>288565.7923457206</v>
       </c>
-      <c r="I208" s="2" t="inlineStr">
-        <is>
-          <t>2019-11-18</t>
-        </is>
-      </c>
-      <c r="J208" s="4" t="n">
-        <v>231.7330680947169</v>
-      </c>
     </row>
     <row r="209" ht="19" customHeight="1">
       <c r="A209" s="5" t="inlineStr">
@@ -8429,14 +6761,6 @@
       <c r="H209" s="7" t="n">
         <v>289320.157439731</v>
       </c>
-      <c r="I209" s="5" t="inlineStr">
-        <is>
-          <t>2019-11-27</t>
-        </is>
-      </c>
-      <c r="J209" s="7" t="n">
-        <v>226.802577284191</v>
-      </c>
     </row>
     <row r="210" ht="19" customHeight="1">
       <c r="A210" s="2" t="inlineStr">
@@ -8467,14 +6791,6 @@
       <c r="H210" s="4" t="n">
         <v>290106.5707240099</v>
       </c>
-      <c r="I210" s="2" t="inlineStr">
-        <is>
-          <t>2019-12-04</t>
-        </is>
-      </c>
-      <c r="J210" s="4" t="n">
-        <v>382.1130378157566</v>
-      </c>
     </row>
     <row r="211" ht="19" customHeight="1">
       <c r="A211" s="5" t="inlineStr">
@@ -8505,14 +6821,6 @@
       <c r="H211" s="7" t="n">
         <v>274013.4487184534</v>
       </c>
-      <c r="I211" s="5" t="inlineStr">
-        <is>
-          <t>2019-12-09</t>
-        </is>
-      </c>
-      <c r="J211" s="7" t="n">
-        <v>1005.820125347282</v>
-      </c>
     </row>
     <row r="212" ht="19" customHeight="1">
       <c r="A212" s="2" t="inlineStr">
@@ -8543,14 +6851,6 @@
       <c r="H212" s="4" t="n">
         <v>257994.2840750547</v>
       </c>
-      <c r="I212" s="2" t="inlineStr">
-        <is>
-          <t>2019-12-09</t>
-        </is>
-      </c>
-      <c r="J212" s="4" t="n">
-        <v>843.1139285999275</v>
-      </c>
     </row>
     <row r="213" ht="19" customHeight="1">
       <c r="A213" s="5" t="inlineStr">
@@ -8581,14 +6881,6 @@
       <c r="H213" s="7" t="n">
         <v>290743.1330345908</v>
       </c>
-      <c r="I213" s="5" t="inlineStr">
-        <is>
-          <t>2020-01-01</t>
-        </is>
-      </c>
-      <c r="J213" s="7" t="n">
-        <v>669.6141039324184</v>
-      </c>
     </row>
     <row r="214" ht="19" customHeight="1">
       <c r="A214" s="2" t="inlineStr">
@@ -8619,14 +6911,6 @@
       <c r="H214" s="4" t="n">
         <v>272611.1955700833</v>
       </c>
-      <c r="I214" s="2" t="inlineStr">
-        <is>
-          <t>2020-01-13</t>
-        </is>
-      </c>
-      <c r="J214" s="4" t="n">
-        <v>259.0276780643923</v>
-      </c>
     </row>
     <row r="215" ht="19" customHeight="1">
       <c r="A215" s="5" t="inlineStr">
@@ -8657,14 +6941,6 @@
       <c r="H215" s="7" t="n">
         <v>275887.6201362382</v>
       </c>
-      <c r="I215" s="5" t="inlineStr">
-        <is>
-          <t>2020-01-15</t>
-        </is>
-      </c>
-      <c r="J215" s="7" t="n">
-        <v>451.9206298144717</v>
-      </c>
     </row>
     <row r="216" ht="19" customHeight="1">
       <c r="A216" s="2" t="inlineStr">
@@ -8695,14 +6971,6 @@
       <c r="H216" s="4" t="n">
         <v>275716.7720932596</v>
       </c>
-      <c r="I216" s="2" t="inlineStr">
-        <is>
-          <t>2020-02-03</t>
-        </is>
-      </c>
-      <c r="J216" s="4" t="n">
-        <v>148.8031342072041</v>
-      </c>
     </row>
     <row r="217" ht="19" customHeight="1">
       <c r="A217" s="5" t="inlineStr">
@@ -8733,14 +7001,6 @@
       <c r="H217" s="7" t="n">
         <v>278362.1611458322</v>
       </c>
-      <c r="I217" s="5" t="inlineStr">
-        <is>
-          <t>2020-02-17</t>
-        </is>
-      </c>
-      <c r="J217" s="7" t="n">
-        <v>275.5613596429706</v>
-      </c>
     </row>
     <row r="218" ht="19" customHeight="1">
       <c r="A218" s="2" t="inlineStr">
@@ -8771,14 +7031,6 @@
       <c r="H218" s="4" t="n">
         <v>260671.1218567535</v>
       </c>
-      <c r="I218" s="2" t="inlineStr">
-        <is>
-          <t>2020-02-17</t>
-        </is>
-      </c>
-      <c r="J218" s="4" t="n">
-        <v>1474.253274089892</v>
-      </c>
     </row>
     <row r="219" ht="19" customHeight="1">
       <c r="A219" s="5" t="inlineStr">
@@ -8809,14 +7061,6 @@
       <c r="H219" s="7" t="n">
         <v>243531.2052869607</v>
       </c>
-      <c r="I219" s="5" t="inlineStr">
-        <is>
-          <t>2020-02-17</t>
-        </is>
-      </c>
-      <c r="J219" s="7" t="n">
-        <v>1713.991656979277</v>
-      </c>
     </row>
     <row r="220" ht="19" customHeight="1">
       <c r="A220" s="2" t="inlineStr">
@@ -8847,14 +7091,6 @@
       <c r="H220" s="4" t="n">
         <v>303206.7733312424</v>
       </c>
-      <c r="I220" s="2" t="inlineStr">
-        <is>
-          <t>2020-07-02</t>
-        </is>
-      </c>
-      <c r="J220" s="4" t="n">
-        <v>270.0501324501112</v>
-      </c>
     </row>
     <row r="221" ht="19" customHeight="1">
       <c r="A221" s="5" t="inlineStr">
@@ -8885,14 +7121,6 @@
       <c r="H221" s="7" t="n">
         <v>304849.1190347145</v>
       </c>
-      <c r="I221" s="5" t="inlineStr">
-        <is>
-          <t>2020-07-07</t>
-        </is>
-      </c>
-      <c r="J221" s="7" t="n">
-        <v>2066.710197322279</v>
-      </c>
     </row>
     <row r="222" ht="19" customHeight="1">
       <c r="A222" s="2" t="inlineStr">
@@ -8923,14 +7151,6 @@
       <c r="H222" s="4" t="n">
         <v>286593.1789583677</v>
       </c>
-      <c r="I222" s="2" t="inlineStr">
-        <is>
-          <t>2020-07-07</t>
-        </is>
-      </c>
-      <c r="J222" s="4" t="n">
-        <v>146.0475206107744</v>
-      </c>
     </row>
     <row r="223" ht="19" customHeight="1">
       <c r="A223" s="5" t="inlineStr">
@@ -8961,14 +7181,6 @@
       <c r="H223" s="7" t="n">
         <v>269177.7010289319</v>
       </c>
-      <c r="I223" s="5" t="inlineStr">
-        <is>
-          <t>2020-07-07</t>
-        </is>
-      </c>
-      <c r="J223" s="7" t="n">
-        <v>1741.547792943574</v>
-      </c>
     </row>
     <row r="224" ht="19" customHeight="1">
       <c r="A224" s="2" t="inlineStr">
@@ -8999,14 +7211,6 @@
       <c r="H224" s="4" t="n">
         <v>310352.0793867846</v>
       </c>
-      <c r="I224" s="2" t="inlineStr">
-        <is>
-          <t>2020-08-09</t>
-        </is>
-      </c>
-      <c r="J224" s="4" t="n">
-        <v>6861.477855109967</v>
-      </c>
     </row>
     <row r="225" ht="19" customHeight="1">
       <c r="A225" s="5" t="inlineStr">
@@ -9037,14 +7241,6 @@
       <c r="H225" s="7" t="n">
         <v>292371.7006700808</v>
       </c>
-      <c r="I225" s="5" t="inlineStr">
-        <is>
-          <t>2020-08-10</t>
-        </is>
-      </c>
-      <c r="J225" s="7" t="n">
-        <v>399.5639714823073</v>
-      </c>
     </row>
     <row r="226" ht="19" customHeight="1">
       <c r="A226" s="2" t="inlineStr">
@@ -9075,14 +7271,6 @@
       <c r="H226" s="4" t="n">
         <v>292900.7784805953</v>
       </c>
-      <c r="I226" s="2" t="inlineStr">
-        <is>
-          <t>2020-08-18</t>
-        </is>
-      </c>
-      <c r="J226" s="4" t="n">
-        <v>256.2720644679626</v>
-      </c>
     </row>
     <row r="227" ht="19" customHeight="1">
       <c r="A227" s="5" t="inlineStr">
@@ -9113,14 +7301,6 @@
       <c r="H227" s="7" t="n">
         <v>293159.8061586596</v>
       </c>
-      <c r="I227" s="5" t="inlineStr">
-        <is>
-          <t>2020-08-25</t>
-        </is>
-      </c>
-      <c r="J227" s="7" t="n">
-        <v>259.0276780643923</v>
-      </c>
     </row>
     <row r="228" ht="19" customHeight="1">
       <c r="A228" s="2" t="inlineStr">
@@ -9151,14 +7331,6 @@
       <c r="H228" s="4" t="n">
         <v>274890.0880143307</v>
       </c>
-      <c r="I228" s="2" t="inlineStr">
-        <is>
-          <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="J228" s="4" t="n">
-        <v>468.4543113930499</v>
-      </c>
     </row>
     <row r="229" ht="19" customHeight="1">
       <c r="A229" s="5" t="inlineStr">
@@ -9189,14 +7361,6 @@
       <c r="H229" s="7" t="n">
         <v>256785.7066857875</v>
       </c>
-      <c r="I229" s="5" t="inlineStr">
-        <is>
-          <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="J229" s="7" t="n">
-        <v>402.319585078737</v>
-      </c>
     </row>
     <row r="230" ht="19" customHeight="1">
       <c r="A230" s="2" t="inlineStr">
@@ -9227,14 +7391,6 @@
       <c r="H230" s="4" t="n">
         <v>239053.3331927623</v>
       </c>
-      <c r="I230" s="2" t="inlineStr">
-        <is>
-          <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="J230" s="4" t="n">
-        <v>1182.158232868344</v>
-      </c>
     </row>
     <row r="231" ht="19" customHeight="1">
       <c r="A231" s="5" t="inlineStr">
@@ -9265,14 +7421,6 @@
       <c r="H231" s="7" t="n">
         <v>239582.4110032769</v>
       </c>
-      <c r="I231" s="5" t="inlineStr">
-        <is>
-          <t>2020-08-27</t>
-        </is>
-      </c>
-      <c r="J231" s="7" t="n">
-        <v>529.0778105145034</v>
-      </c>
     </row>
     <row r="232" ht="19" customHeight="1">
       <c r="A232" s="2" t="inlineStr">
@@ -9303,14 +7451,6 @@
       <c r="H232" s="4" t="n">
         <v>313322.6308437358</v>
       </c>
-      <c r="I232" s="2" t="inlineStr">
-        <is>
-          <t>2020-10-29</t>
-        </is>
-      </c>
-      <c r="J232" s="4" t="n">
-        <v>1598.255885929229</v>
-      </c>
     </row>
     <row r="233" ht="19" customHeight="1">
       <c r="A233" s="5" t="inlineStr">
@@ -9341,14 +7481,6 @@
       <c r="H233" s="7" t="n">
         <v>314281.5843752933</v>
       </c>
-      <c r="I233" s="5" t="inlineStr">
-        <is>
-          <t>2020-11-11</t>
-        </is>
-      </c>
-      <c r="J233" s="7" t="n">
-        <v>1154.602096904047</v>
-      </c>
     </row>
     <row r="234" ht="19" customHeight="1">
       <c r="A234" s="2" t="inlineStr">
@@ -9379,14 +7511,6 @@
       <c r="H234" s="4" t="n">
         <v>312955.064934794</v>
       </c>
-      <c r="I234" s="2" t="inlineStr">
-        <is>
-          <t>2021-01-11</t>
-        </is>
-      </c>
-      <c r="J234" s="4" t="n">
-        <v>341.7598345275014</v>
-      </c>
     </row>
     <row r="235" ht="19" customHeight="1">
       <c r="A235" s="5" t="inlineStr">
@@ -9417,14 +7541,6 @@
       <c r="H235" s="7" t="n">
         <v>313804.8461449704</v>
       </c>
-      <c r="I235" s="5" t="inlineStr">
-        <is>
-          <t>2021-02-08</t>
-        </is>
-      </c>
-      <c r="J235" s="7" t="n">
-        <v>1102.252439286896</v>
-      </c>
     </row>
     <row r="236" ht="19" customHeight="1">
       <c r="A236" s="2" t="inlineStr">
@@ -9455,14 +7571,6 @@
       <c r="H236" s="4" t="n">
         <v>316508.1356469087</v>
       </c>
-      <c r="I236" s="2" t="inlineStr">
-        <is>
-          <t>2021-03-22</t>
-        </is>
-      </c>
-      <c r="J236" s="4" t="n">
-        <v>1003.727081585274</v>
-      </c>
     </row>
     <row r="237" ht="19" customHeight="1">
       <c r="A237" s="5" t="inlineStr">
@@ -9493,14 +7601,6 @@
       <c r="H237" s="7" t="n">
         <v>315301.2000150638</v>
       </c>
-      <c r="I237" s="5" t="inlineStr">
-        <is>
-          <t>2021-04-01</t>
-        </is>
-      </c>
-      <c r="J237" s="7" t="n">
-        <v>634.2569902041918</v>
-      </c>
     </row>
     <row r="238" ht="19" customHeight="1">
       <c r="A238" s="2" t="inlineStr">
@@ -9531,14 +7631,6 @@
       <c r="H238" s="4" t="n">
         <v>317961.3846730076</v>
       </c>
-      <c r="I238" s="2" t="inlineStr">
-        <is>
-          <t>2021-04-22</t>
-        </is>
-      </c>
-      <c r="J238" s="4" t="n">
-        <v>9310.646302803279</v>
-      </c>
     </row>
     <row r="239" ht="19" customHeight="1">
       <c r="A239" s="5" t="inlineStr">
@@ -9569,14 +7661,6 @@
       <c r="H239" s="7" t="n">
         <v>300974.9972217623</v>
       </c>
-      <c r="I239" s="5" t="inlineStr">
-        <is>
-          <t>2021-05-02</t>
-        </is>
-      </c>
-      <c r="J239" s="7" t="n">
-        <v>5662.12915041509</v>
-      </c>
     </row>
     <row r="240" ht="19" customHeight="1">
       <c r="A240" s="2" t="inlineStr">
@@ -9607,14 +7691,6 @@
       <c r="H240" s="4" t="n">
         <v>333580.7327861428</v>
       </c>
-      <c r="I240" s="2" t="inlineStr">
-        <is>
-          <t>2021-05-13</t>
-        </is>
-      </c>
-      <c r="J240" s="4" t="n">
-        <v>723.5455956212867</v>
-      </c>
     </row>
     <row r="241" ht="19" customHeight="1">
       <c r="A241" s="5" t="inlineStr">
@@ -9645,14 +7721,6 @@
       <c r="H241" s="7" t="n">
         <v>313583.1640901418</v>
       </c>
-      <c r="I241" s="5" t="inlineStr">
-        <is>
-          <t>2021-05-16</t>
-        </is>
-      </c>
-      <c r="J241" s="7" t="n">
-        <v>1333.171246400073</v>
-      </c>
     </row>
     <row r="242" ht="19" customHeight="1">
       <c r="A242" s="2" t="inlineStr">
@@ -9683,14 +7751,6 @@
       <c r="H242" s="4" t="n">
         <v>329787.5065146304</v>
       </c>
-      <c r="I242" s="2" t="inlineStr">
-        <is>
-          <t>2021-06-02</t>
-        </is>
-      </c>
-      <c r="J242" s="4" t="n">
-        <v>12072.43523587687</v>
-      </c>
     </row>
     <row r="243" ht="19" customHeight="1">
       <c r="A243" s="5" t="inlineStr">
@@ -9721,14 +7781,6 @@
       <c r="H243" s="7" t="n">
         <v>329729.007083495</v>
       </c>
-      <c r="I243" s="5" t="inlineStr">
-        <is>
-          <t>2021-06-06</t>
-        </is>
-      </c>
-      <c r="J243" s="7" t="n">
-        <v>12389.56373097897</v>
-      </c>
     </row>
     <row r="244" ht="19" customHeight="1">
       <c r="A244" s="2" t="inlineStr">
@@ -9759,14 +7811,6 @@
       <c r="H244" s="4" t="n">
         <v>333525.3122724356</v>
       </c>
-      <c r="I244" s="2" t="inlineStr">
-        <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="J244" s="4" t="n">
-        <v>2650.947905659267</v>
-      </c>
     </row>
     <row r="245" ht="19" customHeight="1">
       <c r="A245" s="5" t="inlineStr">
@@ -9797,14 +7841,6 @@
       <c r="H245" s="7" t="n">
         <v>344794.1500595587</v>
       </c>
-      <c r="I245" s="5" t="inlineStr">
-        <is>
-          <t>2021-07-01</t>
-        </is>
-      </c>
-      <c r="J245" s="7" t="n">
-        <v>3941.01430806488</v>
-      </c>
     </row>
     <row r="246" ht="19" customHeight="1">
       <c r="A246" s="2" t="inlineStr">
@@ -9835,14 +7871,6 @@
       <c r="H246" s="4" t="n">
         <v>348704.3751933418</v>
       </c>
-      <c r="I246" s="2" t="inlineStr">
-        <is>
-          <t>2021-07-18</t>
-        </is>
-      </c>
-      <c r="J246" s="4" t="n">
-        <v>4218.116876600692</v>
-      </c>
     </row>
     <row r="247" ht="19" customHeight="1">
       <c r="A247" s="5" t="inlineStr">
@@ -9873,14 +7901,6 @@
       <c r="H247" s="7" t="n">
         <v>328260.3634702552</v>
       </c>
-      <c r="I247" s="5" t="inlineStr">
-        <is>
-          <t>2021-07-18</t>
-        </is>
-      </c>
-      <c r="J247" s="7" t="n">
-        <v>1277.750732692911</v>
-      </c>
     </row>
     <row r="248" ht="19" customHeight="1">
       <c r="A248" s="2" t="inlineStr">
@@ -9911,14 +7931,6 @@
       <c r="H248" s="4" t="n">
         <v>352355.3554796725</v>
       </c>
-      <c r="I248" s="2" t="inlineStr">
-        <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="J248" s="4" t="n">
-        <v>5224.922875614142</v>
-      </c>
     </row>
     <row r="249" ht="19" customHeight="1">
       <c r="A249" s="5" t="inlineStr">
@@ -9949,14 +7961,6 @@
       <c r="H249" s="7" t="n">
         <v>334990.2611847616</v>
       </c>
-      <c r="I249" s="5" t="inlineStr">
-        <is>
-          <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="J249" s="7" t="n">
-        <v>4341.27357372772</v>
-      </c>
     </row>
     <row r="250" ht="19" customHeight="1">
       <c r="A250" s="2" t="inlineStr">
@@ -9987,14 +7991,6 @@
       <c r="H250" s="4" t="n">
         <v>315777.8164329453</v>
       </c>
-      <c r="I250" s="2" t="inlineStr">
-        <is>
-          <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="J250" s="4" t="n">
-        <v>1477.88036552433</v>
-      </c>
     </row>
     <row r="251" ht="19" customHeight="1">
       <c r="A251" s="5" t="inlineStr">
@@ -10025,14 +8021,6 @@
       <c r="H251" s="7" t="n">
         <v>350034.7754140565</v>
       </c>
-      <c r="I251" s="5" t="inlineStr">
-        <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="J251" s="7" t="n">
-        <v>1164.138679593228</v>
-      </c>
     </row>
     <row r="252" ht="19" customHeight="1">
       <c r="A252" s="2" t="inlineStr">
@@ -10063,14 +8051,6 @@
       <c r="H252" s="4" t="n">
         <v>355333.5923079469</v>
       </c>
-      <c r="I252" s="2" t="inlineStr">
-        <is>
-          <t>2021-11-16</t>
-        </is>
-      </c>
-      <c r="J252" s="4" t="n">
-        <v>16318.26236933115</v>
-      </c>
     </row>
     <row r="253" ht="19" customHeight="1">
       <c r="A253" s="5" t="inlineStr">
@@ -10101,14 +8081,6 @@
       <c r="H253" s="7" t="n">
         <v>345034.6135106992</v>
       </c>
-      <c r="I253" s="5" t="inlineStr">
-        <is>
-          <t>2021-11-16</t>
-        </is>
-      </c>
-      <c r="J253" s="7" t="n">
-        <v>10298.97879724768</v>
-      </c>
     </row>
     <row r="254" ht="19" customHeight="1">
       <c r="A254" s="2" t="inlineStr">
@@ -10139,14 +8111,6 @@
       <c r="H254" s="4" t="n">
         <v>324883.0989432893</v>
       </c>
-      <c r="I254" s="2" t="inlineStr">
-        <is>
-          <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="J254" s="4" t="n">
-        <v>2878.787795344268</v>
-      </c>
     </row>
     <row r="255" ht="19" customHeight="1">
       <c r="A255" s="5" t="inlineStr">
@@ -10177,14 +8141,6 @@
       <c r="H255" s="7" t="n">
         <v>357962.9877916089</v>
       </c>
-      <c r="I255" s="5" t="inlineStr">
-        <is>
-          <t>2021-12-22</t>
-        </is>
-      </c>
-      <c r="J255" s="7" t="n">
-        <v>14009.07429819938</v>
-      </c>
     </row>
     <row r="256" ht="19" customHeight="1">
       <c r="A256" s="2" t="inlineStr">
@@ -10215,14 +8171,6 @@
       <c r="H256" s="4" t="n">
         <v>339982.1100110629</v>
       </c>
-      <c r="I256" s="2" t="inlineStr">
-        <is>
-          <t>2021-12-22</t>
-        </is>
-      </c>
-      <c r="J256" s="4" t="n">
-        <v>4495.219445136504</v>
-      </c>
     </row>
     <row r="257" ht="19" customHeight="1">
       <c r="A257" s="5" t="inlineStr">
@@ -10253,14 +8201,6 @@
       <c r="H257" s="7" t="n">
         <v>335731.4085286077</v>
       </c>
-      <c r="I257" s="5" t="inlineStr">
-        <is>
-          <t>2022-01-04</t>
-        </is>
-      </c>
-      <c r="J257" s="7" t="n">
-        <v>1135.59451908983</v>
-      </c>
     </row>
     <row r="258" ht="19" customHeight="1">
       <c r="A258" s="2" t="inlineStr">
@@ -10291,14 +8231,6 @@
       <c r="H258" s="4" t="n">
         <v>356269.1221880027</v>
       </c>
-      <c r="I258" s="2" t="inlineStr">
-        <is>
-          <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="J258" s="4" t="n">
-        <v>1771.678816513973</v>
-      </c>
     </row>
     <row r="259" ht="19" customHeight="1">
       <c r="A259" s="5" t="inlineStr">
@@ -10329,14 +8261,6 @@
       <c r="H259" s="7" t="n">
         <v>355732.4583134859</v>
       </c>
-      <c r="I259" s="5" t="inlineStr">
-        <is>
-          <t>2022-03-13</t>
-        </is>
-      </c>
-      <c r="J259" s="7" t="n">
-        <v>1341.659686292135</v>
-      </c>
     </row>
     <row r="260" ht="19" customHeight="1">
       <c r="A260" s="2" t="inlineStr">
@@ -10367,14 +8291,6 @@
       <c r="H260" s="4" t="n">
         <v>333134.7810126762</v>
       </c>
-      <c r="I260" s="2" t="inlineStr">
-        <is>
-          <t>2022-03-13</t>
-        </is>
-      </c>
-      <c r="J260" s="4" t="n">
-        <v>2824.70966260121</v>
-      </c>
     </row>
     <row r="261" ht="19" customHeight="1">
       <c r="A261" s="5" t="inlineStr">
@@ -10405,14 +8321,6 @@
       <c r="H261" s="7" t="n">
         <v>310904.5120567281</v>
       </c>
-      <c r="I261" s="5" t="inlineStr">
-        <is>
-          <t>2022-03-13</t>
-        </is>
-      </c>
-      <c r="J261" s="7" t="n">
-        <v>1235.014941997119</v>
-      </c>
     </row>
     <row r="262" ht="19" customHeight="1">
       <c r="A262" s="2" t="inlineStr">
@@ -10443,14 +8351,6 @@
       <c r="H262" s="4" t="n">
         <v>359558.5965265477</v>
       </c>
-      <c r="I262" s="2" t="inlineStr">
-        <is>
-          <t>2022-04-24</t>
-        </is>
-      </c>
-      <c r="J262" s="4" t="n">
-        <v>1558.389327923941</v>
-      </c>
     </row>
     <row r="263" ht="19" customHeight="1">
       <c r="A263" s="5" t="inlineStr">
@@ -10481,14 +8381,6 @@
       <c r="H263" s="7" t="n">
         <v>337315.2549890408</v>
       </c>
-      <c r="I263" s="5" t="inlineStr">
-        <is>
-          <t>2022-04-24</t>
-        </is>
-      </c>
-      <c r="J263" s="7" t="n">
-        <v>1011.060978977586</v>
-      </c>
     </row>
     <row r="264" ht="19" customHeight="1">
       <c r="A264" s="2" t="inlineStr">
@@ -10519,14 +8411,6 @@
       <c r="H264" s="4" t="n">
         <v>361168.5881500983</v>
       </c>
-      <c r="I264" s="2" t="inlineStr">
-        <is>
-          <t>2022-04-27</t>
-        </is>
-      </c>
-      <c r="J264" s="4" t="n">
-        <v>1214.374023746471</v>
-      </c>
     </row>
     <row r="265" ht="19" customHeight="1">
       <c r="A265" s="5" t="inlineStr">
@@ -10557,14 +8441,6 @@
       <c r="H265" s="7" t="n">
         <v>361569.0219641608</v>
       </c>
-      <c r="I265" s="5" t="inlineStr">
-        <is>
-          <t>2022-05-11</t>
-        </is>
-      </c>
-      <c r="J265" s="7" t="n">
-        <v>3699.19656582034</v>
-      </c>
     </row>
     <row r="266" ht="19" customHeight="1">
       <c r="A266" s="2" t="inlineStr">
@@ -10595,14 +8471,6 @@
       <c r="H266" s="4" t="n">
         <v>339394.4834874895</v>
       </c>
-      <c r="I266" s="2" t="inlineStr">
-        <is>
-          <t>2022-05-11</t>
-        </is>
-      </c>
-      <c r="J266" s="4" t="n">
-        <v>1231.918804259522</v>
-      </c>
     </row>
     <row r="267" ht="19" customHeight="1">
       <c r="A267" s="5" t="inlineStr">
@@ -10633,14 +8501,6 @@
       <c r="H267" s="7" t="n">
         <v>316902.7629003664</v>
       </c>
-      <c r="I267" s="5" t="inlineStr">
-        <is>
-          <t>2022-05-11</t>
-        </is>
-      </c>
-      <c r="J267" s="7" t="n">
-        <v>1606.551470508787</v>
-      </c>
     </row>
     <row r="268" ht="19" customHeight="1">
       <c r="A268" s="2" t="inlineStr">
@@ -10671,14 +8531,6 @@
       <c r="H268" s="4" t="n">
         <v>371242.7323176313</v>
       </c>
-      <c r="I268" s="2" t="inlineStr">
-        <is>
-          <t>2022-06-26</t>
-        </is>
-      </c>
-      <c r="J268" s="4" t="n">
-        <v>7744.128512339037</v>
-      </c>
     </row>
     <row r="269" ht="19" customHeight="1">
       <c r="A269" s="5" t="inlineStr">
@@ -10709,14 +8561,6 @@
       <c r="H269" s="7" t="n">
         <v>350123.6327941764</v>
       </c>
-      <c r="I269" s="5" t="inlineStr">
-        <is>
-          <t>2022-06-26</t>
-        </is>
-      </c>
-      <c r="J269" s="7" t="n">
-        <v>2111.909952345491</v>
-      </c>
     </row>
     <row r="270" ht="19" customHeight="1">
       <c r="A270" s="2" t="inlineStr">
@@ -10747,14 +8591,6 @@
       <c r="H270" s="4" t="n">
         <v>327418.6227184634</v>
       </c>
-      <c r="I270" s="2" t="inlineStr">
-        <is>
-          <t>2022-06-26</t>
-        </is>
-      </c>
-      <c r="J270" s="4" t="n">
-        <v>688.0306083549409</v>
-      </c>
     </row>
     <row r="271" ht="19" customHeight="1">
       <c r="A271" s="5" t="inlineStr">
@@ -10785,14 +8621,6 @@
       <c r="H271" s="7" t="n">
         <v>304816.8172340036</v>
       </c>
-      <c r="I271" s="5" t="inlineStr">
-        <is>
-          <t>2022-06-26</t>
-        </is>
-      </c>
-      <c r="J271" s="7" t="n">
-        <v>1506.787032297321</v>
-      </c>
     </row>
     <row r="272" ht="19" customHeight="1">
       <c r="A272" s="2" t="inlineStr">
@@ -10823,14 +8651,6 @@
       <c r="H272" s="4" t="n">
         <v>282565.9073598048</v>
       </c>
-      <c r="I272" s="2" t="inlineStr">
-        <is>
-          <t>2022-06-26</t>
-        </is>
-      </c>
-      <c r="J272" s="4" t="n">
-        <v>1059.567136866609</v>
-      </c>
     </row>
     <row r="273" ht="19" customHeight="1">
       <c r="A273" s="5" t="inlineStr">
@@ -10861,14 +8681,6 @@
       <c r="H273" s="7" t="n">
         <v>353181.9288483142</v>
       </c>
-      <c r="I273" s="5" t="inlineStr">
-        <is>
-          <t>2022-06-30</t>
-        </is>
-      </c>
-      <c r="J273" s="7" t="n">
-        <v>774.0344343993086</v>
-      </c>
     </row>
     <row r="274" ht="19" customHeight="1">
       <c r="A274" s="2" t="inlineStr">
@@ -10899,14 +8711,6 @@
       <c r="H274" s="4" t="n">
         <v>371415.4280003285</v>
       </c>
-      <c r="I274" s="2" t="inlineStr">
-        <is>
-          <t>2022-07-13</t>
-        </is>
-      </c>
-      <c r="J274" s="4" t="n">
-        <v>928.8413212791702</v>
-      </c>
     </row>
     <row r="275" ht="19" customHeight="1">
       <c r="A275" s="5" t="inlineStr">
@@ -10937,14 +8741,6 @@
       <c r="H275" s="7" t="n">
         <v>349536.0546546414</v>
       </c>
-      <c r="I275" s="5" t="inlineStr">
-        <is>
-          <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="J275" s="7" t="n">
-        <v>1093.968667284356</v>
-      </c>
     </row>
     <row r="276" ht="19" customHeight="1">
       <c r="A276" s="2" t="inlineStr">
@@ -10975,14 +8771,6 @@
       <c r="H276" s="4" t="n">
         <v>350829.5521983487</v>
       </c>
-      <c r="I276" s="2" t="inlineStr">
-        <is>
-          <t>2022-07-15</t>
-        </is>
-      </c>
-      <c r="J276" s="4" t="n">
-        <v>894.4397908614231</v>
-      </c>
     </row>
     <row r="277" ht="19" customHeight="1">
       <c r="A277" s="5" t="inlineStr">
@@ -11013,14 +8801,6 @@
       <c r="H277" s="7" t="n">
         <v>328138.3027348027</v>
       </c>
-      <c r="I277" s="5" t="inlineStr">
-        <is>
-          <t>2022-07-17</t>
-        </is>
-      </c>
-      <c r="J277" s="7" t="n">
-        <v>667.3896901042926</v>
-      </c>
     </row>
     <row r="278" ht="19" customHeight="1">
       <c r="A278" s="2" t="inlineStr">
@@ -11051,14 +8831,6 @@
       <c r="H278" s="4" t="n">
         <v>305777.3079632671</v>
       </c>
-      <c r="I278" s="2" t="inlineStr">
-        <is>
-          <t>2022-07-18</t>
-        </is>
-      </c>
-      <c r="J278" s="4" t="n">
-        <v>1118.049738576779</v>
-      </c>
     </row>
     <row r="279" ht="19" customHeight="1">
       <c r="A279" s="5" t="inlineStr">
@@ -11089,14 +8861,6 @@
       <c r="H279" s="7" t="n">
         <v>353602.315550019</v>
       </c>
-      <c r="I279" s="5" t="inlineStr">
-        <is>
-          <t>2022-07-24</t>
-        </is>
-      </c>
-      <c r="J279" s="7" t="n">
-        <v>1995.288764229329</v>
-      </c>
     </row>
     <row r="280" ht="19" customHeight="1">
       <c r="A280" s="2" t="inlineStr">
@@ -11127,14 +8891,6 @@
       <c r="H280" s="4" t="n">
         <v>381839.0917169058</v>
       </c>
-      <c r="I280" s="2" t="inlineStr">
-        <is>
-          <t>2022-08-21</t>
-        </is>
-      </c>
-      <c r="J280" s="4" t="n">
-        <v>1111.16943249323</v>
-      </c>
     </row>
     <row r="281" ht="19" customHeight="1">
       <c r="A281" s="5" t="inlineStr">
@@ -11165,14 +8921,6 @@
       <c r="H281" s="7" t="n">
         <v>382514.7377743103</v>
       </c>
-      <c r="I281" s="5" t="inlineStr">
-        <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="J281" s="7" t="n">
-        <v>3614.224785688504</v>
-      </c>
     </row>
     <row r="282" ht="19" customHeight="1">
       <c r="A282" s="2" t="inlineStr">
@@ -11203,14 +8951,6 @@
       <c r="H282" s="4" t="n">
         <v>359765.0057090542</v>
       </c>
-      <c r="I282" s="2" t="inlineStr">
-        <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="J282" s="4" t="n">
-        <v>669.1097666251801</v>
-      </c>
     </row>
     <row r="283" ht="19" customHeight="1">
       <c r="A283" s="5" t="inlineStr">
@@ -11241,14 +8981,6 @@
       <c r="H283" s="7" t="n">
         <v>337307.686652349</v>
       </c>
-      <c r="I283" s="5" t="inlineStr">
-        <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="J283" s="7" t="n">
-        <v>1321.018768041487</v>
-      </c>
     </row>
     <row r="284" ht="19" customHeight="1">
       <c r="A284" s="2" t="inlineStr">
@@ -11279,14 +9011,6 @@
       <c r="H284" s="4" t="n">
         <v>315978.7377933458</v>
       </c>
-      <c r="I284" s="2" t="inlineStr">
-        <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="J284" s="4" t="n">
-        <v>2666.118607375396</v>
-      </c>
     </row>
     <row r="285" ht="19" customHeight="1">
       <c r="A285" s="5" t="inlineStr">
@@ -11317,14 +9041,6 @@
       <c r="H285" s="7" t="n">
         <v>383819.9318383597</v>
       </c>
-      <c r="I285" s="5" t="inlineStr">
-        <is>
-          <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="J285" s="7" t="n">
-        <v>1068.511534775223</v>
-      </c>
     </row>
     <row r="286" ht="19" customHeight="1">
       <c r="A286" s="2" t="inlineStr">
@@ -11355,14 +9071,6 @@
       <c r="H286" s="4" t="n">
         <v>361219.8464304208</v>
       </c>
-      <c r="I286" s="2" t="inlineStr">
-        <is>
-          <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="J286" s="4" t="n">
-        <v>645.716725941112</v>
-      </c>
     </row>
     <row r="287" ht="19" customHeight="1">
       <c r="A287" s="5" t="inlineStr">
@@ -11393,14 +9101,6 @@
       <c r="H287" s="7" t="n">
         <v>339127.1835961436</v>
       </c>
-      <c r="I287" s="5" t="inlineStr">
-        <is>
-          <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="J287" s="7" t="n">
-        <v>849.717801318352</v>
-      </c>
     </row>
     <row r="288" ht="19" customHeight="1">
       <c r="A288" s="2" t="inlineStr">
@@ -11431,14 +9131,6 @@
       <c r="H288" s="4" t="n">
         <v>318486.2653454954</v>
       </c>
-      <c r="I288" s="2" t="inlineStr">
-        <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="J288" s="4" t="n">
-        <v>3440.153041774704</v>
-      </c>
     </row>
     <row r="289" ht="19" customHeight="1">
       <c r="A289" s="5" t="inlineStr">
@@ -11469,14 +9161,6 @@
       <c r="H289" s="7" t="n">
         <v>296259.436542589</v>
       </c>
-      <c r="I289" s="5" t="inlineStr">
-        <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="J289" s="7" t="n">
-        <v>3175.261257558052</v>
-      </c>
     </row>
     <row r="290" ht="19" customHeight="1">
       <c r="A290" s="2" t="inlineStr">
@@ -11507,14 +9191,6 @@
       <c r="H290" s="4" t="n">
         <v>273657.6310581292</v>
       </c>
-      <c r="I290" s="2" t="inlineStr">
-        <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="J290" s="4" t="n">
-        <v>1255.655860247767</v>
-      </c>
     </row>
     <row r="291" ht="19" customHeight="1">
       <c r="A291" s="5" t="inlineStr">
@@ -11545,14 +9221,6 @@
       <c r="H291" s="7" t="n">
         <v>251984.6668949485</v>
       </c>
-      <c r="I291" s="5" t="inlineStr">
-        <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="J291" s="7" t="n">
-        <v>1444.864277545376</v>
-      </c>
     </row>
     <row r="292" ht="19" customHeight="1">
       <c r="A292" s="2" t="inlineStr">
@@ -11583,14 +9251,6 @@
       <c r="H292" s="4" t="n">
         <v>229348.459880071</v>
       </c>
-      <c r="I292" s="2" t="inlineStr">
-        <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="J292" s="4" t="n">
-        <v>808.4359648170556</v>
-      </c>
     </row>
     <row r="293" ht="19" customHeight="1">
       <c r="A293" s="5" t="inlineStr">
@@ -11621,14 +9281,6 @@
       <c r="H293" s="7" t="n">
         <v>206801.6968442796</v>
       </c>
-      <c r="I293" s="5" t="inlineStr">
-        <is>
-          <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="J293" s="7" t="n">
-        <v>777.4745874410833</v>
-      </c>
     </row>
     <row r="294" ht="19" customHeight="1">
       <c r="A294" s="2" t="inlineStr">
@@ -11659,14 +9311,6 @@
       <c r="H294" s="4" t="n">
         <v>388418.7284246042</v>
       </c>
-      <c r="I294" s="2" t="inlineStr">
-        <is>
-          <t>2022-11-27</t>
-        </is>
-      </c>
-      <c r="J294" s="4" t="n">
-        <v>1451.744583628925</v>
-      </c>
     </row>
     <row r="295" ht="19" customHeight="1">
       <c r="A295" s="5" t="inlineStr">
@@ -11697,14 +9341,6 @@
       <c r="H295" s="7" t="n">
         <v>388972.5930643299</v>
       </c>
-      <c r="I295" s="5" t="inlineStr">
-        <is>
-          <t>2022-12-04</t>
-        </is>
-      </c>
-      <c r="J295" s="7" t="n">
-        <v>1644.393153968309</v>
-      </c>
     </row>
     <row r="296" ht="19" customHeight="1">
       <c r="A296" s="2" t="inlineStr">
@@ -11735,14 +9371,6 @@
       <c r="H296" s="4" t="n">
         <v>390854.3567781807</v>
       </c>
-      <c r="I296" s="2" t="inlineStr">
-        <is>
-          <t>2022-12-12</t>
-        </is>
-      </c>
-      <c r="J296" s="4" t="n">
-        <v>2989.492993302218</v>
-      </c>
     </row>
     <row r="297" ht="19" customHeight="1">
       <c r="A297" s="5" t="inlineStr">
@@ -11773,14 +9401,6 @@
       <c r="H297" s="7" t="n">
         <v>369594.210980013</v>
       </c>
-      <c r="I297" s="5" t="inlineStr">
-        <is>
-          <t>2022-12-26</t>
-        </is>
-      </c>
-      <c r="J297" s="7" t="n">
-        <v>1771.678816513973</v>
-      </c>
     </row>
     <row r="298" ht="19" customHeight="1">
       <c r="A298" s="2" t="inlineStr">
@@ -11811,14 +9431,6 @@
       <c r="H298" s="4" t="n">
         <v>346806.6372312974</v>
       </c>
-      <c r="I298" s="2" t="inlineStr">
-        <is>
-          <t>2022-12-26</t>
-        </is>
-      </c>
-      <c r="J298" s="4" t="n">
-        <v>632.9881596865456</v>
-      </c>
     </row>
     <row r="299" ht="19" customHeight="1">
       <c r="A299" s="5" t="inlineStr">
@@ -11849,14 +9461,6 @@
       <c r="H299" s="7" t="n">
         <v>324583.2485814328</v>
       </c>
-      <c r="I299" s="5" t="inlineStr">
-        <is>
-          <t>2022-12-26</t>
-        </is>
-      </c>
-      <c r="J299" s="7" t="n">
-        <v>1307.258155874388</v>
-      </c>
     </row>
     <row r="300" ht="19" customHeight="1">
       <c r="A300" s="2" t="inlineStr">
@@ -11887,14 +9491,6 @@
       <c r="H300" s="4" t="n">
         <v>302745.5010875511</v>
       </c>
-      <c r="I300" s="2" t="inlineStr">
-        <is>
-          <t>2022-12-26</t>
-        </is>
-      </c>
-      <c r="J300" s="4" t="n">
-        <v>1149.355131256929</v>
-      </c>
     </row>
     <row r="301" ht="19" customHeight="1">
       <c r="A301" s="5" t="inlineStr">
@@ -11925,14 +9521,6 @@
       <c r="H301" s="7" t="n">
         <v>414335.1722424757</v>
       </c>
-      <c r="I301" s="5" t="inlineStr">
-        <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="J301" s="7" t="n">
-        <v>1584.017946168807</v>
-      </c>
     </row>
     <row r="302" ht="19" customHeight="1">
       <c r="A302" s="2" t="inlineStr">
@@ -11963,14 +9551,6 @@
       <c r="H302" s="4" t="n">
         <v>416437.7148693972</v>
       </c>
-      <c r="I302" s="2" t="inlineStr">
-        <is>
-          <t>2023-03-19</t>
-        </is>
-      </c>
-      <c r="J302" s="4" t="n">
-        <v>7745.198159500476</v>
-      </c>
     </row>
     <row r="303" ht="19" customHeight="1">
       <c r="A303" s="5" t="inlineStr">
@@ -12001,14 +9581,6 @@
       <c r="H303" s="7" t="n">
         <v>391876.0194653237</v>
       </c>
-      <c r="I303" s="5" t="inlineStr">
-        <is>
-          <t>2023-03-20</t>
-        </is>
-      </c>
-      <c r="J303" s="7" t="n">
-        <v>1364.538633559637</v>
-      </c>
     </row>
     <row r="304" ht="19" customHeight="1">
       <c r="A304" s="2" t="inlineStr">
@@ -12039,14 +9611,6 @@
       <c r="H304" s="4" t="n">
         <v>391437.8295942651</v>
       </c>
-      <c r="I304" s="2" t="inlineStr">
-        <is>
-          <t>2023-03-23</t>
-        </is>
-      </c>
-      <c r="J304" s="4" t="n">
-        <v>849.4733465258587</v>
-      </c>
     </row>
     <row r="305" ht="19" customHeight="1">
       <c r="A305" s="5" t="inlineStr">
@@ -12077,14 +9641,6 @@
       <c r="H305" s="7" t="n">
         <v>416852.8421156632</v>
       </c>
-      <c r="I305" s="5" t="inlineStr">
-        <is>
-          <t>2023-04-10</t>
-        </is>
-      </c>
-      <c r="J305" s="7" t="n">
-        <v>849.4733465258587</v>
-      </c>
     </row>
     <row r="306" ht="19" customHeight="1">
       <c r="A306" s="2" t="inlineStr">
@@ -12115,14 +9671,6 @@
       <c r="H306" s="4" t="n">
         <v>391230.2659711321</v>
       </c>
-      <c r="I306" s="2" t="inlineStr">
-        <is>
-          <t>2023-04-12</t>
-        </is>
-      </c>
-      <c r="J306" s="4" t="n">
-        <v>2329.325104048282</v>
-      </c>
     </row>
     <row r="307" ht="19" customHeight="1">
       <c r="A307" s="5" t="inlineStr">
@@ -12153,14 +9701,6 @@
       <c r="H307" s="7" t="n">
         <v>366630.132859071</v>
       </c>
-      <c r="I307" s="5" t="inlineStr">
-        <is>
-          <t>2023-04-12</t>
-        </is>
-      </c>
-      <c r="J307" s="7" t="n">
-        <v>12300.06655603053</v>
-      </c>
     </row>
     <row r="308" ht="19" customHeight="1">
       <c r="A308" s="2" t="inlineStr">
@@ -12191,14 +9731,6 @@
       <c r="H308" s="4" t="n">
         <v>343163.912132644</v>
       </c>
-      <c r="I308" s="2" t="inlineStr">
-        <is>
-          <t>2023-04-12</t>
-        </is>
-      </c>
-      <c r="J308" s="4" t="n">
-        <v>7822.073575475668</v>
-      </c>
     </row>
     <row r="309" ht="19" customHeight="1">
       <c r="A309" s="5" t="inlineStr">
@@ -12229,14 +9761,6 @@
       <c r="H309" s="7" t="n">
         <v>318450.0034049397</v>
       </c>
-      <c r="I309" s="5" t="inlineStr">
-        <is>
-          <t>2023-04-12</t>
-        </is>
-      </c>
-      <c r="J309" s="7" t="n">
-        <v>1029.746196987681</v>
-      </c>
     </row>
     <row r="310" ht="19" customHeight="1">
       <c r="A310" s="2" t="inlineStr">
@@ -12267,14 +9791,6 @@
       <c r="H310" s="4" t="n">
         <v>294042.0588328165</v>
       </c>
-      <c r="I310" s="2" t="inlineStr">
-        <is>
-          <t>2023-04-12</t>
-        </is>
-      </c>
-      <c r="J310" s="4" t="n">
-        <v>4881.588914424618</v>
-      </c>
     </row>
     <row r="311" ht="19" customHeight="1">
       <c r="A311" s="5" t="inlineStr">
@@ -12305,14 +9821,6 @@
       <c r="H311" s="7" t="n">
         <v>268580.9210618333</v>
       </c>
-      <c r="I311" s="5" t="inlineStr">
-        <is>
-          <t>2023-04-12</t>
-        </is>
-      </c>
-      <c r="J311" s="7" t="n">
-        <v>1414.507653943511</v>
-      </c>
     </row>
     <row r="312" ht="19" customHeight="1">
       <c r="A312" s="2" t="inlineStr">
@@ -12343,14 +9851,6 @@
       <c r="H312" s="4" t="n">
         <v>422592.7450494508</v>
       </c>
-      <c r="I312" s="2" t="inlineStr">
-        <is>
-          <t>2023-04-25</t>
-        </is>
-      </c>
-      <c r="J312" s="4" t="n">
-        <v>1484.848659560811</v>
-      </c>
     </row>
     <row r="313" ht="19" customHeight="1">
       <c r="A313" s="5" t="inlineStr">
@@ -12381,14 +9881,6 @@
       <c r="H313" s="7" t="n">
         <v>423296.1551056238</v>
       </c>
-      <c r="I313" s="5" t="inlineStr">
-        <is>
-          <t>2023-05-17</t>
-        </is>
-      </c>
-      <c r="J313" s="7" t="n">
-        <v>1057.036969658874</v>
-      </c>
     </row>
     <row r="314" ht="19" customHeight="1">
       <c r="A314" s="2" t="inlineStr">
@@ -12419,14 +9911,6 @@
       <c r="H314" s="4" t="n">
         <v>398542.2711616123</v>
       </c>
-      <c r="I314" s="2" t="inlineStr">
-        <is>
-          <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="J314" s="4" t="n">
-        <v>1076.255823652672</v>
-      </c>
     </row>
     <row r="315" ht="19" customHeight="1">
       <c r="A315" s="5" t="inlineStr">
@@ -12457,14 +9941,6 @@
       <c r="H315" s="7" t="n">
         <v>372927.3825586787</v>
       </c>
-      <c r="I315" s="5" t="inlineStr">
-        <is>
-          <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="J315" s="7" t="n">
-        <v>640.3722150733396</v>
-      </c>
     </row>
     <row r="316" ht="19" customHeight="1">
       <c r="A316" s="2" t="inlineStr">
@@ -12495,14 +9971,6 @@
       <c r="H316" s="4" t="n">
         <v>347904.4346587542</v>
       </c>
-      <c r="I316" s="2" t="inlineStr">
-        <is>
-          <t>2023-05-18</t>
-        </is>
-      </c>
-      <c r="J316" s="4" t="n">
-        <v>807.1918677395038</v>
-      </c>
     </row>
     <row r="317" ht="19" customHeight="1">
       <c r="A317" s="5" t="inlineStr">
@@ -12533,14 +10001,6 @@
       <c r="H317" s="7" t="n">
         <v>400386.1280137773</v>
       </c>
-      <c r="I317" s="5" t="inlineStr">
-        <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="J317" s="7" t="n">
-        <v>941.3394686162118</v>
-      </c>
     </row>
     <row r="318" ht="19" customHeight="1">
       <c r="A318" s="2" t="inlineStr">
@@ -12571,14 +10031,6 @@
       <c r="H318" s="4" t="n">
         <v>375524.6184874006</v>
       </c>
-      <c r="I318" s="2" t="inlineStr">
-        <is>
-          <t>2023-05-22</t>
-        </is>
-      </c>
-      <c r="J318" s="4" t="n">
-        <v>1775.822109026908</v>
-      </c>
     </row>
     <row r="319" ht="19" customHeight="1">
       <c r="A319" s="5" t="inlineStr">
@@ -12609,14 +10061,6 @@
       <c r="H319" s="7" t="n">
         <v>351539.488703141</v>
       </c>
-      <c r="I319" s="5" t="inlineStr">
-        <is>
-          <t>2023-05-23</t>
-        </is>
-      </c>
-      <c r="J319" s="7" t="n">
-        <v>2998.141223032443</v>
-      </c>
     </row>
     <row r="320" ht="19" customHeight="1">
       <c r="A320" s="2" t="inlineStr">
@@ -12647,14 +10091,6 @@
       <c r="H320" s="4" t="n">
         <v>429781.7495743708</v>
       </c>
-      <c r="I320" s="2" t="inlineStr">
-        <is>
-          <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="J320" s="4" t="n">
-        <v>1433.726507937309</v>
-      </c>
     </row>
     <row r="321" ht="19" customHeight="1">
       <c r="A321" s="5" t="inlineStr">
@@ -12685,14 +10121,6 @@
       <c r="H321" s="7" t="n">
         <v>404820.3020072263</v>
       </c>
-      <c r="I321" s="5" t="inlineStr">
-        <is>
-          <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="J321" s="7" t="n">
-        <v>1468.320445126145</v>
-      </c>
     </row>
     <row r="322" ht="19" customHeight="1">
       <c r="A322" s="2" t="inlineStr">
@@ -12723,14 +10151,6 @@
       <c r="H322" s="4" t="n">
         <v>381142.6738868675</v>
       </c>
-      <c r="I322" s="2" t="inlineStr">
-        <is>
-          <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="J322" s="4" t="n">
-        <v>2959.703515044847</v>
-      </c>
     </row>
     <row r="323" ht="19" customHeight="1">
       <c r="A323" s="5" t="inlineStr">
@@ -12761,14 +10181,6 @@
       <c r="H323" s="7" t="n">
         <v>430255.6865138578</v>
       </c>
-      <c r="I323" s="5" t="inlineStr">
-        <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="J323" s="7" t="n">
-        <v>654.59416702875</v>
-      </c>
     </row>
     <row r="324" ht="19" customHeight="1">
       <c r="A324" s="2" t="inlineStr">
@@ -12799,14 +10211,6 @@
       <c r="H324" s="4" t="n">
         <v>431941.5643861938</v>
       </c>
-      <c r="I324" s="2" t="inlineStr">
-        <is>
-          <t>2023-06-25</t>
-        </is>
-      </c>
-      <c r="J324" s="4" t="n">
-        <v>1245.381738798091</v>
-      </c>
     </row>
     <row r="325" ht="19" customHeight="1">
       <c r="A325" s="5" t="inlineStr">
@@ -12837,14 +10241,6 @@
       <c r="H325" s="7" t="n">
         <v>406453.9045966991</v>
       </c>
-      <c r="I325" s="5" t="inlineStr">
-        <is>
-          <t>2023-06-27</t>
-        </is>
-      </c>
-      <c r="J325" s="7" t="n">
-        <v>822.182573854666</v>
-      </c>
     </row>
     <row r="326" ht="19" customHeight="1">
       <c r="A326" s="2" t="inlineStr">
@@ -12875,14 +10271,6 @@
       <c r="H326" s="4" t="n">
         <v>381317.5654582111</v>
       </c>
-      <c r="I326" s="2" t="inlineStr">
-        <is>
-          <t>2023-06-27</t>
-        </is>
-      </c>
-      <c r="J326" s="4" t="n">
-        <v>866.7703151202767</v>
-      </c>
     </row>
     <row r="327" ht="19" customHeight="1">
       <c r="A327" s="5" t="inlineStr">
@@ -12913,14 +10301,6 @@
       <c r="H327" s="7" t="n">
         <v>434176.3327285926</v>
       </c>
-      <c r="I327" s="5" t="inlineStr">
-        <is>
-          <t>2023-07-16</t>
-        </is>
-      </c>
-      <c r="J327" s="7" t="n">
-        <v>891.3704482323377</v>
-      </c>
     </row>
     <row r="328" ht="19" customHeight="1">
       <c r="A328" s="2" t="inlineStr">
@@ -12951,14 +10331,6 @@
       <c r="H328" s="4" t="n">
         <v>409123.4034164377</v>
       </c>
-      <c r="I328" s="2" t="inlineStr">
-        <is>
-          <t>2023-07-16</t>
-        </is>
-      </c>
-      <c r="J328" s="4" t="n">
-        <v>736.8508621222041</v>
-      </c>
     </row>
     <row r="329" ht="19" customHeight="1">
       <c r="A329" s="5" t="inlineStr">
@@ -12989,14 +10361,6 @@
       <c r="H329" s="7" t="n">
         <v>438698.9134504131</v>
       </c>
-      <c r="I329" s="5" t="inlineStr">
-        <is>
-          <t>2023-08-13</t>
-        </is>
-      </c>
-      <c r="J329" s="7" t="n">
-        <v>1979.541961361164</v>
-      </c>
     </row>
     <row r="330" ht="19" customHeight="1">
       <c r="A330" s="2" t="inlineStr">
@@ -13027,14 +10391,6 @@
       <c r="H330" s="4" t="n">
         <v>440527.0108423032</v>
       </c>
-      <c r="I330" s="2" t="inlineStr">
-        <is>
-          <t>2023-08-23</t>
-        </is>
-      </c>
-      <c r="J330" s="4" t="n">
-        <v>5516.195473299818</v>
-      </c>
     </row>
     <row r="331" ht="19" customHeight="1">
       <c r="A331" s="5" t="inlineStr">
@@ -13065,14 +10421,6 @@
       <c r="H331" s="7" t="n">
         <v>438266.8736126326</v>
       </c>
-      <c r="I331" s="5" t="inlineStr">
-        <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="J331" s="7" t="n">
-        <v>1260.75682199313</v>
-      </c>
     </row>
     <row r="332" ht="19" customHeight="1">
       <c r="A332" s="2" t="inlineStr">
@@ -13103,14 +10451,6 @@
       <c r="H332" s="4" t="n">
         <v>438997.1900643969</v>
       </c>
-      <c r="I332" s="2" t="inlineStr">
-        <is>
-          <t>2023-09-13</t>
-        </is>
-      </c>
-      <c r="J332" s="4" t="n">
-        <v>2460.013311206107</v>
-      </c>
     </row>
     <row r="333" ht="19" customHeight="1">
       <c r="A333" s="5" t="inlineStr">
@@ -13141,14 +10481,6 @@
       <c r="H333" s="7" t="n">
         <v>415018.2103134154</v>
       </c>
-      <c r="I333" s="5" t="inlineStr">
-        <is>
-          <t>2023-09-13</t>
-        </is>
-      </c>
-      <c r="J333" s="7" t="n">
-        <v>2997.372468872691</v>
-      </c>
     </row>
     <row r="334" ht="19" customHeight="1">
       <c r="A334" s="2" t="inlineStr">
@@ -13179,14 +10511,6 @@
       <c r="H334" s="4" t="n">
         <v>449381.5212543257</v>
       </c>
-      <c r="I334" s="2" t="inlineStr">
-        <is>
-          <t>2023-09-18</t>
-        </is>
-      </c>
-      <c r="J334" s="4" t="n">
-        <v>14491.01591132347</v>
-      </c>
     </row>
     <row r="335" ht="19" customHeight="1">
       <c r="A335" s="5" t="inlineStr">
@@ -13217,14 +10541,6 @@
       <c r="H335" s="7" t="n">
         <v>425611.6426347967</v>
       </c>
-      <c r="I335" s="5" t="inlineStr">
-        <is>
-          <t>2023-09-18</t>
-        </is>
-      </c>
-      <c r="J335" s="7" t="n">
-        <v>2971.234827441126</v>
-      </c>
     </row>
     <row r="336" ht="19" customHeight="1">
       <c r="A336" s="2" t="inlineStr">
@@ -13255,14 +10571,6 @@
       <c r="H336" s="4" t="n">
         <v>438839.9798387276</v>
       </c>
-      <c r="I336" s="2" t="inlineStr">
-        <is>
-          <t>2023-09-26</t>
-        </is>
-      </c>
-      <c r="J336" s="4" t="n">
-        <v>724.5507955661736</v>
-      </c>
     </row>
     <row r="337" ht="19" customHeight="1">
       <c r="A337" s="5" t="inlineStr">
@@ -13293,14 +10601,6 @@
       <c r="H337" s="7" t="n">
         <v>439872.0322981945</v>
       </c>
-      <c r="I337" s="5" t="inlineStr">
-        <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="J337" s="7" t="n">
-        <v>2240.918375676813</v>
-      </c>
     </row>
     <row r="338" ht="19" customHeight="1">
       <c r="A338" s="2" t="inlineStr">
@@ -13331,14 +10631,6 @@
       <c r="H338" s="4" t="n">
         <v>442222.498141636</v>
       </c>
-      <c r="I338" s="2" t="inlineStr">
-        <is>
-          <t>2023-10-19</t>
-        </is>
-      </c>
-      <c r="J338" s="4" t="n">
-        <v>3267.20517894561</v>
-      </c>
     </row>
     <row r="339" ht="19" customHeight="1">
       <c r="A339" s="5" t="inlineStr">
@@ -13369,14 +10661,6 @@
       <c r="H339" s="7" t="n">
         <v>439982.7328971988</v>
       </c>
-      <c r="I339" s="5" t="inlineStr">
-        <is>
-          <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="J339" s="7" t="n">
-        <v>1507.142530193616</v>
-      </c>
     </row>
     <row r="340" ht="19" customHeight="1">
       <c r="A340" s="2" t="inlineStr">
@@ -13407,14 +10691,6 @@
       <c r="H340" s="4" t="n">
         <v>441101.2701996379</v>
       </c>
-      <c r="I340" s="2" t="inlineStr">
-        <is>
-          <t>2023-12-07</t>
-        </is>
-      </c>
-      <c r="J340" s="4" t="n">
-        <v>1397.210685349093</v>
-      </c>
     </row>
     <row r="341" ht="19" customHeight="1">
       <c r="A341" s="5" t="inlineStr">
@@ -13445,14 +10721,6 @@
       <c r="H341" s="7" t="n">
         <v>415809.6427208799</v>
       </c>
-      <c r="I341" s="5" t="inlineStr">
-        <is>
-          <t>2023-12-10</t>
-        </is>
-      </c>
-      <c r="J341" s="7" t="n">
-        <v>936.7269436577003</v>
-      </c>
     </row>
     <row r="342" ht="19" customHeight="1">
       <c r="A342" s="2" t="inlineStr">
@@ -13483,14 +10751,6 @@
       <c r="H342" s="4" t="n">
         <v>390521.4746358409</v>
       </c>
-      <c r="I342" s="2" t="inlineStr">
-        <is>
-          <t>2023-12-10</t>
-        </is>
-      </c>
-      <c r="J342" s="4" t="n">
-        <v>588.0969322102098</v>
-      </c>
     </row>
     <row r="343" ht="19" customHeight="1">
       <c r="A343" s="5" t="inlineStr">
@@ -13521,14 +10781,6 @@
       <c r="H343" s="7" t="n">
         <v>365139.9029203921</v>
       </c>
-      <c r="I343" s="5" t="inlineStr">
-        <is>
-          <t>2023-12-10</t>
-        </is>
-      </c>
-      <c r="J343" s="7" t="n">
-        <v>769.1385368317843</v>
-      </c>
     </row>
     <row r="344" ht="19" customHeight="1">
       <c r="A344" s="2" t="inlineStr">
@@ -13559,14 +10811,6 @@
       <c r="H344" s="4" t="n">
         <v>339847.8910645543</v>
       </c>
-      <c r="I344" s="2" t="inlineStr">
-        <is>
-          <t>2023-12-10</t>
-        </is>
-      </c>
-      <c r="J344" s="4" t="n">
-        <v>722.6289101667938</v>
-      </c>
     </row>
     <row r="345" ht="19" customHeight="1">
       <c r="A345" s="5" t="inlineStr">
@@ -13597,14 +10841,6 @@
       <c r="H345" s="7" t="n">
         <v>314543.5791421605</v>
       </c>
-      <c r="I345" s="5" t="inlineStr">
-        <is>
-          <t>2023-12-10</t>
-        </is>
-      </c>
-      <c r="J345" s="7" t="n">
-        <v>1054.346330099742</v>
-      </c>
     </row>
     <row r="346" ht="19" customHeight="1">
       <c r="A346" s="2" t="inlineStr">
@@ -13635,14 +10871,6 @@
       <c r="H346" s="4" t="n">
         <v>450041.8678521843</v>
       </c>
-      <c r="I346" s="2" t="inlineStr">
-        <is>
-          <t>2024-01-16</t>
-        </is>
-      </c>
-      <c r="J346" s="4" t="n">
-        <v>867.8946529285539</v>
-      </c>
     </row>
     <row r="347" ht="19" customHeight="1">
       <c r="A347" s="5" t="inlineStr">
@@ -13673,14 +10901,6 @@
       <c r="H347" s="7" t="n">
         <v>453367.3651856829</v>
       </c>
-      <c r="I347" s="5" t="inlineStr">
-        <is>
-          <t>2024-02-05</t>
-        </is>
-      </c>
-      <c r="J347" s="7" t="n">
-        <v>3737.962119048722</v>
-      </c>
     </row>
     <row r="348" ht="19" customHeight="1">
       <c r="A348" s="2" t="inlineStr">
@@ -13711,14 +10931,6 @@
       <c r="H348" s="4" t="n">
         <v>452328.8991578966</v>
       </c>
-      <c r="I348" s="2" t="inlineStr">
-        <is>
-          <t>2024-02-14</t>
-        </is>
-      </c>
-      <c r="J348" s="4" t="n">
-        <v>1276.062930295943</v>
-      </c>
     </row>
     <row r="349" ht="19" customHeight="1">
       <c r="A349" s="5" t="inlineStr">
@@ -13749,14 +10961,6 @@
       <c r="H349" s="7" t="n">
         <v>424809.764246969</v>
       </c>
-      <c r="I349" s="5" t="inlineStr">
-        <is>
-          <t>2024-02-14</t>
-        </is>
-      </c>
-      <c r="J349" s="7" t="n">
-        <v>1310.43499575846</v>
-      </c>
     </row>
     <row r="350" ht="19" customHeight="1">
       <c r="A350" s="2" t="inlineStr">
@@ -13787,14 +10991,6 @@
       <c r="H350" s="4" t="n">
         <v>453447.2802378833</v>
       </c>
-      <c r="I350" s="2" t="inlineStr">
-        <is>
-          <t>2024-02-27</t>
-        </is>
-      </c>
-      <c r="J350" s="4" t="n">
-        <v>1228.801340284982</v>
-      </c>
     </row>
     <row r="351" ht="19" customHeight="1">
       <c r="A351" s="5" t="inlineStr">
@@ -13825,14 +11021,6 @@
       <c r="H351" s="7" t="n">
         <v>454190.5761535102</v>
       </c>
-      <c r="I351" s="5" t="inlineStr">
-        <is>
-          <t>2024-03-04</t>
-        </is>
-      </c>
-      <c r="J351" s="7" t="n">
-        <v>979.6038656817341</v>
-      </c>
     </row>
     <row r="352" ht="19" customHeight="1">
       <c r="A352" s="2" t="inlineStr">
@@ -13863,14 +11051,6 @@
       <c r="H352" s="4" t="n">
         <v>427212.8012736172</v>
       </c>
-      <c r="I352" s="2" t="inlineStr">
-        <is>
-          <t>2024-03-04</t>
-        </is>
-      </c>
-      <c r="J352" s="4" t="n">
-        <v>8992.591626631007</v>
-      </c>
     </row>
     <row r="353" ht="19" customHeight="1">
       <c r="A353" s="5" t="inlineStr">
@@ -13901,14 +11081,6 @@
       <c r="H353" s="7" t="n">
         <v>399199.5679216658</v>
       </c>
-      <c r="I353" s="5" t="inlineStr">
-        <is>
-          <t>2024-03-04</t>
-        </is>
-      </c>
-      <c r="J353" s="7" t="n">
-        <v>700.3308337987836</v>
-      </c>
     </row>
     <row r="354" ht="19" customHeight="1">
       <c r="A354" s="2" t="inlineStr">
@@ -13939,14 +11111,6 @@
       <c r="H354" s="4" t="n">
         <v>373707.5255713901</v>
       </c>
-      <c r="I354" s="2" t="inlineStr">
-        <is>
-          <t>2024-03-04</t>
-        </is>
-      </c>
-      <c r="J354" s="4" t="n">
-        <v>3641.720335753675</v>
-      </c>
     </row>
     <row r="355" ht="19" customHeight="1">
       <c r="A355" s="5" t="inlineStr">
@@ -13977,14 +11141,6 @@
       <c r="H355" s="7" t="n">
         <v>346028.5605560617</v>
       </c>
-      <c r="I355" s="5" t="inlineStr">
-        <is>
-          <t>2024-03-04</t>
-        </is>
-      </c>
-      <c r="J355" s="7" t="n">
-        <v>1025.146852419569</v>
-      </c>
     </row>
     <row r="356" ht="19" customHeight="1">
       <c r="A356" s="2" t="inlineStr">
@@ -14015,14 +11171,6 @@
       <c r="H356" s="4" t="n">
         <v>317805.657604789</v>
       </c>
-      <c r="I356" s="2" t="inlineStr">
-        <is>
-          <t>2024-03-04</t>
-        </is>
-      </c>
-      <c r="J356" s="4" t="n">
-        <v>1227.082737011857</v>
-      </c>
     </row>
     <row r="357" ht="19" customHeight="1">
       <c r="A357" s="5" t="inlineStr">
@@ -14053,14 +11201,6 @@
       <c r="H357" s="7" t="n">
         <v>291579.7716568885</v>
       </c>
-      <c r="I357" s="5" t="inlineStr">
-        <is>
-          <t>2024-03-04</t>
-        </is>
-      </c>
-      <c r="J357" s="7" t="n">
-        <v>3278.235743487558</v>
-      </c>
     </row>
     <row r="358" ht="19" customHeight="1">
       <c r="A358" s="2" t="inlineStr">
@@ -14091,14 +11231,6 @@
       <c r="H358" s="4" t="n">
         <v>435921.8233601823</v>
       </c>
-      <c r="I358" s="2" t="inlineStr">
-        <is>
-          <t>2024-03-10</t>
-        </is>
-      </c>
-      <c r="J358" s="4" t="n">
-        <v>3596.17734901584</v>
-      </c>
     </row>
     <row r="359" ht="19" customHeight="1">
       <c r="A359" s="5" t="inlineStr">
@@ -14129,14 +11261,6 @@
       <c r="H359" s="7" t="n">
         <v>410142.7742632946</v>
       </c>
-      <c r="I359" s="5" t="inlineStr">
-        <is>
-          <t>2024-03-10</t>
-        </is>
-      </c>
-      <c r="J359" s="7" t="n">
-        <v>3222.381137110967</v>
-      </c>
     </row>
     <row r="360" ht="19" customHeight="1">
       <c r="A360" s="2" t="inlineStr">
@@ -14167,14 +11291,6 @@
       <c r="H360" s="4" t="n">
         <v>383590.3536935002</v>
       </c>
-      <c r="I360" s="2" t="inlineStr">
-        <is>
-          <t>2024-03-10</t>
-        </is>
-      </c>
-      <c r="J360" s="4" t="n">
-        <v>2212.701714149531</v>
-      </c>
     </row>
     <row r="361" ht="19" customHeight="1">
       <c r="A361" s="5" t="inlineStr">
@@ -14205,14 +11321,6 @@
       <c r="H361" s="7" t="n">
         <v>355706.0155870333</v>
       </c>
-      <c r="I361" s="5" t="inlineStr">
-        <is>
-          <t>2024-03-10</t>
-        </is>
-      </c>
-      <c r="J361" s="7" t="n">
-        <v>1267.469913930314</v>
-      </c>
     </row>
     <row r="362" ht="19" customHeight="1">
       <c r="A362" s="2" t="inlineStr">
@@ -14243,14 +11351,6 @@
       <c r="H362" s="4" t="n">
         <v>465163.4284016003</v>
       </c>
-      <c r="I362" s="2" t="inlineStr">
-        <is>
-          <t>2024-04-04</t>
-        </is>
-      </c>
-      <c r="J362" s="4" t="n">
-        <v>3346.979874412591</v>
-      </c>
     </row>
     <row r="363" ht="19" customHeight="1">
       <c r="A363" s="5" t="inlineStr">
@@ -14281,14 +11381,6 @@
       <c r="H363" s="7" t="n">
         <v>441704.4937234325</v>
       </c>
-      <c r="I363" s="5" t="inlineStr">
-        <is>
-          <t>2024-04-09</t>
-        </is>
-      </c>
-      <c r="J363" s="7" t="n">
-        <v>5864.733669541961</v>
-      </c>
     </row>
     <row r="364" ht="19" customHeight="1">
       <c r="A364" s="2" t="inlineStr">
@@ -14319,14 +11411,6 @@
       <c r="H364" s="4" t="n">
         <v>440707.7038250195</v>
       </c>
-      <c r="I364" s="2" t="inlineStr">
-        <is>
-          <t>2024-04-10</t>
-        </is>
-      </c>
-      <c r="J364" s="4" t="n">
-        <v>1615.487076738298</v>
-      </c>
     </row>
     <row r="365" ht="19" customHeight="1">
       <c r="A365" s="5" t="inlineStr">
@@ -14357,14 +11441,6 @@
       <c r="H365" s="7" t="n">
         <v>462955.8824972702</v>
       </c>
-      <c r="I365" s="5" t="inlineStr">
-        <is>
-          <t>2024-04-21</t>
-        </is>
-      </c>
-      <c r="J365" s="7" t="n">
-        <v>978.7445640451712</v>
-      </c>
     </row>
     <row r="366" ht="19" customHeight="1">
       <c r="A366" s="2" t="inlineStr">
@@ -14395,14 +11471,6 @@
       <c r="H366" s="4" t="n">
         <v>435097.3234399002</v>
       </c>
-      <c r="I366" s="2" t="inlineStr">
-        <is>
-          <t>2024-04-28</t>
-        </is>
-      </c>
-      <c r="J366" s="4" t="n">
-        <v>3482.319882171252</v>
-      </c>
     </row>
     <row r="367" ht="19" customHeight="1">
       <c r="A367" s="5" t="inlineStr">
@@ -14433,14 +11501,6 @@
       <c r="H367" s="7" t="n">
         <v>407298.056195453</v>
       </c>
-      <c r="I367" s="5" t="inlineStr">
-        <is>
-          <t>2024-04-28</t>
-        </is>
-      </c>
-      <c r="J367" s="7" t="n">
-        <v>1263.603056565781</v>
-      </c>
     </row>
     <row r="368" ht="19" customHeight="1">
       <c r="A368" s="2" t="inlineStr">
@@ -14471,14 +11531,6 @@
       <c r="H368" s="4" t="n">
         <v>379379.3460235235</v>
       </c>
-      <c r="I368" s="2" t="inlineStr">
-        <is>
-          <t>2024-04-29</t>
-        </is>
-      </c>
-      <c r="J368" s="4" t="n">
-        <v>1551.039453996079</v>
-      </c>
     </row>
     <row r="369" ht="19" customHeight="1">
       <c r="A369" s="5" t="inlineStr">
@@ -14509,14 +11561,6 @@
       <c r="H369" s="7" t="n">
         <v>379484.1808231842</v>
       </c>
-      <c r="I369" s="5" t="inlineStr">
-        <is>
-          <t>2024-04-30</t>
-        </is>
-      </c>
-      <c r="J369" s="7" t="n">
-        <v>1021.279995055036</v>
-      </c>
     </row>
     <row r="370" ht="19" customHeight="1">
       <c r="A370" s="2" t="inlineStr">
@@ -14547,14 +11591,6 @@
       <c r="H370" s="4" t="n">
         <v>439759.8941198906</v>
       </c>
-      <c r="I370" s="2" t="inlineStr">
-        <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="J370" s="4" t="n">
-        <v>3072.003350712456</v>
-      </c>
     </row>
     <row r="371" ht="19" customHeight="1">
       <c r="A371" s="5" t="inlineStr">
@@ -14585,14 +11621,6 @@
       <c r="H371" s="7" t="n">
         <v>411303.2611234728</v>
       </c>
-      <c r="I371" s="5" t="inlineStr">
-        <is>
-          <t>2024-05-12</t>
-        </is>
-      </c>
-      <c r="J371" s="7" t="n">
-        <v>836.9597940122886</v>
-      </c>
     </row>
     <row r="372" ht="19" customHeight="1">
       <c r="A372" s="2" t="inlineStr">
@@ -14623,14 +11651,6 @@
       <c r="H372" s="4" t="n">
         <v>413628.9610028304</v>
       </c>
-      <c r="I372" s="2" t="inlineStr">
-        <is>
-          <t>2024-05-13</t>
-        </is>
-      </c>
-      <c r="J372" s="4" t="n">
-        <v>2156.847107772941</v>
-      </c>
     </row>
     <row r="373" ht="19" customHeight="1">
       <c r="A373" s="5" t="inlineStr">
@@ -14661,14 +11681,6 @@
       <c r="H373" s="7" t="n">
         <v>385383.716209007</v>
       </c>
-      <c r="I373" s="5" t="inlineStr">
-        <is>
-          <t>2024-05-13</t>
-        </is>
-      </c>
-      <c r="J373" s="7" t="n">
-        <v>743.2959156269299</v>
-      </c>
     </row>
     <row r="374" ht="19" customHeight="1">
       <c r="A374" s="2" t="inlineStr">
@@ -14699,14 +11711,6 @@
       <c r="H374" s="4" t="n">
         <v>356841.1530489329</v>
       </c>
-      <c r="I374" s="2" t="inlineStr">
-        <is>
-          <t>2024-05-13</t>
-        </is>
-      </c>
-      <c r="J374" s="4" t="n">
-        <v>1189.273465003088</v>
-      </c>
     </row>
     <row r="375" ht="19" customHeight="1">
       <c r="A375" s="5" t="inlineStr">
@@ -14737,14 +11741,6 @@
       <c r="H375" s="7" t="n">
         <v>479680.0405988761</v>
       </c>
-      <c r="I375" s="5" t="inlineStr">
-        <is>
-          <t>2024-06-11</t>
-        </is>
-      </c>
-      <c r="J375" s="7" t="n">
-        <v>2625.166499699735</v>
-      </c>
     </row>
     <row r="376" ht="19" customHeight="1">
       <c r="A376" s="2" t="inlineStr">
@@ -14775,14 +11771,6 @@
       <c r="H376" s="4" t="n">
         <v>451644.4654043741</v>
       </c>
-      <c r="I376" s="2" t="inlineStr">
-        <is>
-          <t>2024-06-12</t>
-        </is>
-      </c>
-      <c r="J376" s="4" t="n">
-        <v>637.1721635114087</v>
-      </c>
     </row>
     <row r="377" ht="19" customHeight="1">
       <c r="A377" s="5" t="inlineStr">
@@ -14813,14 +11801,6 @@
       <c r="H377" s="7" t="n">
         <v>478831.9098835886</v>
       </c>
-      <c r="I377" s="5" t="inlineStr">
-        <is>
-          <t>2024-07-01</t>
-        </is>
-      </c>
-      <c r="J377" s="7" t="n">
-        <v>1308.716392485334</v>
-      </c>
     </row>
     <row r="378" ht="19" customHeight="1">
       <c r="A378" s="2" t="inlineStr">
@@ -14851,14 +11831,6 @@
       <c r="H378" s="4" t="n">
         <v>450565.1825488511</v>
       </c>
-      <c r="I378" s="2" t="inlineStr">
-        <is>
-          <t>2024-07-02</t>
-        </is>
-      </c>
-      <c r="J378" s="4" t="n">
-        <v>657.3657519706373</v>
-      </c>
     </row>
     <row r="379" ht="19" customHeight="1">
       <c r="A379" s="5" t="inlineStr">
@@ -14889,14 +11861,6 @@
       <c r="H379" s="7" t="n">
         <v>422234.0075913715</v>
       </c>
-      <c r="I379" s="5" t="inlineStr">
-        <is>
-          <t>2024-07-02</t>
-        </is>
-      </c>
-      <c r="J379" s="7" t="n">
-        <v>1888.744997165308</v>
-      </c>
     </row>
     <row r="380" ht="19" customHeight="1">
       <c r="A380" s="2" t="inlineStr">
@@ -14927,14 +11891,6 @@
       <c r="H380" s="4" t="n">
         <v>394284.3625605258</v>
       </c>
-      <c r="I380" s="2" t="inlineStr">
-        <is>
-          <t>2024-07-02</t>
-        </is>
-      </c>
-      <c r="J380" s="4" t="n">
-        <v>1552.758057269205</v>
-      </c>
     </row>
     <row r="381" ht="19" customHeight="1">
       <c r="A381" s="5" t="inlineStr">
@@ -14965,14 +11921,6 @@
       <c r="H381" s="7" t="n">
         <v>398135.3228447826</v>
       </c>
-      <c r="I381" s="5" t="inlineStr">
-        <is>
-          <t>2024-07-07</t>
-        </is>
-      </c>
-      <c r="J381" s="7" t="n">
-        <v>3596.17734901584</v>
-      </c>
     </row>
     <row r="382" ht="19" customHeight="1">
       <c r="A382" s="2" t="inlineStr">
@@ -15003,14 +11951,6 @@
       <c r="H382" s="4" t="n">
         <v>369872.892018228</v>
       </c>
-      <c r="I382" s="2" t="inlineStr">
-        <is>
-          <t>2024-07-07</t>
-        </is>
-      </c>
-      <c r="J382" s="4" t="n">
-        <v>614.4006701424911</v>
-      </c>
     </row>
     <row r="383" ht="19" customHeight="1">
       <c r="A383" s="5" t="inlineStr">
@@ -15041,14 +11981,6 @@
       <c r="H383" s="7" t="n">
         <v>504927.1819827314</v>
       </c>
-      <c r="I383" s="5" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="J383" s="7" t="n">
-        <v>2367.376008730857</v>
-      </c>
     </row>
     <row r="384" ht="19" customHeight="1">
       <c r="A384" s="2" t="inlineStr">
@@ -15079,14 +12011,6 @@
       <c r="H384" s="4" t="n">
         <v>477326.4134163303</v>
       </c>
-      <c r="I384" s="2" t="inlineStr">
-        <is>
-          <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="J384" s="4" t="n">
-        <v>3450.096070800143</v>
-      </c>
     </row>
     <row r="385" ht="19" customHeight="1">
       <c r="A385" s="5" t="inlineStr">
@@ -15117,14 +12041,6 @@
       <c r="H385" s="7" t="n">
         <v>449613.935637176</v>
       </c>
-      <c r="I385" s="5" t="inlineStr">
-        <is>
-          <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="J385" s="7" t="n">
-        <v>1847.498518610288</v>
-      </c>
     </row>
     <row r="386" ht="19" customHeight="1">
       <c r="A386" s="2" t="inlineStr">
@@ -15155,14 +12071,6 @@
       <c r="H386" s="4" t="n">
         <v>431310.8107783857</v>
       </c>
-      <c r="I386" s="2" t="inlineStr">
-        <is>
-          <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="J386" s="4" t="n">
-        <v>18303.1248587903</v>
-      </c>
     </row>
     <row r="387" ht="19" customHeight="1">
       <c r="A387" s="5" t="inlineStr">
@@ -15193,14 +12101,6 @@
       <c r="H387" s="7" t="n">
         <v>511244.3379639238</v>
       </c>
-      <c r="I387" s="5" t="inlineStr">
-        <is>
-          <t>2024-10-28</t>
-        </is>
-      </c>
-      <c r="J387" s="7" t="n">
-        <v>3892.636413630049</v>
-      </c>
     </row>
     <row r="388" ht="19" customHeight="1">
       <c r="A388" s="2" t="inlineStr">
@@ -15231,14 +12131,6 @@
       <c r="H388" s="4" t="n">
         <v>511084.9375103415</v>
       </c>
-      <c r="I388" s="2" t="inlineStr">
-        <is>
-          <t>2024-12-29</t>
-        </is>
-      </c>
-      <c r="J388" s="4" t="n">
-        <v>4085.979281856707</v>
-      </c>
     </row>
     <row r="389" ht="19" customHeight="1">
       <c r="A389" s="5" t="inlineStr">
@@ -15269,14 +12161,6 @@
       <c r="H389" s="7" t="n">
         <v>510732.9988835343</v>
       </c>
-      <c r="I389" s="5" t="inlineStr">
-        <is>
-          <t>2025-01-05</t>
-        </is>
-      </c>
-      <c r="J389" s="7" t="n">
-        <v>4872.249380417559</v>
-      </c>
     </row>
     <row r="390" ht="19" customHeight="1">
       <c r="A390" s="2" t="inlineStr">
@@ -15307,14 +12191,6 @@
       <c r="H390" s="4" t="n">
         <v>481988.5337482942</v>
       </c>
-      <c r="I390" s="2" t="inlineStr">
-        <is>
-          <t>2025-01-06</t>
-        </is>
-      </c>
-      <c r="J390" s="4" t="n">
-        <v>3193.829459471121</v>
-      </c>
     </row>
     <row r="391" ht="19" customHeight="1">
       <c r="A391" s="5" t="inlineStr">
@@ -15345,14 +12221,6 @@
       <c r="H391" s="7" t="n">
         <v>453163.6923026079</v>
       </c>
-      <c r="I391" s="5" t="inlineStr">
-        <is>
-          <t>2025-01-06</t>
-        </is>
-      </c>
-      <c r="J391" s="7" t="n">
-        <v>1695.578908569781</v>
-      </c>
     </row>
     <row r="392" ht="19" customHeight="1">
       <c r="A392" s="2" t="inlineStr">
@@ -15383,14 +12251,6 @@
       <c r="H392" s="4" t="n">
         <v>511608.1072523247</v>
       </c>
-      <c r="I392" s="2" t="inlineStr">
-        <is>
-          <t>2025-02-02</t>
-        </is>
-      </c>
-      <c r="J392" s="4" t="n">
-        <v>988.8995498715898</v>
-      </c>
     </row>
     <row r="393" ht="19" customHeight="1">
       <c r="A393" s="5" t="inlineStr">
@@ -15421,14 +12281,6 @@
       <c r="H393" s="7" t="n">
         <v>513030.4970158386</v>
       </c>
-      <c r="I393" s="5" t="inlineStr">
-        <is>
-          <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="J393" s="7" t="n">
-        <v>1001.543014436158</v>
-      </c>
     </row>
     <row r="394" ht="19" customHeight="1">
       <c r="A394" s="2" t="inlineStr">
@@ -15459,14 +12311,6 @@
       <c r="H394" s="4" t="n">
         <v>484965.1665486381</v>
       </c>
-      <c r="I394" s="2" t="inlineStr">
-        <is>
-          <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="J394" s="4" t="n">
-        <v>4009.332923885774</v>
-      </c>
     </row>
     <row r="395" ht="19" customHeight="1">
       <c r="A395" s="5" t="inlineStr">
@@ -15497,14 +12341,6 @@
       <c r="H395" s="7" t="n">
         <v>455198.8385451974</v>
       </c>
-      <c r="I395" s="5" t="inlineStr">
-        <is>
-          <t>2025-02-17</t>
-        </is>
-      </c>
-      <c r="J395" s="7" t="n">
-        <v>1860.395500215046</v>
-      </c>
     </row>
     <row r="396" ht="19" customHeight="1">
       <c r="A396" s="2" t="inlineStr">
@@ -15535,14 +12371,6 @@
       <c r="H396" s="4" t="n">
         <v>486243.0595742713</v>
       </c>
-      <c r="I396" s="2" t="inlineStr">
-        <is>
-          <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="J396" s="4" t="n">
-        <v>1616.557255041229</v>
-      </c>
     </row>
     <row r="397" ht="19" customHeight="1">
       <c r="A397" s="5" t="inlineStr">
@@ -15573,14 +12401,6 @@
       <c r="H397" s="7" t="n">
         <v>522904.5912884604</v>
       </c>
-      <c r="I397" s="5" t="inlineStr">
-        <is>
-          <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="J397" s="7" t="n">
-        <v>23485.23542868556</v>
-      </c>
     </row>
     <row r="398" ht="19" customHeight="1">
       <c r="A398" s="2" t="inlineStr">
@@ -15611,14 +12431,6 @@
       <c r="H398" s="4" t="n">
         <v>492993.7665471389</v>
       </c>
-      <c r="I398" s="2" t="inlineStr">
-        <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="J398" s="4" t="n">
-        <v>1300.470640927022</v>
-      </c>
     </row>
     <row r="399" ht="19" customHeight="1">
       <c r="A399" s="5" t="inlineStr">
@@ -15649,14 +12461,6 @@
       <c r="H399" s="7" t="n">
         <v>463212.9888699101</v>
       </c>
-      <c r="I399" s="5" t="inlineStr">
-        <is>
-          <t>2025-04-02</t>
-        </is>
-      </c>
-      <c r="J399" s="7" t="n">
-        <v>930.6493024134003</v>
-      </c>
     </row>
     <row r="400" ht="19" customHeight="1">
       <c r="A400" s="2" t="inlineStr">
@@ -15687,14 +12491,6 @@
       <c r="H400" s="4" t="n">
         <v>494148.8373455734</v>
       </c>
-      <c r="I400" s="2" t="inlineStr">
-        <is>
-          <t>2025-04-15</t>
-        </is>
-      </c>
-      <c r="J400" s="4" t="n">
-        <v>1110.818672458498</v>
-      </c>
     </row>
     <row r="401" ht="19" customHeight="1">
       <c r="A401" s="5" t="inlineStr">
@@ -15725,14 +12521,6 @@
       <c r="H401" s="7" t="n">
         <v>465132.0861698892</v>
       </c>
-      <c r="I401" s="5" t="inlineStr">
-        <is>
-          <t>2025-04-15</t>
-        </is>
-      </c>
-      <c r="J401" s="7" t="n">
-        <v>1381.750055984961</v>
-      </c>
     </row>
     <row r="402" ht="19" customHeight="1">
       <c r="A402" s="2" t="inlineStr">
@@ -15763,14 +12551,6 @@
       <c r="H402" s="4" t="n">
         <v>525387.2258661746</v>
       </c>
-      <c r="I402" s="2" t="inlineStr">
-        <is>
-          <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="J402" s="4" t="n">
-        <v>2212.606298799447</v>
-      </c>
     </row>
     <row r="403" ht="19" customHeight="1">
       <c r="A403" s="5" t="inlineStr">
@@ -15801,14 +12581,6 @@
       <c r="H403" s="7" t="n">
         <v>524971.7977447673</v>
       </c>
-      <c r="I403" s="5" t="inlineStr">
-        <is>
-          <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="J403" s="7" t="n">
-        <v>3242.145556200007</v>
-      </c>
     </row>
     <row r="404" ht="19" customHeight="1">
       <c r="A404" s="2" t="inlineStr">
@@ -15839,14 +12611,6 @@
       <c r="H404" s="4" t="n">
         <v>495273.654139514</v>
       </c>
-      <c r="I404" s="2" t="inlineStr">
-        <is>
-          <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="J404" s="4" t="n">
-        <v>899.9437456137346</v>
-      </c>
     </row>
     <row r="405" ht="19" customHeight="1">
       <c r="A405" s="5" t="inlineStr">
@@ -15877,14 +12641,6 @@
       <c r="H405" s="7" t="n">
         <v>466721.0987342718</v>
       </c>
-      <c r="I405" s="5" t="inlineStr">
-        <is>
-          <t>2025-05-21</t>
-        </is>
-      </c>
-      <c r="J405" s="7" t="n">
-        <v>1784.534712827636</v>
-      </c>
     </row>
     <row r="406" ht="19" customHeight="1">
       <c r="A406" s="2" t="inlineStr">
@@ -15915,14 +12671,6 @@
       <c r="H406" s="4" t="n">
         <v>529125.1758542279</v>
       </c>
-      <c r="I406" s="2" t="inlineStr">
-        <is>
-          <t>2025-06-29</t>
-        </is>
-      </c>
-      <c r="J406" s="4" t="n">
-        <v>3309.878402081622</v>
-      </c>
     </row>
     <row r="407" ht="19" customHeight="1">
       <c r="A407" s="5" t="inlineStr">
@@ -15953,14 +12701,6 @@
       <c r="H407" s="7" t="n">
         <v>532416.4954565379</v>
       </c>
-      <c r="I407" s="5" t="inlineStr">
-        <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="J407" s="7" t="n">
-        <v>3364.064678786915</v>
-      </c>
     </row>
     <row r="408" ht="19" customHeight="1">
       <c r="A408" s="2" t="inlineStr">
@@ -15991,14 +12731,6 @@
       <c r="H408" s="4" t="n">
         <v>503429.0048702746</v>
       </c>
-      <c r="I408" s="2" t="inlineStr">
-        <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="J408" s="4" t="n">
-        <v>1610.416143681296</v>
-      </c>
     </row>
     <row r="409" ht="19" customHeight="1">
       <c r="A409" s="5" t="inlineStr">
@@ -16028,14 +12760,6 @@
       </c>
       <c r="H409" s="7" t="n">
         <v>501242.588605216</v>
-      </c>
-      <c r="I409" s="5" t="inlineStr">
-        <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="J409" s="7" t="n">
-        <v>1299.567536315267</v>
       </c>
     </row>
   </sheetData>

--- a/projection_1.5m_buy.xlsx
+++ b/projection_1.5m_buy.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I323"/>
+  <dimension ref="A1:G323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -493,10 +493,8 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="145" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="145" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -527,20 +525,10 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Allocated</t>
+          <t>CashAfterTrade</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>RemainingAllocation</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>CashAfterTrade</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Reason</t>
         </is>
@@ -567,15 +555,9 @@
         <v>24035</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>455.1599999999999</v>
-      </c>
-      <c r="H2" s="4" t="n">
         <v>175965</v>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 115.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -602,15 +584,9 @@
         <v>23287</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G3" s="8" t="n">
-        <v>1203.16</v>
-      </c>
-      <c r="H3" s="8" t="n">
         <v>152678</v>
       </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 319.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -637,15 +613,9 @@
         <v>24024</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>466.1599999999999</v>
-      </c>
-      <c r="H4" s="4" t="n">
         <v>128654</v>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 168.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -672,15 +642,9 @@
         <v>24192</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G5" s="8" t="n">
-        <v>298.1599999999999</v>
-      </c>
-      <c r="H5" s="8" t="n">
         <v>104462</v>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 504.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -707,15 +671,9 @@
         <v>24040</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>450.1599999999999</v>
-      </c>
-      <c r="H6" s="4" t="n">
         <v>80422</v>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 601.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -742,15 +700,9 @@
         <v>23904</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>586.1599999999999</v>
-      </c>
-      <c r="H7" s="8" t="n">
         <v>56518</v>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 498.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -777,15 +729,9 @@
         <v>24310</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>180.1599999999999</v>
-      </c>
-      <c r="H8" s="4" t="n">
         <v>32208</v>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 170.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -812,15 +758,9 @@
         <v>24156</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>334.1599999999999</v>
-      </c>
-      <c r="H9" s="8" t="n">
         <v>8052</v>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 244.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -847,15 +787,9 @@
         <v>22968</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>1522.16</v>
-      </c>
-      <c r="H10" s="4" t="n">
         <v>-14916</v>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 696.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -882,15 +816,9 @@
         <v>24304</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>186.1599999999999</v>
-      </c>
-      <c r="H11" s="8" t="n">
         <v>-39220</v>
       </c>
-      <c r="I11" s="9" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 112.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -917,15 +845,9 @@
         <v>23817</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>673.1599999999999</v>
-      </c>
-      <c r="H12" s="4" t="n">
         <v>-63037</v>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 467.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -952,15 +874,9 @@
         <v>24436</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <v>54.15999999999985</v>
-      </c>
-      <c r="H13" s="8" t="n">
         <v>-87473</v>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="G13" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 82.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -987,15 +903,9 @@
         <v>24282</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>208.1599999999999</v>
-      </c>
-      <c r="H14" s="4" t="n">
         <v>-111755</v>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 213.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -1022,15 +932,9 @@
         <v>24336</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>154.1599999999999</v>
-      </c>
-      <c r="H15" s="8" t="n">
         <v>-136091</v>
       </c>
-      <c r="I15" s="9" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 144.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -1057,15 +961,9 @@
         <v>22698</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>1792.16</v>
-      </c>
-      <c r="H16" s="4" t="n">
         <v>-158789</v>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 873.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -1092,15 +990,9 @@
         <v>24500</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G17" s="8" t="n">
-        <v>-9.840000000000146</v>
-      </c>
-      <c r="H17" s="8" t="n">
         <v>-183289</v>
       </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 50.00) (scaled by 3.67x to fit Rs. 1.5M target) (Qty adjusted by 1 to hit exact 1.5M target)</t>
         </is>
@@ -1127,15 +1019,9 @@
         <v>24490</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>0.1599999999998545</v>
-      </c>
-      <c r="H18" s="4" t="n">
         <v>-207779</v>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 155.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -1162,15 +1048,9 @@
         <v>23210</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G19" s="8" t="n">
-        <v>1280.16</v>
-      </c>
-      <c r="H19" s="8" t="n">
         <v>-230989</v>
       </c>
-      <c r="I19" s="9" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 422.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -1197,15 +1077,9 @@
         <v>24400</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>90.15999999999985</v>
-      </c>
-      <c r="H20" s="4" t="n">
         <v>-255389</v>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 80.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -1232,15 +1106,9 @@
         <v>24420</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G21" s="8" t="n">
-        <v>70.15999999999985</v>
-      </c>
-      <c r="H21" s="8" t="n">
         <v>-279809</v>
       </c>
-      <c r="I21" s="9" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 185.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -1267,15 +1135,9 @@
         <v>23954</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>536.1599999999999</v>
-      </c>
-      <c r="H22" s="4" t="n">
         <v>-303763</v>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 406.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -1302,15 +1164,9 @@
         <v>23136</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G23" s="8" t="n">
-        <v>1354.16</v>
-      </c>
-      <c r="H23" s="8" t="n">
         <v>-326899</v>
       </c>
-      <c r="I23" s="9" t="inlineStr">
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 482.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -1337,15 +1193,9 @@
         <v>23192</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>1298.16</v>
-      </c>
-      <c r="H24" s="4" t="n">
         <v>-301321</v>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 892.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -1372,15 +1222,9 @@
         <v>24000</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G25" s="8" t="n">
-        <v>490.1599999999999</v>
-      </c>
-      <c r="H25" s="8" t="n">
         <v>-325321</v>
       </c>
-      <c r="I25" s="9" t="inlineStr">
+      <c r="G25" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 600.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -1407,15 +1251,9 @@
         <v>24220</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>270.1599999999999</v>
-      </c>
-      <c r="H26" s="4" t="n">
         <v>-349541</v>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 346.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -1442,15 +1280,9 @@
         <v>24360</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G27" s="8" t="n">
-        <v>130.1599999999999</v>
-      </c>
-      <c r="H27" s="8" t="n">
         <v>-373901</v>
       </c>
-      <c r="I27" s="9" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 84.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -1477,15 +1309,9 @@
         <v>24288</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>202.1599999999999</v>
-      </c>
-      <c r="H28" s="4" t="n">
         <v>-398189</v>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 96.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -1512,15 +1338,9 @@
         <v>19670</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G29" s="8" t="n">
-        <v>4820.16</v>
-      </c>
-      <c r="H29" s="8" t="n">
         <v>-417859</v>
       </c>
-      <c r="I29" s="9" t="inlineStr">
+      <c r="G29" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 2810.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -1547,15 +1367,9 @@
         <v>24024</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>466.1599999999999</v>
-      </c>
-      <c r="H30" s="4" t="n">
         <v>-340698</v>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 273.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -1582,15 +1396,9 @@
         <v>22605</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G31" s="8" t="n">
-        <v>1885.16</v>
-      </c>
-      <c r="H31" s="8" t="n">
         <v>-312903</v>
       </c>
-      <c r="I31" s="9" t="inlineStr">
+      <c r="G31" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 685.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -1617,15 +1425,9 @@
         <v>22990</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>1500.16</v>
-      </c>
-      <c r="H32" s="4" t="n">
         <v>-335893</v>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 418.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -1652,15 +1454,9 @@
         <v>22880</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G33" s="8" t="n">
-        <v>1610.16</v>
-      </c>
-      <c r="H33" s="8" t="n">
         <v>-333045</v>
       </c>
-      <c r="I33" s="9" t="inlineStr">
+      <c r="G33" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 520.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -1687,15 +1483,9 @@
         <v>23520</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>970.1599999999999</v>
-      </c>
-      <c r="H34" s="4" t="n">
         <v>-356565</v>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 280.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -1722,15 +1512,9 @@
         <v>22848</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G35" s="8" t="n">
-        <v>1642.16</v>
-      </c>
-      <c r="H35" s="8" t="n">
         <v>-355323</v>
       </c>
-      <c r="I35" s="9" t="inlineStr">
+      <c r="G35" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 448.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -1757,15 +1541,9 @@
         <v>24024</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>466.1599999999999</v>
-      </c>
-      <c r="H36" s="4" t="n">
         <v>113947</v>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 312.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -1792,15 +1570,9 @@
         <v>24288</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G37" s="8" t="n">
-        <v>202.1599999999999</v>
-      </c>
-      <c r="H37" s="8" t="n">
         <v>89659</v>
       </c>
-      <c r="I37" s="9" t="inlineStr">
+      <c r="G37" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 736.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -1827,15 +1599,9 @@
         <v>21924</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G38" s="4" t="n">
-        <v>2566.16</v>
-      </c>
-      <c r="H38" s="4" t="n">
         <v>67735</v>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 756.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -1862,15 +1628,9 @@
         <v>24311</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G39" s="8" t="n">
-        <v>179.1599999999999</v>
-      </c>
-      <c r="H39" s="8" t="n">
         <v>43424</v>
       </c>
-      <c r="I39" s="9" t="inlineStr">
+      <c r="G39" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 161.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -1897,15 +1657,9 @@
         <v>24208</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>282.1599999999999</v>
-      </c>
-      <c r="H40" s="4" t="n">
         <v>19216</v>
       </c>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 89.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -1932,15 +1686,9 @@
         <v>24480</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G41" s="8" t="n">
-        <v>10.15999999999985</v>
-      </c>
-      <c r="H41" s="8" t="n">
         <v>23275</v>
       </c>
-      <c r="I41" s="9" t="inlineStr">
+      <c r="G41" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 180.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -1967,15 +1715,9 @@
         <v>24168</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>322.1599999999999</v>
-      </c>
-      <c r="H42" s="4" t="n">
         <v>51740</v>
       </c>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 212.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -2002,15 +1744,9 @@
         <v>24396</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G43" s="8" t="n">
-        <v>94.15999999999985</v>
-      </c>
-      <c r="H43" s="8" t="n">
         <v>27344</v>
       </c>
-      <c r="I43" s="9" t="inlineStr">
+      <c r="G43" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 228.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -2037,15 +1773,9 @@
         <v>24200</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G44" s="4" t="n">
-        <v>290.1599999999999</v>
-      </c>
-      <c r="H44" s="4" t="n">
         <v>3144</v>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 275.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -2072,15 +1802,9 @@
         <v>22840</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G45" s="8" t="n">
-        <v>1650.16</v>
-      </c>
-      <c r="H45" s="8" t="n">
         <v>29321</v>
       </c>
-      <c r="I45" s="9" t="inlineStr">
+      <c r="G45" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 571.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -2107,15 +1831,9 @@
         <v>20775</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>3715.16</v>
-      </c>
-      <c r="H46" s="4" t="n">
         <v>8546</v>
       </c>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1385.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -2142,15 +1860,9 @@
         <v>23579</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G47" s="8" t="n">
-        <v>911.1599999999999</v>
-      </c>
-      <c r="H47" s="8" t="n">
         <v>-15033</v>
       </c>
-      <c r="I47" s="9" t="inlineStr">
+      <c r="G47" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 323.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -2177,15 +1889,9 @@
         <v>24336</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G48" s="4" t="n">
-        <v>154.1599999999999</v>
-      </c>
-      <c r="H48" s="4" t="n">
         <v>-39369</v>
       </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 144.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -2212,15 +1918,9 @@
         <v>21078</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G49" s="8" t="n">
-        <v>3412.16</v>
-      </c>
-      <c r="H49" s="8" t="n">
         <v>-29947</v>
       </c>
-      <c r="I49" s="9" t="inlineStr">
+      <c r="G49" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1171.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -2247,15 +1947,9 @@
         <v>24017</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G50" s="4" t="n">
-        <v>473.1599999999999</v>
-      </c>
-      <c r="H50" s="4" t="n">
         <v>122498</v>
       </c>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 329.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -2282,15 +1976,9 @@
         <v>23664</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G51" s="8" t="n">
-        <v>826.1599999999999</v>
-      </c>
-      <c r="H51" s="8" t="n">
         <v>98834</v>
       </c>
-      <c r="I51" s="9" t="inlineStr">
+      <c r="G51" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 493.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -2317,15 +2005,9 @@
         <v>23925</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>24490.16</v>
-      </c>
-      <c r="G52" s="4" t="n">
-        <v>565.1599999999999</v>
-      </c>
-      <c r="H52" s="4" t="n">
         <v>74909</v>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 145.00) (scaled by 3.67x to fit Rs. 1.5M target)</t>
         </is>
@@ -2352,15 +2034,9 @@
         <v>21150</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>24943.57</v>
-      </c>
-      <c r="G53" s="8" t="n">
-        <v>3793.57</v>
-      </c>
-      <c r="H53" s="8" t="n">
         <v>53759</v>
       </c>
-      <c r="I53" s="9" t="inlineStr">
+      <c r="G53" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1410.00) (scaled by 3.74x to fit Rs. 1.5M target)</t>
         </is>
@@ -2387,15 +2063,9 @@
         <v>24360</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>24943.57</v>
-      </c>
-      <c r="G54" s="4" t="n">
-        <v>583.5699999999997</v>
-      </c>
-      <c r="H54" s="4" t="n">
         <v>29399</v>
       </c>
-      <c r="I54" s="5" t="inlineStr">
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 232.00) (scaled by 3.74x to fit Rs. 1.5M target)</t>
         </is>
@@ -2422,15 +2092,9 @@
         <v>24750</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>24943.57</v>
-      </c>
-      <c r="G55" s="8" t="n">
-        <v>193.5699999999997</v>
-      </c>
-      <c r="H55" s="8" t="n">
         <v>4649</v>
       </c>
-      <c r="I55" s="9" t="inlineStr">
+      <c r="G55" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 165.00) (scaled by 3.74x to fit Rs. 1.5M target)</t>
         </is>
@@ -2457,15 +2121,9 @@
         <v>22680</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>24943.57</v>
-      </c>
-      <c r="G56" s="4" t="n">
-        <v>2263.57</v>
-      </c>
-      <c r="H56" s="4" t="n">
         <v>-18031</v>
       </c>
-      <c r="I56" s="5" t="inlineStr">
+      <c r="G56" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 756.00) (scaled by 3.74x to fit Rs. 1.5M target)</t>
         </is>
@@ -2492,15 +2150,9 @@
         <v>24124</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>24943.57</v>
-      </c>
-      <c r="G57" s="8" t="n">
-        <v>819.5699999999997</v>
-      </c>
-      <c r="H57" s="8" t="n">
         <v>-15680</v>
       </c>
-      <c r="I57" s="9" t="inlineStr">
+      <c r="G57" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 652.00) (scaled by 3.74x to fit Rs. 1.5M target)</t>
         </is>
@@ -2527,15 +2179,9 @@
         <v>24682</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>24943.57</v>
-      </c>
-      <c r="G58" s="4" t="n">
-        <v>261.5699999999997</v>
-      </c>
-      <c r="H58" s="4" t="n">
         <v>9408</v>
       </c>
-      <c r="I58" s="5" t="inlineStr">
+      <c r="G58" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 287.00) (scaled by 3.74x to fit Rs. 1.5M target)</t>
         </is>
@@ -2562,15 +2208,9 @@
         <v>24806</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>24943.57</v>
-      </c>
-      <c r="G59" s="8" t="n">
-        <v>137.5699999999997</v>
-      </c>
-      <c r="H59" s="8" t="n">
         <v>-15398</v>
       </c>
-      <c r="I59" s="9" t="inlineStr">
+      <c r="G59" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 314.00) (scaled by 3.74x to fit Rs. 1.5M target)</t>
         </is>
@@ -2597,15 +2237,9 @@
         <v>24552</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>24943.57</v>
-      </c>
-      <c r="G60" s="4" t="n">
-        <v>391.5699999999997</v>
-      </c>
-      <c r="H60" s="4" t="n">
         <v>-12050</v>
       </c>
-      <c r="I60" s="5" t="inlineStr">
+      <c r="G60" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 124.00) (scaled by 3.74x to fit Rs. 1.5M target)</t>
         </is>
@@ -2632,15 +2266,9 @@
         <v>22650</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>24943.57</v>
-      </c>
-      <c r="G61" s="8" t="n">
-        <v>2293.57</v>
-      </c>
-      <c r="H61" s="8" t="n">
         <v>-34700</v>
       </c>
-      <c r="I61" s="9" t="inlineStr">
+      <c r="G61" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 755.00) (scaled by 3.74x to fit Rs. 1.5M target)</t>
         </is>
@@ -2667,15 +2295,9 @@
         <v>24820</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>24943.57</v>
-      </c>
-      <c r="G62" s="4" t="n">
-        <v>123.5699999999997</v>
-      </c>
-      <c r="H62" s="4" t="n">
         <v>-59520</v>
       </c>
-      <c r="I62" s="5" t="inlineStr">
+      <c r="G62" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 170.00) (scaled by 3.74x to fit Rs. 1.5M target)</t>
         </is>
@@ -2702,15 +2324,9 @@
         <v>24840</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>24943.57</v>
-      </c>
-      <c r="G63" s="8" t="n">
-        <v>103.5699999999997</v>
-      </c>
-      <c r="H63" s="8" t="n">
         <v>-34192</v>
       </c>
-      <c r="I63" s="9" t="inlineStr">
+      <c r="G63" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 54.00) (scaled by 3.74x to fit Rs. 1.5M target)</t>
         </is>
@@ -2737,15 +2353,9 @@
         <v>24240</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>24943.57</v>
-      </c>
-      <c r="G64" s="4" t="n">
-        <v>703.5699999999997</v>
-      </c>
-      <c r="H64" s="4" t="n">
         <v>-27352</v>
       </c>
-      <c r="I64" s="5" t="inlineStr">
+      <c r="G64" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 240.00) (scaled by 3.74x to fit Rs. 1.5M target)</t>
         </is>
@@ -2772,15 +2382,9 @@
         <v>22230</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>24943.57</v>
-      </c>
-      <c r="G65" s="8" t="n">
-        <v>2713.57</v>
-      </c>
-      <c r="H65" s="8" t="n">
         <v>-49582</v>
       </c>
-      <c r="I65" s="9" t="inlineStr">
+      <c r="G65" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 741.00) (scaled by 3.74x to fit Rs. 1.5M target)</t>
         </is>
@@ -2807,15 +2411,9 @@
         <v>20370</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>24943.57</v>
-      </c>
-      <c r="G66" s="4" t="n">
-        <v>4573.57</v>
-      </c>
-      <c r="H66" s="4" t="n">
         <v>-69952</v>
       </c>
-      <c r="I66" s="5" t="inlineStr">
+      <c r="G66" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1358.00) (scaled by 3.74x to fit Rs. 1.5M target)</t>
         </is>
@@ -2842,15 +2440,9 @@
         <v>24158</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>24943.57</v>
-      </c>
-      <c r="G67" s="8" t="n">
-        <v>785.5699999999997</v>
-      </c>
-      <c r="H67" s="8" t="n">
         <v>-60070</v>
       </c>
-      <c r="I67" s="9" t="inlineStr">
+      <c r="G67" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 257.00) (scaled by 3.74x to fit Rs. 1.5M target)</t>
         </is>
@@ -2877,15 +2469,9 @@
         <v>25137</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>24943.57</v>
-      </c>
-      <c r="G68" s="4" t="n">
-        <v>-193.4300000000003</v>
-      </c>
-      <c r="H68" s="4" t="n">
         <v>-85207</v>
       </c>
-      <c r="I68" s="5" t="inlineStr">
+      <c r="G68" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1323.00) (scaled by 3.74x to fit Rs. 1.5M target)</t>
         </is>
@@ -2912,15 +2498,9 @@
         <v>24440</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>24943.57</v>
-      </c>
-      <c r="G69" s="8" t="n">
-        <v>503.5699999999997</v>
-      </c>
-      <c r="H69" s="8" t="n">
         <v>-109647</v>
       </c>
-      <c r="I69" s="9" t="inlineStr">
+      <c r="G69" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 260.00) (scaled by 3.74x to fit Rs. 1.5M target)</t>
         </is>
@@ -2947,15 +2527,9 @@
         <v>24440</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>24943.57</v>
-      </c>
-      <c r="G70" s="4" t="n">
-        <v>503.5699999999997</v>
-      </c>
-      <c r="H70" s="4" t="n">
         <v>-134087</v>
       </c>
-      <c r="I70" s="5" t="inlineStr">
+      <c r="G70" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 260.00) (scaled by 3.74x to fit Rs. 1.5M target)</t>
         </is>
@@ -2982,15 +2556,9 @@
         <v>24252</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>24943.57</v>
-      </c>
-      <c r="G71" s="8" t="n">
-        <v>691.5699999999997</v>
-      </c>
-      <c r="H71" s="8" t="n">
         <v>-158339</v>
       </c>
-      <c r="I71" s="9" t="inlineStr">
+      <c r="G71" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 258.00) (scaled by 3.74x to fit Rs. 1.5M target)</t>
         </is>
@@ -3017,15 +2585,9 @@
         <v>24888</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>24943.57</v>
-      </c>
-      <c r="G72" s="4" t="n">
-        <v>55.56999999999971</v>
-      </c>
-      <c r="H72" s="4" t="n">
         <v>-183227</v>
       </c>
-      <c r="I72" s="5" t="inlineStr">
+      <c r="G72" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 61.00) (scaled by 3.74x to fit Rs. 1.5M target)</t>
         </is>
@@ -3052,15 +2614,9 @@
         <v>24480</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>24943.57</v>
-      </c>
-      <c r="G73" s="8" t="n">
-        <v>463.5699999999997</v>
-      </c>
-      <c r="H73" s="8" t="n">
         <v>-207707</v>
       </c>
-      <c r="I73" s="9" t="inlineStr">
+      <c r="G73" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 816.00) (scaled by 3.74x to fit Rs. 1.5M target)</t>
         </is>
@@ -3087,15 +2643,9 @@
         <v>22500</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>24943.57</v>
-      </c>
-      <c r="G74" s="4" t="n">
-        <v>2443.57</v>
-      </c>
-      <c r="H74" s="4" t="n">
         <v>-230207</v>
       </c>
-      <c r="I74" s="5" t="inlineStr">
+      <c r="G74" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 750.00) (scaled by 3.74x to fit Rs. 1.5M target)</t>
         </is>
@@ -3122,15 +2672,9 @@
         <v>24354</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>24943.57</v>
-      </c>
-      <c r="G75" s="8" t="n">
-        <v>589.5699999999997</v>
-      </c>
-      <c r="H75" s="8" t="n">
         <v>-254561</v>
       </c>
-      <c r="I75" s="9" t="inlineStr">
+      <c r="G75" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1107.00) (scaled by 3.74x to fit Rs. 1.5M target)</t>
         </is>
@@ -3157,15 +2701,9 @@
         <v>23715</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>24943.57</v>
-      </c>
-      <c r="G76" s="4" t="n">
-        <v>1228.57</v>
-      </c>
-      <c r="H76" s="4" t="n">
         <v>-149158</v>
       </c>
-      <c r="I76" s="5" t="inlineStr">
+      <c r="G76" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1581.00) (scaled by 3.74x to fit Rs. 1.5M target)</t>
         </is>
@@ -3192,15 +2730,9 @@
         <v>24521</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>24943.57</v>
-      </c>
-      <c r="G77" s="8" t="n">
-        <v>422.5699999999997</v>
-      </c>
-      <c r="H77" s="8" t="n">
         <v>-173679</v>
       </c>
-      <c r="I77" s="9" t="inlineStr">
+      <c r="G77" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 113.00) (scaled by 3.74x to fit Rs. 1.5M target)</t>
         </is>
@@ -3227,15 +2759,9 @@
         <v>23925</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>24943.57</v>
-      </c>
-      <c r="G78" s="4" t="n">
-        <v>1018.57</v>
-      </c>
-      <c r="H78" s="4" t="n">
         <v>-50807</v>
       </c>
-      <c r="I78" s="5" t="inlineStr">
+      <c r="G78" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 319.00) (scaled by 3.74x to fit Rs. 1.5M target)</t>
         </is>
@@ -3262,15 +2788,9 @@
         <v>24832</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>24943.57</v>
-      </c>
-      <c r="G79" s="8" t="n">
-        <v>111.5699999999997</v>
-      </c>
-      <c r="H79" s="8" t="n">
         <v>34464</v>
       </c>
-      <c r="I79" s="9" t="inlineStr">
+      <c r="G79" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 256.00) (scaled by 3.74x to fit Rs. 1.5M target)</t>
         </is>
@@ -3297,15 +2817,9 @@
         <v>23070</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>24943.57</v>
-      </c>
-      <c r="G80" s="4" t="n">
-        <v>1873.57</v>
-      </c>
-      <c r="H80" s="4" t="n">
         <v>11394</v>
       </c>
-      <c r="I80" s="5" t="inlineStr">
+      <c r="G80" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1538.00) (scaled by 3.74x to fit Rs. 1.5M target)</t>
         </is>
@@ -3332,15 +2846,9 @@
         <v>21840</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>24943.57</v>
-      </c>
-      <c r="G81" s="8" t="n">
-        <v>3103.57</v>
-      </c>
-      <c r="H81" s="8" t="n">
         <v>-10446</v>
       </c>
-      <c r="I81" s="9" t="inlineStr">
+      <c r="G81" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 840.00) (scaled by 3.74x to fit Rs. 1.5M target)</t>
         </is>
@@ -3367,15 +2875,9 @@
         <v>24633</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>24943.57</v>
-      </c>
-      <c r="G82" s="4" t="n">
-        <v>310.5699999999997</v>
-      </c>
-      <c r="H82" s="4" t="n">
         <v>-10599</v>
       </c>
-      <c r="I82" s="5" t="inlineStr">
+      <c r="G82" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 153.00) (scaled by 3.74x to fit Rs. 1.5M target)</t>
         </is>
@@ -3402,15 +2904,9 @@
         <v>23700</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>24943.57</v>
-      </c>
-      <c r="G83" s="8" t="n">
-        <v>1243.57</v>
-      </c>
-      <c r="H83" s="8" t="n">
         <v>38587</v>
       </c>
-      <c r="I83" s="9" t="inlineStr">
+      <c r="G83" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 790.00) (scaled by 3.74x to fit Rs. 1.5M target)</t>
         </is>
@@ -3437,15 +2933,9 @@
         <v>24585</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>24943.57</v>
-      </c>
-      <c r="G84" s="4" t="n">
-        <v>358.5699999999997</v>
-      </c>
-      <c r="H84" s="4" t="n">
         <v>42660</v>
       </c>
-      <c r="I84" s="5" t="inlineStr">
+      <c r="G84" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 149.00) (scaled by 3.74x to fit Rs. 1.5M target)</t>
         </is>
@@ -3472,15 +2962,9 @@
         <v>27677</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G85" s="8" t="n">
-        <v>1642.259999999998</v>
-      </c>
-      <c r="H85" s="8" t="n">
         <v>320406</v>
       </c>
-      <c r="I85" s="9" t="inlineStr">
+      <c r="G85" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 2129.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -3507,15 +2991,9 @@
         <v>26195</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G86" s="4" t="n">
-        <v>3124.259999999998</v>
-      </c>
-      <c r="H86" s="4" t="n">
         <v>322226</v>
       </c>
-      <c r="I86" s="5" t="inlineStr">
+      <c r="G86" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 2015.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -3542,15 +3020,9 @@
         <v>28644</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G87" s="8" t="n">
-        <v>675.2599999999984</v>
-      </c>
-      <c r="H87" s="8" t="n">
         <v>293582</v>
       </c>
-      <c r="I87" s="9" t="inlineStr">
+      <c r="G87" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 462.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -3577,15 +3049,9 @@
         <v>28582</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G88" s="4" t="n">
-        <v>737.2599999999984</v>
-      </c>
-      <c r="H88" s="4" t="n">
         <v>265000</v>
       </c>
-      <c r="I88" s="5" t="inlineStr">
+      <c r="G88" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 461.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -3612,15 +3078,9 @@
         <v>27930</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G89" s="8" t="n">
-        <v>1389.259999999998</v>
-      </c>
-      <c r="H89" s="8" t="n">
         <v>237070</v>
       </c>
-      <c r="I89" s="9" t="inlineStr">
+      <c r="G89" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 490.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -3647,15 +3107,9 @@
         <v>28000</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G90" s="4" t="n">
-        <v>1319.259999999998</v>
-      </c>
-      <c r="H90" s="4" t="n">
         <v>209070</v>
       </c>
-      <c r="I90" s="5" t="inlineStr">
+      <c r="G90" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 400.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -3682,15 +3136,9 @@
         <v>28908</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G91" s="8" t="n">
-        <v>411.2599999999984</v>
-      </c>
-      <c r="H91" s="8" t="n">
         <v>180162</v>
       </c>
-      <c r="I91" s="9" t="inlineStr">
+      <c r="G91" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 438.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -3717,15 +3165,9 @@
         <v>26403</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G92" s="4" t="n">
-        <v>2916.259999999998</v>
-      </c>
-      <c r="H92" s="4" t="n">
         <v>153759</v>
       </c>
-      <c r="I92" s="5" t="inlineStr">
+      <c r="G92" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 2031.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -3752,15 +3194,9 @@
         <v>26350</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G93" s="8" t="n">
-        <v>2969.259999999998</v>
-      </c>
-      <c r="H93" s="8" t="n">
         <v>127409</v>
       </c>
-      <c r="I93" s="9" t="inlineStr">
+      <c r="G93" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 850.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -3787,15 +3223,9 @@
         <v>29250</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G94" s="4" t="n">
-        <v>69.2599999999984</v>
-      </c>
-      <c r="H94" s="4" t="n">
         <v>98159</v>
       </c>
-      <c r="I94" s="5" t="inlineStr">
+      <c r="G94" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 390.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -3822,15 +3252,9 @@
         <v>24960</v>
       </c>
       <c r="F95" s="8" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G95" s="8" t="n">
-        <v>4359.259999999998</v>
-      </c>
-      <c r="H95" s="8" t="n">
         <v>73199</v>
       </c>
-      <c r="I95" s="9" t="inlineStr">
+      <c r="G95" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 960.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -3857,15 +3281,9 @@
         <v>28996</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G96" s="4" t="n">
-        <v>323.2599999999984</v>
-      </c>
-      <c r="H96" s="4" t="n">
         <v>44203</v>
       </c>
-      <c r="I96" s="5" t="inlineStr">
+      <c r="G96" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 659.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -3892,15 +3310,9 @@
         <v>26133</v>
       </c>
       <c r="F97" s="8" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G97" s="8" t="n">
-        <v>3186.259999999998</v>
-      </c>
-      <c r="H97" s="8" t="n">
         <v>101585</v>
       </c>
-      <c r="I97" s="9" t="inlineStr">
+      <c r="G97" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 843.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -3927,15 +3339,9 @@
         <v>28614</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G98" s="4" t="n">
-        <v>705.2599999999984</v>
-      </c>
-      <c r="H98" s="4" t="n">
         <v>103041</v>
       </c>
-      <c r="I98" s="5" t="inlineStr">
+      <c r="G98" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 251.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -3962,15 +3368,9 @@
         <v>28600</v>
       </c>
       <c r="F99" s="8" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G99" s="8" t="n">
-        <v>719.2599999999984</v>
-      </c>
-      <c r="H99" s="8" t="n">
         <v>104317</v>
       </c>
-      <c r="I99" s="9" t="inlineStr">
+      <c r="G99" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 650.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -3997,15 +3397,9 @@
         <v>14624</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G100" s="4" t="n">
-        <v>14695.26</v>
-      </c>
-      <c r="H100" s="4" t="n">
         <v>151061</v>
       </c>
-      <c r="I100" s="5" t="inlineStr">
+      <c r="G100" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 3656.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -4032,15 +3426,9 @@
         <v>28644</v>
       </c>
       <c r="F101" s="8" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G101" s="8" t="n">
-        <v>675.2599999999984</v>
-      </c>
-      <c r="H101" s="8" t="n">
         <v>226849</v>
       </c>
-      <c r="I101" s="9" t="inlineStr">
+      <c r="G101" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 462.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -4067,15 +3455,9 @@
         <v>14800</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G102" s="4" t="n">
-        <v>14519.26</v>
-      </c>
-      <c r="H102" s="4" t="n">
         <v>268716</v>
       </c>
-      <c r="I102" s="5" t="inlineStr">
+      <c r="G102" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 3700.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -4102,15 +3484,9 @@
         <v>14640</v>
       </c>
       <c r="F103" s="8" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G103" s="8" t="n">
-        <v>14679.26</v>
-      </c>
-      <c r="H103" s="8" t="n">
         <v>269356</v>
       </c>
-      <c r="I103" s="9" t="inlineStr">
+      <c r="G103" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 3660.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -4137,15 +3513,9 @@
         <v>28600</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G104" s="4" t="n">
-        <v>719.2599999999984</v>
-      </c>
-      <c r="H104" s="4" t="n">
         <v>301926</v>
       </c>
-      <c r="I104" s="5" t="inlineStr">
+      <c r="G104" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 650.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -4172,15 +3542,9 @@
         <v>14116</v>
       </c>
       <c r="F105" s="8" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G105" s="8" t="n">
-        <v>15203.26</v>
-      </c>
-      <c r="H105" s="8" t="n">
         <v>359425</v>
       </c>
-      <c r="I105" s="9" t="inlineStr">
+      <c r="G105" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 3529.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -4207,15 +3571,9 @@
         <v>29100</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G106" s="4" t="n">
-        <v>219.2599999999984</v>
-      </c>
-      <c r="H106" s="4" t="n">
         <v>330325</v>
       </c>
-      <c r="I106" s="5" t="inlineStr">
+      <c r="G106" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 300.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -4242,15 +3600,9 @@
         <v>28600</v>
       </c>
       <c r="F107" s="8" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G107" s="8" t="n">
-        <v>719.2599999999984</v>
-      </c>
-      <c r="H107" s="8" t="n">
         <v>301725</v>
       </c>
-      <c r="I107" s="9" t="inlineStr">
+      <c r="G107" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 715.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -4277,15 +3629,9 @@
         <v>26915</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G108" s="4" t="n">
-        <v>2404.259999999998</v>
-      </c>
-      <c r="H108" s="4" t="n">
         <v>274810</v>
       </c>
-      <c r="I108" s="5" t="inlineStr">
+      <c r="G108" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 769.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -4312,15 +3658,9 @@
         <v>20250</v>
       </c>
       <c r="F109" s="8" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G109" s="8" t="n">
-        <v>9069.259999999998</v>
-      </c>
-      <c r="H109" s="8" t="n">
         <v>254560</v>
       </c>
-      <c r="I109" s="9" t="inlineStr">
+      <c r="G109" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 2250.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -4347,15 +3687,9 @@
         <v>28050</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G110" s="4" t="n">
-        <v>1269.259999999998</v>
-      </c>
-      <c r="H110" s="4" t="n">
         <v>226510</v>
       </c>
-      <c r="I110" s="5" t="inlineStr">
+      <c r="G110" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 425.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -4382,15 +3716,9 @@
         <v>28500</v>
       </c>
       <c r="F111" s="8" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G111" s="8" t="n">
-        <v>819.2599999999984</v>
-      </c>
-      <c r="H111" s="8" t="n">
         <v>198010</v>
       </c>
-      <c r="I111" s="9" t="inlineStr">
+      <c r="G111" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 500.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -4417,15 +3745,9 @@
         <v>22500</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G112" s="4" t="n">
-        <v>6819.259999999998</v>
-      </c>
-      <c r="H112" s="4" t="n">
         <v>175510</v>
       </c>
-      <c r="I112" s="5" t="inlineStr">
+      <c r="G112" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 2500.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -4452,15 +3774,9 @@
         <v>29898</v>
       </c>
       <c r="F113" s="8" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G113" s="8" t="n">
-        <v>-578.7400000000016</v>
-      </c>
-      <c r="H113" s="8" t="n">
         <v>145612</v>
       </c>
-      <c r="I113" s="9" t="inlineStr">
+      <c r="G113" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 3322.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -4487,15 +3803,9 @@
         <v>28896</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G114" s="4" t="n">
-        <v>423.2599999999984</v>
-      </c>
-      <c r="H114" s="4" t="n">
         <v>116716</v>
       </c>
-      <c r="I114" s="5" t="inlineStr">
+      <c r="G114" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 168.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -4522,15 +3832,9 @@
         <v>28210</v>
       </c>
       <c r="F115" s="8" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G115" s="8" t="n">
-        <v>1109.259999999998</v>
-      </c>
-      <c r="H115" s="8" t="n">
         <v>140472</v>
       </c>
-      <c r="I115" s="9" t="inlineStr">
+      <c r="G115" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1085.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -4557,15 +3861,9 @@
         <v>28896</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G116" s="4" t="n">
-        <v>423.2599999999984</v>
-      </c>
-      <c r="H116" s="4" t="n">
         <v>111576</v>
       </c>
-      <c r="I116" s="5" t="inlineStr">
+      <c r="G116" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 168.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -4592,15 +3890,9 @@
         <v>28917</v>
       </c>
       <c r="F117" s="8" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G117" s="8" t="n">
-        <v>402.2599999999984</v>
-      </c>
-      <c r="H117" s="8" t="n">
         <v>82659</v>
       </c>
-      <c r="I117" s="9" t="inlineStr">
+      <c r="G117" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 3213.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -4627,15 +3919,9 @@
         <v>28830</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G118" s="4" t="n">
-        <v>489.2599999999984</v>
-      </c>
-      <c r="H118" s="4" t="n">
         <v>53829</v>
       </c>
-      <c r="I118" s="5" t="inlineStr">
+      <c r="G118" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 465.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -4662,15 +3948,9 @@
         <v>28500</v>
       </c>
       <c r="F119" s="8" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G119" s="8" t="n">
-        <v>819.2599999999984</v>
-      </c>
-      <c r="H119" s="8" t="n">
         <v>25329</v>
       </c>
-      <c r="I119" s="9" t="inlineStr">
+      <c r="G119" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 500.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -4697,15 +3977,9 @@
         <v>27745</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G120" s="4" t="n">
-        <v>1574.259999999998</v>
-      </c>
-      <c r="H120" s="4" t="n">
         <v>-2416</v>
       </c>
-      <c r="I120" s="5" t="inlineStr">
+      <c r="G120" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 895.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -4732,15 +4006,9 @@
         <v>27776</v>
       </c>
       <c r="F121" s="8" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G121" s="8" t="n">
-        <v>1543.259999999998</v>
-      </c>
-      <c r="H121" s="8" t="n">
         <v>29704</v>
       </c>
-      <c r="I121" s="9" t="inlineStr">
+      <c r="G121" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 448.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -4767,15 +4035,9 @@
         <v>27040</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G122" s="4" t="n">
-        <v>2279.259999999998</v>
-      </c>
-      <c r="H122" s="4" t="n">
         <v>2664</v>
       </c>
-      <c r="I122" s="5" t="inlineStr">
+      <c r="G122" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 2080.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -4802,15 +4064,9 @@
         <v>28500</v>
       </c>
       <c r="F123" s="8" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G123" s="8" t="n">
-        <v>819.2599999999984</v>
-      </c>
-      <c r="H123" s="8" t="n">
         <v>-25836</v>
       </c>
-      <c r="I123" s="9" t="inlineStr">
+      <c r="G123" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 500.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -4837,15 +4093,9 @@
         <v>20223</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G124" s="4" t="n">
-        <v>9096.259999999998</v>
-      </c>
-      <c r="H124" s="4" t="n">
         <v>-46059</v>
       </c>
-      <c r="I124" s="5" t="inlineStr">
+      <c r="G124" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 2247.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -4872,15 +4122,9 @@
         <v>27759</v>
       </c>
       <c r="F125" s="8" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G125" s="8" t="n">
-        <v>1560.259999999998</v>
-      </c>
-      <c r="H125" s="8" t="n">
         <v>6909</v>
       </c>
-      <c r="I125" s="9" t="inlineStr">
+      <c r="G125" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 487.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -4907,15 +4151,9 @@
         <v>28314</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G126" s="4" t="n">
-        <v>1005.259999999998</v>
-      </c>
-      <c r="H126" s="4" t="n">
         <v>46227</v>
       </c>
-      <c r="I126" s="5" t="inlineStr">
+      <c r="G126" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 429.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -4942,15 +4180,9 @@
         <v>29230</v>
       </c>
       <c r="F127" s="8" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G127" s="8" t="n">
-        <v>89.2599999999984</v>
-      </c>
-      <c r="H127" s="8" t="n">
         <v>46637</v>
       </c>
-      <c r="I127" s="9" t="inlineStr">
+      <c r="G127" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 158.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -4977,15 +4209,9 @@
         <v>27702</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G128" s="4" t="n">
-        <v>1617.259999999998</v>
-      </c>
-      <c r="H128" s="4" t="n">
         <v>18935</v>
       </c>
-      <c r="I128" s="5" t="inlineStr">
+      <c r="G128" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 486.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -5012,15 +4238,9 @@
         <v>28796</v>
       </c>
       <c r="F129" s="8" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G129" s="8" t="n">
-        <v>523.2599999999984</v>
-      </c>
-      <c r="H129" s="8" t="n">
         <v>-9861</v>
       </c>
-      <c r="I129" s="9" t="inlineStr">
+      <c r="G129" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 313.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -5047,15 +4267,9 @@
         <v>28600</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G130" s="4" t="n">
-        <v>719.2599999999984</v>
-      </c>
-      <c r="H130" s="4" t="n">
         <v>-38461</v>
       </c>
-      <c r="I130" s="5" t="inlineStr">
+      <c r="G130" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 2200.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -5082,15 +4296,9 @@
         <v>29140</v>
       </c>
       <c r="F131" s="8" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G131" s="8" t="n">
-        <v>179.2599999999984</v>
-      </c>
-      <c r="H131" s="8" t="n">
         <v>-67601</v>
       </c>
-      <c r="I131" s="9" t="inlineStr">
+      <c r="G131" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 470.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -5117,15 +4325,9 @@
         <v>28842</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G132" s="4" t="n">
-        <v>477.2599999999984</v>
-      </c>
-      <c r="H132" s="4" t="n">
         <v>-96443</v>
       </c>
-      <c r="I132" s="5" t="inlineStr">
+      <c r="G132" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 506.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -5152,15 +4354,9 @@
         <v>29388</v>
       </c>
       <c r="F133" s="8" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G133" s="8" t="n">
-        <v>-68.7400000000016</v>
-      </c>
-      <c r="H133" s="8" t="n">
         <v>-125831</v>
       </c>
-      <c r="I133" s="9" t="inlineStr">
+      <c r="G133" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 474.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -5187,15 +4383,9 @@
         <v>25608</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G134" s="4" t="n">
-        <v>3711.259999999998</v>
-      </c>
-      <c r="H134" s="4" t="n">
         <v>-151439</v>
       </c>
-      <c r="I134" s="5" t="inlineStr">
+      <c r="G134" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1164.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -5222,15 +4412,9 @@
         <v>27900</v>
       </c>
       <c r="F135" s="8" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G135" s="8" t="n">
-        <v>1419.259999999998</v>
-      </c>
-      <c r="H135" s="8" t="n">
         <v>-179339</v>
       </c>
-      <c r="I135" s="9" t="inlineStr">
+      <c r="G135" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 900.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -5257,15 +4441,9 @@
         <v>28706</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G136" s="4" t="n">
-        <v>613.2599999999984</v>
-      </c>
-      <c r="H136" s="4" t="n">
         <v>-177417</v>
       </c>
-      <c r="I136" s="5" t="inlineStr">
+      <c r="G136" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 926.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -5292,15 +4470,9 @@
         <v>27900</v>
       </c>
       <c r="F137" s="8" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G137" s="8" t="n">
-        <v>1419.259999999998</v>
-      </c>
-      <c r="H137" s="8" t="n">
         <v>-205317</v>
       </c>
-      <c r="I137" s="9" t="inlineStr">
+      <c r="G137" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 3100.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -5327,15 +4499,9 @@
         <v>28842</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>29319.26</v>
-      </c>
-      <c r="G138" s="4" t="n">
-        <v>477.2599999999984</v>
-      </c>
-      <c r="H138" s="4" t="n">
         <v>-89170</v>
       </c>
-      <c r="I138" s="5" t="inlineStr">
+      <c r="G138" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 437.00) (scaled by 4.40x to fit Rs. 1.5M target)</t>
         </is>
@@ -5362,15 +4528,9 @@
         <v>29348</v>
       </c>
       <c r="F139" s="8" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G139" s="8" t="n">
-        <v>3166.349999999999</v>
-      </c>
-      <c r="H139" s="8" t="n">
         <v>202892</v>
       </c>
-      <c r="I139" s="9" t="inlineStr">
+      <c r="G139" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 667.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -5397,15 +4557,9 @@
         <v>26920</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G140" s="4" t="n">
-        <v>5594.349999999999</v>
-      </c>
-      <c r="H140" s="4" t="n">
         <v>208224</v>
       </c>
-      <c r="I140" s="5" t="inlineStr">
+      <c r="G140" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 2692.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -5432,15 +4586,9 @@
         <v>28540</v>
       </c>
       <c r="F141" s="8" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G141" s="8" t="n">
-        <v>3974.349999999999</v>
-      </c>
-      <c r="H141" s="8" t="n">
         <v>179684</v>
       </c>
-      <c r="I141" s="9" t="inlineStr">
+      <c r="G141" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 2854.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -5467,15 +4615,9 @@
         <v>30771</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G142" s="4" t="n">
-        <v>1743.349999999999</v>
-      </c>
-      <c r="H142" s="4" t="n">
         <v>177453</v>
       </c>
-      <c r="I142" s="5" t="inlineStr">
+      <c r="G142" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 789.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -5502,15 +4644,9 @@
         <v>32047</v>
       </c>
       <c r="F143" s="8" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G143" s="8" t="n">
-        <v>467.3499999999985</v>
-      </c>
-      <c r="H143" s="8" t="n">
         <v>145406</v>
       </c>
-      <c r="I143" s="9" t="inlineStr">
+      <c r="G143" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 439.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -5537,15 +4673,9 @@
         <v>31892</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G144" s="4" t="n">
-        <v>622.3499999999985</v>
-      </c>
-      <c r="H144" s="4" t="n">
         <v>113514</v>
       </c>
-      <c r="I144" s="5" t="inlineStr">
+      <c r="G144" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 469.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -5572,15 +4702,9 @@
         <v>32130</v>
       </c>
       <c r="F145" s="8" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G145" s="8" t="n">
-        <v>384.3499999999985</v>
-      </c>
-      <c r="H145" s="8" t="n">
         <v>81384</v>
       </c>
-      <c r="I145" s="9" t="inlineStr">
+      <c r="G145" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 315.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -5607,15 +4731,9 @@
         <v>22300</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G146" s="4" t="n">
-        <v>10214.35</v>
-      </c>
-      <c r="H146" s="4" t="n">
         <v>59084</v>
       </c>
-      <c r="I146" s="5" t="inlineStr">
+      <c r="G146" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 4460.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -5642,15 +4760,9 @@
         <v>28920</v>
       </c>
       <c r="F147" s="8" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G147" s="8" t="n">
-        <v>3594.349999999999</v>
-      </c>
-      <c r="H147" s="8" t="n">
         <v>30164</v>
       </c>
-      <c r="I147" s="9" t="inlineStr">
+      <c r="G147" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1205.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -5677,15 +4789,9 @@
         <v>31556</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G148" s="4" t="n">
-        <v>958.3499999999985</v>
-      </c>
-      <c r="H148" s="4" t="n">
         <v>-1392</v>
       </c>
-      <c r="I148" s="5" t="inlineStr">
+      <c r="G148" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 322.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -5712,15 +4818,9 @@
         <v>29240</v>
       </c>
       <c r="F149" s="8" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G149" s="8" t="n">
-        <v>3274.349999999999</v>
-      </c>
-      <c r="H149" s="8" t="n">
         <v>-30632</v>
       </c>
-      <c r="I149" s="9" t="inlineStr">
+      <c r="G149" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 860.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -5747,15 +4847,9 @@
         <v>31816</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G150" s="4" t="n">
-        <v>698.3499999999985</v>
-      </c>
-      <c r="H150" s="4" t="n">
         <v>-62448</v>
       </c>
-      <c r="I150" s="5" t="inlineStr">
+      <c r="G150" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 164.00) (scaled by 4.88x to fit Rs. 1.5M target) (Qty adjusted by -1 to hit exact 1.5M target)</t>
         </is>
@@ -5782,15 +4876,9 @@
         <v>32232</v>
       </c>
       <c r="F151" s="8" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G151" s="8" t="n">
-        <v>282.3499999999985</v>
-      </c>
-      <c r="H151" s="8" t="n">
         <v>-94680</v>
       </c>
-      <c r="I151" s="9" t="inlineStr">
+      <c r="G151" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 474.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -5817,15 +4905,9 @@
         <v>30186</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G152" s="4" t="n">
-        <v>2328.349999999999</v>
-      </c>
-      <c r="H152" s="4" t="n">
         <v>-124866</v>
       </c>
-      <c r="I152" s="5" t="inlineStr">
+      <c r="G152" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 559.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -5852,15 +4934,9 @@
         <v>30396</v>
       </c>
       <c r="F153" s="8" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G153" s="8" t="n">
-        <v>2118.349999999999</v>
-      </c>
-      <c r="H153" s="8" t="n">
         <v>-155262</v>
       </c>
-      <c r="I153" s="9" t="inlineStr">
+      <c r="G153" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 447.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -5887,15 +4963,9 @@
         <v>30700</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G154" s="4" t="n">
-        <v>1814.349999999999</v>
-      </c>
-      <c r="H154" s="4" t="n">
         <v>-185962</v>
       </c>
-      <c r="I154" s="5" t="inlineStr">
+      <c r="G154" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1535.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -5922,15 +4992,9 @@
         <v>32155</v>
       </c>
       <c r="F155" s="8" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G155" s="8" t="n">
-        <v>359.3499999999985</v>
-      </c>
-      <c r="H155" s="8" t="n">
         <v>-218117</v>
       </c>
-      <c r="I155" s="9" t="inlineStr">
+      <c r="G155" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 545.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -5957,15 +5021,9 @@
         <v>31460</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G156" s="4" t="n">
-        <v>1054.349999999999</v>
-      </c>
-      <c r="H156" s="4" t="n">
         <v>-249577</v>
       </c>
-      <c r="I156" s="5" t="inlineStr">
+      <c r="G156" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 715.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -5992,15 +5050,9 @@
         <v>27624</v>
       </c>
       <c r="F157" s="8" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G157" s="8" t="n">
-        <v>4890.349999999999</v>
-      </c>
-      <c r="H157" s="8" t="n">
         <v>-277201</v>
       </c>
-      <c r="I157" s="9" t="inlineStr">
+      <c r="G157" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1151.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -6027,15 +5079,9 @@
         <v>30984</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G158" s="4" t="n">
-        <v>1530.349999999999</v>
-      </c>
-      <c r="H158" s="4" t="n">
         <v>-18539</v>
       </c>
-      <c r="I158" s="5" t="inlineStr">
+      <c r="G158" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1291.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -6062,15 +5108,9 @@
         <v>28400</v>
       </c>
       <c r="F159" s="8" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G159" s="8" t="n">
-        <v>4114.349999999999</v>
-      </c>
-      <c r="H159" s="8" t="n">
         <v>-46939</v>
       </c>
-      <c r="I159" s="9" t="inlineStr">
+      <c r="G159" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1420.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -6097,15 +5137,9 @@
         <v>32155</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G160" s="4" t="n">
-        <v>359.3499999999985</v>
-      </c>
-      <c r="H160" s="4" t="n">
         <v>311624</v>
       </c>
-      <c r="I160" s="5" t="inlineStr">
+      <c r="G160" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 545.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -6132,15 +5166,9 @@
         <v>32178</v>
       </c>
       <c r="F161" s="8" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G161" s="8" t="n">
-        <v>336.3499999999985</v>
-      </c>
-      <c r="H161" s="8" t="n">
         <v>279446</v>
       </c>
-      <c r="I161" s="9" t="inlineStr">
+      <c r="G161" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 346.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -6167,15 +5195,9 @@
         <v>32364</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G162" s="4" t="n">
-        <v>150.3499999999985</v>
-      </c>
-      <c r="H162" s="4" t="n">
         <v>247082</v>
       </c>
-      <c r="I162" s="5" t="inlineStr">
+      <c r="G162" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 174.00) (scaled by 4.88x to fit Rs. 1.5M target) (Qty adjusted by 1 to hit exact 1.5M target)</t>
         </is>
@@ -6202,15 +5224,9 @@
         <v>23400</v>
       </c>
       <c r="F163" s="8" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G163" s="8" t="n">
-        <v>9114.349999999999</v>
-      </c>
-      <c r="H163" s="8" t="n">
         <v>223682</v>
       </c>
-      <c r="I163" s="9" t="inlineStr">
+      <c r="G163" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 2340.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -6237,15 +5253,9 @@
         <v>30131</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G164" s="4" t="n">
-        <v>2383.349999999999</v>
-      </c>
-      <c r="H164" s="4" t="n">
         <v>193551</v>
       </c>
-      <c r="I164" s="5" t="inlineStr">
+      <c r="G164" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1039.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -6272,15 +5282,9 @@
         <v>30625</v>
       </c>
       <c r="F165" s="8" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G165" s="8" t="n">
-        <v>1889.349999999999</v>
-      </c>
-      <c r="H165" s="8" t="n">
         <v>162926</v>
       </c>
-      <c r="I165" s="9" t="inlineStr">
+      <c r="G165" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 625.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -6307,15 +5311,9 @@
         <v>30503</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G166" s="4" t="n">
-        <v>2011.349999999999</v>
-      </c>
-      <c r="H166" s="4" t="n">
         <v>164077</v>
       </c>
-      <c r="I166" s="5" t="inlineStr">
+      <c r="G166" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 517.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -6342,15 +5340,9 @@
         <v>26940</v>
       </c>
       <c r="F167" s="8" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G167" s="8" t="n">
-        <v>5574.349999999999</v>
-      </c>
-      <c r="H167" s="8" t="n">
         <v>137137</v>
       </c>
-      <c r="I167" s="9" t="inlineStr">
+      <c r="G167" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 2694.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -6377,15 +5369,9 @@
         <v>31044</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G168" s="4" t="n">
-        <v>1470.349999999999</v>
-      </c>
-      <c r="H168" s="4" t="n">
         <v>106093</v>
       </c>
-      <c r="I168" s="5" t="inlineStr">
+      <c r="G168" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 398.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -6412,15 +5398,9 @@
         <v>32450</v>
       </c>
       <c r="F169" s="8" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G169" s="8" t="n">
-        <v>64.34999999999854</v>
-      </c>
-      <c r="H169" s="8" t="n">
         <v>73643</v>
       </c>
-      <c r="I169" s="9" t="inlineStr">
+      <c r="G169" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 550.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -6447,15 +5427,9 @@
         <v>30674</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G170" s="4" t="n">
-        <v>1840.349999999999</v>
-      </c>
-      <c r="H170" s="4" t="n">
         <v>42969</v>
       </c>
-      <c r="I170" s="5" t="inlineStr">
+      <c r="G170" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 626.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -6482,15 +5456,9 @@
         <v>31010</v>
       </c>
       <c r="F171" s="8" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G171" s="8" t="n">
-        <v>1504.349999999999</v>
-      </c>
-      <c r="H171" s="8" t="n">
         <v>11959</v>
       </c>
-      <c r="I171" s="9" t="inlineStr">
+      <c r="G171" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 3101.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -6517,15 +5485,9 @@
         <v>32296</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G172" s="4" t="n">
-        <v>218.3499999999985</v>
-      </c>
-      <c r="H172" s="4" t="n">
         <v>-20337</v>
       </c>
-      <c r="I172" s="5" t="inlineStr">
+      <c r="G172" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 367.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -6552,15 +5514,9 @@
         <v>29480</v>
       </c>
       <c r="F173" s="8" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G173" s="8" t="n">
-        <v>3034.349999999999</v>
-      </c>
-      <c r="H173" s="8" t="n">
         <v>-18417</v>
       </c>
-      <c r="I173" s="9" t="inlineStr">
+      <c r="G173" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 670.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -6587,15 +5543,9 @@
         <v>30240</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G174" s="4" t="n">
-        <v>2274.349999999999</v>
-      </c>
-      <c r="H174" s="4" t="n">
         <v>-48657</v>
       </c>
-      <c r="I174" s="5" t="inlineStr">
+      <c r="G174" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 560.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -6622,15 +5572,9 @@
         <v>31000</v>
       </c>
       <c r="F175" s="8" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G175" s="8" t="n">
-        <v>1514.349999999999</v>
-      </c>
-      <c r="H175" s="8" t="n">
         <v>-79657</v>
       </c>
-      <c r="I175" s="9" t="inlineStr">
+      <c r="G175" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 3100.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -6657,15 +5601,9 @@
         <v>30480</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G176" s="4" t="n">
-        <v>2034.349999999999</v>
-      </c>
-      <c r="H176" s="4" t="n">
         <v>-110137</v>
       </c>
-      <c r="I176" s="5" t="inlineStr">
+      <c r="G176" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1270.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -6692,15 +5630,9 @@
         <v>32266</v>
       </c>
       <c r="F177" s="8" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G177" s="8" t="n">
-        <v>248.3499999999985</v>
-      </c>
-      <c r="H177" s="8" t="n">
         <v>-142403</v>
       </c>
-      <c r="I177" s="9" t="inlineStr">
+      <c r="G177" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 442.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -6727,15 +5659,9 @@
         <v>31580</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G178" s="4" t="n">
-        <v>934.3499999999985</v>
-      </c>
-      <c r="H178" s="4" t="n">
         <v>-173983</v>
       </c>
-      <c r="I178" s="5" t="inlineStr">
+      <c r="G178" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1579.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -6762,15 +5688,9 @@
         <v>18980</v>
       </c>
       <c r="F179" s="8" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G179" s="8" t="n">
-        <v>13534.35</v>
-      </c>
-      <c r="H179" s="8" t="n">
         <v>-160463</v>
       </c>
-      <c r="I179" s="9" t="inlineStr">
+      <c r="G179" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 3796.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -6797,15 +5717,9 @@
         <v>28739</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G180" s="4" t="n">
-        <v>3775.349999999999</v>
-      </c>
-      <c r="H180" s="4" t="n">
         <v>-106787</v>
       </c>
-      <c r="I180" s="5" t="inlineStr">
+      <c r="G180" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 991.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -6832,15 +5746,9 @@
         <v>29435</v>
       </c>
       <c r="F181" s="8" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G181" s="8" t="n">
-        <v>3079.349999999999</v>
-      </c>
-      <c r="H181" s="8" t="n">
         <v>-71733</v>
       </c>
-      <c r="I181" s="9" t="inlineStr">
+      <c r="G181" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1015.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -6867,15 +5775,9 @@
         <v>30660</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G182" s="4" t="n">
-        <v>1854.349999999999</v>
-      </c>
-      <c r="H182" s="4" t="n">
         <v>125093</v>
       </c>
-      <c r="I182" s="5" t="inlineStr">
+      <c r="G182" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1533.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -6902,15 +5804,9 @@
         <v>30000</v>
       </c>
       <c r="F183" s="8" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G183" s="8" t="n">
-        <v>2514.349999999999</v>
-      </c>
-      <c r="H183" s="8" t="n">
         <v>95093</v>
       </c>
-      <c r="I183" s="9" t="inlineStr">
+      <c r="G183" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1500.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -6937,15 +5833,9 @@
         <v>30240</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G184" s="4" t="n">
-        <v>2274.349999999999</v>
-      </c>
-      <c r="H184" s="4" t="n">
         <v>127733</v>
       </c>
-      <c r="I184" s="5" t="inlineStr">
+      <c r="G184" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 480.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -6972,15 +5862,9 @@
         <v>31605</v>
       </c>
       <c r="F185" s="8" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G185" s="8" t="n">
-        <v>909.3499999999985</v>
-      </c>
-      <c r="H185" s="8" t="n">
         <v>96128</v>
       </c>
-      <c r="I185" s="9" t="inlineStr">
+      <c r="G185" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 645.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -7007,15 +5891,9 @@
         <v>31752</v>
       </c>
       <c r="F186" s="4" t="n">
-        <v>32514.35</v>
-      </c>
-      <c r="G186" s="4" t="n">
-        <v>762.3499999999985</v>
-      </c>
-      <c r="H186" s="4" t="n">
         <v>95876</v>
       </c>
-      <c r="I186" s="5" t="inlineStr">
+      <c r="G186" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 504.00) (scaled by 4.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -7042,15 +5920,9 @@
         <v>21264</v>
       </c>
       <c r="F187" s="8" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G187" s="8" t="n">
-        <v>17967.57</v>
-      </c>
-      <c r="H187" s="8" t="n">
         <v>269540</v>
       </c>
-      <c r="I187" s="9" t="inlineStr">
+      <c r="G187" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 3544.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -7077,15 +5949,9 @@
         <v>22524</v>
       </c>
       <c r="F188" s="4" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G188" s="4" t="n">
-        <v>16707.57</v>
-      </c>
-      <c r="H188" s="4" t="n">
         <v>247016</v>
       </c>
-      <c r="I188" s="5" t="inlineStr">
+      <c r="G188" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 3754.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -7112,15 +5978,9 @@
         <v>37312</v>
       </c>
       <c r="F189" s="8" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G189" s="8" t="n">
-        <v>1919.57</v>
-      </c>
-      <c r="H189" s="8" t="n">
         <v>373152</v>
       </c>
-      <c r="I189" s="9" t="inlineStr">
+      <c r="G189" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 352.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -7147,15 +6007,9 @@
         <v>37153</v>
       </c>
       <c r="F190" s="4" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G190" s="4" t="n">
-        <v>2078.57</v>
-      </c>
-      <c r="H190" s="4" t="n">
         <v>335999</v>
       </c>
-      <c r="I190" s="5" t="inlineStr">
+      <c r="G190" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 701.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -7182,15 +6036,9 @@
         <v>20340</v>
       </c>
       <c r="F191" s="8" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G191" s="8" t="n">
-        <v>18891.57</v>
-      </c>
-      <c r="H191" s="8" t="n">
         <v>355621</v>
       </c>
-      <c r="I191" s="9" t="inlineStr">
+      <c r="G191" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 3390.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -7217,15 +6065,9 @@
         <v>20742</v>
       </c>
       <c r="F192" s="4" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G192" s="4" t="n">
-        <v>18489.57</v>
-      </c>
-      <c r="H192" s="4" t="n">
         <v>334879</v>
       </c>
-      <c r="I192" s="5" t="inlineStr">
+      <c r="G192" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 3457.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -7252,15 +6094,9 @@
         <v>36465</v>
       </c>
       <c r="F193" s="8" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G193" s="8" t="n">
-        <v>2766.57</v>
-      </c>
-      <c r="H193" s="8" t="n">
         <v>340456</v>
       </c>
-      <c r="I193" s="9" t="inlineStr">
+      <c r="G193" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 561.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -7287,15 +6123,9 @@
         <v>38350</v>
       </c>
       <c r="F194" s="4" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G194" s="4" t="n">
-        <v>881.5699999999997</v>
-      </c>
-      <c r="H194" s="4" t="n">
         <v>302106</v>
       </c>
-      <c r="I194" s="5" t="inlineStr">
+      <c r="G194" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 590.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -7322,15 +6152,9 @@
         <v>38527</v>
       </c>
       <c r="F195" s="8" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G195" s="8" t="n">
-        <v>704.5699999999997</v>
-      </c>
-      <c r="H195" s="8" t="n">
         <v>301929</v>
       </c>
-      <c r="I195" s="9" t="inlineStr">
+      <c r="G195" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 653.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -7357,15 +6181,9 @@
         <v>36676</v>
       </c>
       <c r="F196" s="4" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G196" s="4" t="n">
-        <v>2555.57</v>
-      </c>
-      <c r="H196" s="4" t="n">
         <v>265253</v>
       </c>
-      <c r="I196" s="5" t="inlineStr">
+      <c r="G196" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 692.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -7392,15 +6210,9 @@
         <v>38940</v>
       </c>
       <c r="F197" s="8" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G197" s="8" t="n">
-        <v>291.5699999999997</v>
-      </c>
-      <c r="H197" s="8" t="n">
         <v>527418</v>
       </c>
-      <c r="I197" s="9" t="inlineStr">
+      <c r="G197" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 660.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -7427,15 +6239,9 @@
         <v>38400</v>
       </c>
       <c r="F198" s="4" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G198" s="4" t="n">
-        <v>831.5699999999997</v>
-      </c>
-      <c r="H198" s="4" t="n">
         <v>529374</v>
       </c>
-      <c r="I198" s="5" t="inlineStr">
+      <c r="G198" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 3200.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -7462,15 +6268,9 @@
         <v>35910</v>
       </c>
       <c r="F199" s="8" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G199" s="8" t="n">
-        <v>3321.57</v>
-      </c>
-      <c r="H199" s="8" t="n">
         <v>532284</v>
       </c>
-      <c r="I199" s="9" t="inlineStr">
+      <c r="G199" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1995.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -7497,15 +6297,9 @@
         <v>37980</v>
       </c>
       <c r="F200" s="4" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G200" s="4" t="n">
-        <v>1251.57</v>
-      </c>
-      <c r="H200" s="4" t="n">
         <v>494304</v>
       </c>
-      <c r="I200" s="5" t="inlineStr">
+      <c r="G200" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 3165.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -7532,15 +6326,9 @@
         <v>38940</v>
       </c>
       <c r="F201" s="8" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G201" s="8" t="n">
-        <v>291.5699999999997</v>
-      </c>
-      <c r="H201" s="8" t="n">
         <v>455364</v>
       </c>
-      <c r="I201" s="9" t="inlineStr">
+      <c r="G201" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 330.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -7567,15 +6355,9 @@
         <v>38192</v>
       </c>
       <c r="F202" s="4" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G202" s="4" t="n">
-        <v>1039.57</v>
-      </c>
-      <c r="H202" s="4" t="n">
         <v>417172</v>
       </c>
-      <c r="I202" s="5" t="inlineStr">
+      <c r="G202" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 176.00) (scaled by 5.88x to fit Rs. 1.5M target) (Qty adjusted by -1 to hit exact 1.5M target)</t>
         </is>
@@ -7602,15 +6384,9 @@
         <v>38963</v>
       </c>
       <c r="F203" s="8" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G203" s="8" t="n">
-        <v>268.5699999999997</v>
-      </c>
-      <c r="H203" s="8" t="n">
         <v>454829</v>
       </c>
-      <c r="I203" s="9" t="inlineStr">
+      <c r="G203" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 829.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -7637,15 +6413,9 @@
         <v>37680</v>
       </c>
       <c r="F204" s="4" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G204" s="4" t="n">
-        <v>1551.57</v>
-      </c>
-      <c r="H204" s="4" t="n">
         <v>417149</v>
       </c>
-      <c r="I204" s="5" t="inlineStr">
+      <c r="G204" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1570.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -7672,15 +6442,9 @@
         <v>36226</v>
       </c>
       <c r="F205" s="8" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G205" s="8" t="n">
-        <v>3005.57</v>
-      </c>
-      <c r="H205" s="8" t="n">
         <v>380923</v>
       </c>
-      <c r="I205" s="9" t="inlineStr">
+      <c r="G205" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 614.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -7707,15 +6471,9 @@
         <v>32544</v>
       </c>
       <c r="F206" s="4" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G206" s="4" t="n">
-        <v>6687.57</v>
-      </c>
-      <c r="H206" s="4" t="n">
         <v>348379</v>
       </c>
-      <c r="I206" s="5" t="inlineStr">
+      <c r="G206" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1808.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -7742,15 +6500,9 @@
         <v>36941</v>
       </c>
       <c r="F207" s="8" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G207" s="8" t="n">
-        <v>2290.57</v>
-      </c>
-      <c r="H207" s="8" t="n">
         <v>311438</v>
       </c>
-      <c r="I207" s="9" t="inlineStr">
+      <c r="G207" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 697.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -7777,15 +6529,9 @@
         <v>35178</v>
       </c>
       <c r="F208" s="4" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G208" s="4" t="n">
-        <v>4053.57</v>
-      </c>
-      <c r="H208" s="4" t="n">
         <v>276260</v>
       </c>
-      <c r="I208" s="5" t="inlineStr">
+      <c r="G208" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 858.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -7812,15 +6558,9 @@
         <v>34771</v>
       </c>
       <c r="F209" s="8" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G209" s="8" t="n">
-        <v>4460.57</v>
-      </c>
-      <c r="H209" s="8" t="n">
         <v>241489</v>
       </c>
-      <c r="I209" s="9" t="inlineStr">
+      <c r="G209" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1199.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -7847,15 +6587,9 @@
         <v>35550</v>
       </c>
       <c r="F210" s="4" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G210" s="4" t="n">
-        <v>3681.57</v>
-      </c>
-      <c r="H210" s="4" t="n">
         <v>205939</v>
       </c>
-      <c r="I210" s="5" t="inlineStr">
+      <c r="G210" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1975.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -7882,15 +6616,9 @@
         <v>38822</v>
       </c>
       <c r="F211" s="8" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G211" s="8" t="n">
-        <v>409.5699999999997</v>
-      </c>
-      <c r="H211" s="8" t="n">
         <v>214605</v>
       </c>
-      <c r="I211" s="9" t="inlineStr">
+      <c r="G211" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 658.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -7917,15 +6645,9 @@
         <v>34560</v>
       </c>
       <c r="F212" s="4" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G212" s="4" t="n">
-        <v>4671.57</v>
-      </c>
-      <c r="H212" s="4" t="n">
         <v>257209</v>
       </c>
-      <c r="I212" s="5" t="inlineStr">
+      <c r="G212" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 2880.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -7952,15 +6674,9 @@
         <v>39102</v>
       </c>
       <c r="F213" s="8" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G213" s="8" t="n">
-        <v>129.5699999999997</v>
-      </c>
-      <c r="H213" s="8" t="n">
         <v>254474</v>
       </c>
-      <c r="I213" s="9" t="inlineStr">
+      <c r="G213" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 266.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -7987,15 +6703,9 @@
         <v>35767</v>
       </c>
       <c r="F214" s="4" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G214" s="4" t="n">
-        <v>3464.57</v>
-      </c>
-      <c r="H214" s="4" t="n">
         <v>218707</v>
       </c>
-      <c r="I214" s="5" t="inlineStr">
+      <c r="G214" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 761.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -8022,15 +6732,9 @@
         <v>33792</v>
       </c>
       <c r="F215" s="8" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G215" s="8" t="n">
-        <v>5439.57</v>
-      </c>
-      <c r="H215" s="8" t="n">
         <v>184915</v>
       </c>
-      <c r="I215" s="9" t="inlineStr">
+      <c r="G215" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1408.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -8057,15 +6761,9 @@
         <v>38319</v>
       </c>
       <c r="F216" s="4" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G216" s="4" t="n">
-        <v>912.5699999999997</v>
-      </c>
-      <c r="H216" s="4" t="n">
         <v>182578</v>
       </c>
-      <c r="I216" s="5" t="inlineStr">
+      <c r="G216" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 723.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -8092,15 +6790,9 @@
         <v>38291</v>
       </c>
       <c r="F217" s="8" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G217" s="8" t="n">
-        <v>940.5699999999997</v>
-      </c>
-      <c r="H217" s="8" t="n">
         <v>144287</v>
       </c>
-      <c r="I217" s="9" t="inlineStr">
+      <c r="G217" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 649.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -8127,15 +6819,9 @@
         <v>37966</v>
       </c>
       <c r="F218" s="4" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G218" s="4" t="n">
-        <v>1265.57</v>
-      </c>
-      <c r="H218" s="4" t="n">
         <v>106321</v>
       </c>
-      <c r="I218" s="5" t="inlineStr">
+      <c r="G218" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 463.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -8162,15 +6848,9 @@
         <v>26880</v>
       </c>
       <c r="F219" s="8" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G219" s="8" t="n">
-        <v>12351.57</v>
-      </c>
-      <c r="H219" s="8" t="n">
         <v>79441</v>
       </c>
-      <c r="I219" s="9" t="inlineStr">
+      <c r="G219" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 4480.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -8197,15 +6877,9 @@
         <v>34162</v>
       </c>
       <c r="F220" s="4" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G220" s="4" t="n">
-        <v>5069.57</v>
-      </c>
-      <c r="H220" s="4" t="n">
         <v>45279</v>
       </c>
-      <c r="I220" s="5" t="inlineStr">
+      <c r="G220" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1178.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -8232,15 +6906,9 @@
         <v>30258</v>
       </c>
       <c r="F221" s="8" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G221" s="8" t="n">
-        <v>8973.57</v>
-      </c>
-      <c r="H221" s="8" t="n">
         <v>15021</v>
       </c>
-      <c r="I221" s="9" t="inlineStr">
+      <c r="G221" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1681.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -8267,15 +6935,9 @@
         <v>38478</v>
       </c>
       <c r="F222" s="4" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G222" s="4" t="n">
-        <v>753.5699999999997</v>
-      </c>
-      <c r="H222" s="4" t="n">
         <v>-23457</v>
       </c>
-      <c r="I222" s="5" t="inlineStr">
+      <c r="G222" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 363.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -8302,15 +6964,9 @@
         <v>26580</v>
       </c>
       <c r="F223" s="8" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G223" s="8" t="n">
-        <v>12651.57</v>
-      </c>
-      <c r="H223" s="8" t="n">
         <v>19721</v>
       </c>
-      <c r="I223" s="9" t="inlineStr">
+      <c r="G223" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 4430.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -8337,15 +6993,9 @@
         <v>37440</v>
       </c>
       <c r="F224" s="4" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G224" s="4" t="n">
-        <v>1791.57</v>
-      </c>
-      <c r="H224" s="4" t="n">
         <v>-17719</v>
       </c>
-      <c r="I224" s="5" t="inlineStr">
+      <c r="G224" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 3120.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -8372,15 +7022,9 @@
         <v>21168</v>
       </c>
       <c r="F225" s="8" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G225" s="8" t="n">
-        <v>18063.57</v>
-      </c>
-      <c r="H225" s="8" t="n">
         <v>-38887</v>
       </c>
-      <c r="I225" s="9" t="inlineStr">
+      <c r="G225" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 3528.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -8407,15 +7051,9 @@
         <v>33300</v>
       </c>
       <c r="F226" s="4" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G226" s="4" t="n">
-        <v>5931.57</v>
-      </c>
-      <c r="H226" s="4" t="n">
         <v>-72187</v>
       </c>
-      <c r="I226" s="5" t="inlineStr">
+      <c r="G226" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1850.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -8442,15 +7080,9 @@
         <v>33660</v>
       </c>
       <c r="F227" s="8" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G227" s="8" t="n">
-        <v>5571.57</v>
-      </c>
-      <c r="H227" s="8" t="n">
         <v>-105847</v>
       </c>
-      <c r="I227" s="9" t="inlineStr">
+      <c r="G227" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1870.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -8477,15 +7109,9 @@
         <v>39360</v>
       </c>
       <c r="F228" s="4" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G228" s="4" t="n">
-        <v>-128.4300000000003</v>
-      </c>
-      <c r="H228" s="4" t="n">
         <v>-111547</v>
       </c>
-      <c r="I228" s="5" t="inlineStr">
+      <c r="G228" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1640.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -8512,15 +7138,9 @@
         <v>37600</v>
       </c>
       <c r="F229" s="8" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G229" s="8" t="n">
-        <v>1631.57</v>
-      </c>
-      <c r="H229" s="8" t="n">
         <v>-149147</v>
       </c>
-      <c r="I229" s="9" t="inlineStr">
+      <c r="G229" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 400.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -8547,15 +7167,9 @@
         <v>20436</v>
       </c>
       <c r="F230" s="4" t="n">
-        <v>39231.57</v>
-      </c>
-      <c r="G230" s="4" t="n">
-        <v>18795.57</v>
-      </c>
-      <c r="H230" s="4" t="n">
         <v>-169583</v>
       </c>
-      <c r="I230" s="5" t="inlineStr">
+      <c r="G230" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 3406.00) (scaled by 5.88x to fit Rs. 1.5M target)</t>
         </is>
@@ -8582,15 +7196,9 @@
         <v>48450</v>
       </c>
       <c r="F231" s="8" t="n">
-        <v>49155.2</v>
-      </c>
-      <c r="G231" s="8" t="n">
-        <v>705.1999999999971</v>
-      </c>
-      <c r="H231" s="8" t="n">
         <v>-178553</v>
       </c>
-      <c r="I231" s="9" t="inlineStr">
+      <c r="G231" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 285.00) (scaled by 7.37x to fit Rs. 1.5M target)</t>
         </is>
@@ -8617,15 +7225,9 @@
         <v>48750</v>
       </c>
       <c r="F232" s="4" t="n">
-        <v>49155.2</v>
-      </c>
-      <c r="G232" s="4" t="n">
-        <v>405.1999999999971</v>
-      </c>
-      <c r="H232" s="4" t="n">
         <v>-227303</v>
       </c>
-      <c r="I232" s="5" t="inlineStr">
+      <c r="G232" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 390.00) (scaled by 7.37x to fit Rs. 1.5M target)</t>
         </is>
@@ -8652,15 +7254,9 @@
         <v>48576</v>
       </c>
       <c r="F233" s="8" t="n">
-        <v>49155.2</v>
-      </c>
-      <c r="G233" s="8" t="n">
-        <v>579.1999999999971</v>
-      </c>
-      <c r="H233" s="8" t="n">
         <v>-275879</v>
       </c>
-      <c r="I233" s="9" t="inlineStr">
+      <c r="G233" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 506.00) (scaled by 7.37x to fit Rs. 1.5M target)</t>
         </is>
@@ -8687,15 +7283,9 @@
         <v>47180</v>
       </c>
       <c r="F234" s="4" t="n">
-        <v>49155.2</v>
-      </c>
-      <c r="G234" s="4" t="n">
-        <v>1975.199999999997</v>
-      </c>
-      <c r="H234" s="4" t="n">
         <v>-220554</v>
       </c>
-      <c r="I234" s="5" t="inlineStr">
+      <c r="G234" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 337.00) (scaled by 7.37x to fit Rs. 1.5M target)</t>
         </is>
@@ -8722,15 +7312,9 @@
         <v>47520</v>
       </c>
       <c r="F235" s="8" t="n">
-        <v>49155.2</v>
-      </c>
-      <c r="G235" s="8" t="n">
-        <v>1635.199999999997</v>
-      </c>
-      <c r="H235" s="8" t="n">
         <v>-268074</v>
       </c>
-      <c r="I235" s="9" t="inlineStr">
+      <c r="G235" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 495.00) (scaled by 7.37x to fit Rs. 1.5M target)</t>
         </is>
@@ -8757,15 +7341,9 @@
         <v>48657</v>
       </c>
       <c r="F236" s="4" t="n">
-        <v>49155.2</v>
-      </c>
-      <c r="G236" s="4" t="n">
-        <v>498.1999999999971</v>
-      </c>
-      <c r="H236" s="4" t="n">
         <v>-266523</v>
       </c>
-      <c r="I236" s="5" t="inlineStr">
+      <c r="G236" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 331.00) (scaled by 7.37x to fit Rs. 1.5M target)</t>
         </is>
@@ -8792,15 +7370,9 @@
         <v>47040</v>
       </c>
       <c r="F237" s="8" t="n">
-        <v>49155.2</v>
-      </c>
-      <c r="G237" s="8" t="n">
-        <v>2115.199999999997</v>
-      </c>
-      <c r="H237" s="8" t="n">
         <v>-9197</v>
       </c>
-      <c r="I237" s="9" t="inlineStr">
+      <c r="G237" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 320.00) (scaled by 7.37x to fit Rs. 1.5M target)</t>
         </is>
@@ -8827,15 +7399,9 @@
         <v>47760</v>
       </c>
       <c r="F238" s="4" t="n">
-        <v>49155.2</v>
-      </c>
-      <c r="G238" s="4" t="n">
-        <v>1395.199999999997</v>
-      </c>
-      <c r="H238" s="4" t="n">
         <v>-56957</v>
       </c>
-      <c r="I238" s="5" t="inlineStr">
+      <c r="G238" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 240.00) (scaled by 7.37x to fit Rs. 1.5M target)</t>
         </is>
@@ -8862,15 +7428,9 @@
         <v>47481</v>
       </c>
       <c r="F239" s="8" t="n">
-        <v>49155.2</v>
-      </c>
-      <c r="G239" s="8" t="n">
-        <v>1674.199999999997</v>
-      </c>
-      <c r="H239" s="8" t="n">
         <v>-104438</v>
       </c>
-      <c r="I239" s="9" t="inlineStr">
+      <c r="G239" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 323.00) (scaled by 7.37x to fit Rs. 1.5M target)</t>
         </is>
@@ -8897,15 +7457,9 @@
         <v>47334</v>
       </c>
       <c r="F240" s="4" t="n">
-        <v>49155.2</v>
-      </c>
-      <c r="G240" s="4" t="n">
-        <v>1821.199999999997</v>
-      </c>
-      <c r="H240" s="4" t="n">
         <v>-100028</v>
       </c>
-      <c r="I240" s="5" t="inlineStr">
+      <c r="G240" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 322.00) (scaled by 7.37x to fit Rs. 1.5M target)</t>
         </is>
@@ -8932,15 +7486,9 @@
         <v>43065</v>
       </c>
       <c r="F241" s="8" t="n">
-        <v>49155.2</v>
-      </c>
-      <c r="G241" s="8" t="n">
-        <v>6090.199999999997</v>
-      </c>
-      <c r="H241" s="8" t="n">
         <v>-143093</v>
       </c>
-      <c r="I241" s="9" t="inlineStr">
+      <c r="G241" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1485.00) (scaled by 7.37x to fit Rs. 1.5M target)</t>
         </is>
@@ -8967,15 +7515,9 @@
         <v>48875</v>
       </c>
       <c r="F242" s="4" t="n">
-        <v>49155.2</v>
-      </c>
-      <c r="G242" s="4" t="n">
-        <v>280.1999999999971</v>
-      </c>
-      <c r="H242" s="4" t="n">
         <v>-191968</v>
       </c>
-      <c r="I242" s="5" t="inlineStr">
+      <c r="G242" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 391.00) (scaled by 7.37x to fit Rs. 1.5M target)</t>
         </is>
@@ -9002,15 +7544,9 @@
         <v>27300</v>
       </c>
       <c r="F243" s="8" t="n">
-        <v>49155.2</v>
-      </c>
-      <c r="G243" s="8" t="n">
-        <v>21855.2</v>
-      </c>
-      <c r="H243" s="8" t="n">
         <v>-35705</v>
       </c>
-      <c r="I243" s="9" t="inlineStr">
+      <c r="G243" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 3900.00) (scaled by 7.37x to fit Rs. 1.5M target)</t>
         </is>
@@ -9037,15 +7573,9 @@
         <v>47250</v>
       </c>
       <c r="F244" s="4" t="n">
-        <v>49155.2</v>
-      </c>
-      <c r="G244" s="4" t="n">
-        <v>1905.199999999997</v>
-      </c>
-      <c r="H244" s="4" t="n">
         <v>-82955</v>
       </c>
-      <c r="I244" s="5" t="inlineStr">
+      <c r="G244" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 378.00) (scaled by 7.37x to fit Rs. 1.5M target)</t>
         </is>
@@ -9072,15 +7602,9 @@
         <v>42630</v>
       </c>
       <c r="F245" s="8" t="n">
-        <v>49155.2</v>
-      </c>
-      <c r="G245" s="8" t="n">
-        <v>6525.199999999997</v>
-      </c>
-      <c r="H245" s="8" t="n">
         <v>-80135</v>
       </c>
-      <c r="I245" s="9" t="inlineStr">
+      <c r="G245" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1470.00) (scaled by 7.37x to fit Rs. 1.5M target)</t>
         </is>
@@ -9107,15 +7631,9 @@
         <v>48818</v>
       </c>
       <c r="F246" s="4" t="n">
-        <v>49155.2</v>
-      </c>
-      <c r="G246" s="4" t="n">
-        <v>337.1999999999971</v>
-      </c>
-      <c r="H246" s="4" t="n">
         <v>-128953</v>
       </c>
-      <c r="I246" s="5" t="inlineStr">
+      <c r="G246" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 2219.00) (scaled by 7.37x to fit Rs. 1.5M target)</t>
         </is>
@@ -9142,15 +7660,9 @@
         <v>44486</v>
       </c>
       <c r="F247" s="8" t="n">
-        <v>49155.2</v>
-      </c>
-      <c r="G247" s="8" t="n">
-        <v>4669.199999999997</v>
-      </c>
-      <c r="H247" s="8" t="n">
         <v>-82179</v>
       </c>
-      <c r="I247" s="9" t="inlineStr">
+      <c r="G247" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 754.00) (scaled by 7.37x to fit Rs. 1.5M target)</t>
         </is>
@@ -9177,15 +7689,9 @@
         <v>41528</v>
       </c>
       <c r="F248" s="4" t="n">
-        <v>49155.2</v>
-      </c>
-      <c r="G248" s="4" t="n">
-        <v>7627.199999999997</v>
-      </c>
-      <c r="H248" s="4" t="n">
         <v>-123707</v>
       </c>
-      <c r="I248" s="5" t="inlineStr">
+      <c r="G248" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1432.00) (scaled by 7.37x to fit Rs. 1.5M target)</t>
         </is>
@@ -9212,15 +7718,9 @@
         <v>39875</v>
       </c>
       <c r="F249" s="8" t="n">
-        <v>49155.2</v>
-      </c>
-      <c r="G249" s="8" t="n">
-        <v>9280.199999999997</v>
-      </c>
-      <c r="H249" s="8" t="n">
         <v>-121010</v>
       </c>
-      <c r="I249" s="9" t="inlineStr">
+      <c r="G249" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1375.00) (scaled by 7.37x to fit Rs. 1.5M target)</t>
         </is>
@@ -9247,15 +7747,9 @@
         <v>52820</v>
       </c>
       <c r="F250" s="4" t="n">
-        <v>63786.07</v>
-      </c>
-      <c r="G250" s="4" t="n">
-        <v>10966.07</v>
-      </c>
-      <c r="H250" s="4" t="n">
         <v>-120668</v>
       </c>
-      <c r="I250" s="5" t="inlineStr">
+      <c r="G250" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1390.00) (scaled by 9.57x to fit Rs. 1.5M target)</t>
         </is>
@@ -9282,15 +7776,9 @@
         <v>59213</v>
       </c>
       <c r="F251" s="8" t="n">
-        <v>63786.07</v>
-      </c>
-      <c r="G251" s="8" t="n">
-        <v>4573.07</v>
-      </c>
-      <c r="H251" s="8" t="n">
         <v>-179881</v>
       </c>
-      <c r="I251" s="9" t="inlineStr">
+      <c r="G251" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 769.00) (scaled by 9.57x to fit Rs. 1.5M target)</t>
         </is>
@@ -9317,15 +7805,9 @@
         <v>62310</v>
       </c>
       <c r="F252" s="4" t="n">
-        <v>63786.07</v>
-      </c>
-      <c r="G252" s="4" t="n">
-        <v>1476.07</v>
-      </c>
-      <c r="H252" s="4" t="n">
         <v>-242191</v>
       </c>
-      <c r="I252" s="5" t="inlineStr">
+      <c r="G252" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 310.00) (scaled by 9.57x to fit Rs. 1.5M target)</t>
         </is>
@@ -9352,15 +7834,9 @@
         <v>61920</v>
       </c>
       <c r="F253" s="8" t="n">
-        <v>63786.07</v>
-      </c>
-      <c r="G253" s="8" t="n">
-        <v>1866.07</v>
-      </c>
-      <c r="H253" s="8" t="n">
         <v>-243127</v>
       </c>
-      <c r="I253" s="9" t="inlineStr">
+      <c r="G253" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 720.00) (scaled by 9.57x to fit Rs. 1.5M target)</t>
         </is>
@@ -9387,15 +7863,9 @@
         <v>61369</v>
       </c>
       <c r="F254" s="4" t="n">
-        <v>63786.07</v>
-      </c>
-      <c r="G254" s="4" t="n">
-        <v>2417.07</v>
-      </c>
-      <c r="H254" s="4" t="n">
         <v>-240770</v>
       </c>
-      <c r="I254" s="5" t="inlineStr">
+      <c r="G254" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 797.00) (scaled by 9.57x to fit Rs. 1.5M target)</t>
         </is>
@@ -9422,15 +7892,9 @@
         <v>67229</v>
       </c>
       <c r="F255" s="8" t="n">
-        <v>77017.72</v>
-      </c>
-      <c r="G255" s="8" t="n">
-        <v>9788.720000000001</v>
-      </c>
-      <c r="H255" s="8" t="n">
         <v>-12579</v>
       </c>
-      <c r="I255" s="9" t="inlineStr">
+      <c r="G255" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 2923.00) (scaled by 11.55x to fit Rs. 1.5M target)</t>
         </is>
@@ -9457,15 +7921,9 @@
         <v>47280</v>
       </c>
       <c r="F256" s="4" t="n">
-        <v>81013.67999999999</v>
-      </c>
-      <c r="G256" s="4" t="n">
-        <v>33733.67999999999</v>
-      </c>
-      <c r="H256" s="4" t="n">
         <v>348938</v>
       </c>
-      <c r="I256" s="5" t="inlineStr">
+      <c r="G256" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 3940.00) (scaled by 12.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -9492,15 +7950,9 @@
         <v>79833</v>
       </c>
       <c r="F257" s="8" t="n">
-        <v>81013.67999999999</v>
-      </c>
-      <c r="G257" s="8" t="n">
-        <v>1180.679999999993</v>
-      </c>
-      <c r="H257" s="8" t="n">
         <v>269105</v>
       </c>
-      <c r="I257" s="9" t="inlineStr">
+      <c r="G257" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 299.00) (scaled by 12.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -9527,15 +7979,9 @@
         <v>45600</v>
       </c>
       <c r="F258" s="4" t="n">
-        <v>81013.67999999999</v>
-      </c>
-      <c r="G258" s="4" t="n">
-        <v>35413.67999999999</v>
-      </c>
-      <c r="H258" s="4" t="n">
         <v>625745</v>
       </c>
-      <c r="I258" s="5" t="inlineStr">
+      <c r="G258" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 3800.00) (scaled by 12.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -9562,15 +8008,9 @@
         <v>75920.59999999999</v>
       </c>
       <c r="F259" s="8" t="n">
-        <v>81013.67999999999</v>
-      </c>
-      <c r="G259" s="8" t="n">
-        <v>5093.080000000002</v>
-      </c>
-      <c r="H259" s="8" t="n">
         <v>748142.4</v>
       </c>
-      <c r="I259" s="9" t="inlineStr">
+      <c r="G259" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1244.60) (scaled by 12.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -9597,15 +8037,9 @@
         <v>79716</v>
       </c>
       <c r="F260" s="4" t="n">
-        <v>81013.67999999999</v>
-      </c>
-      <c r="G260" s="4" t="n">
-        <v>1297.679999999993</v>
-      </c>
-      <c r="H260" s="4" t="n">
         <v>668426.4</v>
       </c>
-      <c r="I260" s="5" t="inlineStr">
+      <c r="G260" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 364.00) (scaled by 12.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -9632,15 +8066,9 @@
         <v>80520</v>
       </c>
       <c r="F261" s="8" t="n">
-        <v>81013.67999999999</v>
-      </c>
-      <c r="G261" s="8" t="n">
-        <v>493.679999999993</v>
-      </c>
-      <c r="H261" s="8" t="n">
         <v>587906.4</v>
       </c>
-      <c r="I261" s="9" t="inlineStr">
+      <c r="G261" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1320.00) (scaled by 12.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -9667,15 +8095,9 @@
         <v>78195.90000000001</v>
       </c>
       <c r="F262" s="4" t="n">
-        <v>81013.67999999999</v>
-      </c>
-      <c r="G262" s="4" t="n">
-        <v>2817.779999999984</v>
-      </c>
-      <c r="H262" s="4" t="n">
         <v>591609.1</v>
       </c>
-      <c r="I262" s="5" t="inlineStr">
+      <c r="G262" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1281.90) (scaled by 12.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -9702,15 +8124,9 @@
         <v>81144</v>
       </c>
       <c r="F263" s="8" t="n">
-        <v>81013.67999999999</v>
-      </c>
-      <c r="G263" s="8" t="n">
-        <v>-130.320000000007</v>
-      </c>
-      <c r="H263" s="8" t="n">
         <v>510465.1</v>
       </c>
-      <c r="I263" s="9" t="inlineStr">
+      <c r="G263" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 392.00) (scaled by 12.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -9737,15 +8153,9 @@
         <v>43210.8</v>
       </c>
       <c r="F264" s="4" t="n">
-        <v>81013.67999999999</v>
-      </c>
-      <c r="G264" s="4" t="n">
-        <v>37802.87999999999</v>
-      </c>
-      <c r="H264" s="4" t="n">
         <v>467254.3</v>
       </c>
-      <c r="I264" s="5" t="inlineStr">
+      <c r="G264" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 3600.90) (scaled by 12.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -9772,15 +8182,9 @@
         <v>60696</v>
       </c>
       <c r="F265" s="8" t="n">
-        <v>81013.67999999999</v>
-      </c>
-      <c r="G265" s="8" t="n">
-        <v>20317.67999999999</v>
-      </c>
-      <c r="H265" s="8" t="n">
         <v>406558.3</v>
       </c>
-      <c r="I265" s="9" t="inlineStr">
+      <c r="G265" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1686.00) (scaled by 12.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -9807,15 +8211,9 @@
         <v>67944</v>
       </c>
       <c r="F266" s="4" t="n">
-        <v>81013.67999999999</v>
-      </c>
-      <c r="G266" s="4" t="n">
-        <v>13069.67999999999</v>
-      </c>
-      <c r="H266" s="4" t="n">
         <v>400282.3</v>
       </c>
-      <c r="I266" s="5" t="inlineStr">
+      <c r="G266" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 5662.00) (scaled by 12.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -9842,15 +8240,9 @@
         <v>61128</v>
       </c>
       <c r="F267" s="8" t="n">
-        <v>81013.67999999999</v>
-      </c>
-      <c r="G267" s="8" t="n">
-        <v>19885.67999999999</v>
-      </c>
-      <c r="H267" s="8" t="n">
         <v>339154.3</v>
       </c>
-      <c r="I267" s="9" t="inlineStr">
+      <c r="G267" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1698.00) (scaled by 12.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -9877,15 +8269,9 @@
         <v>76806</v>
       </c>
       <c r="F268" s="4" t="n">
-        <v>81013.67999999999</v>
-      </c>
-      <c r="G268" s="4" t="n">
-        <v>4207.679999999993</v>
-      </c>
-      <c r="H268" s="4" t="n">
         <v>325492.3</v>
       </c>
-      <c r="I268" s="5" t="inlineStr">
+      <c r="G268" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 451.80) (scaled by 12.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -9912,15 +8298,9 @@
         <v>80730</v>
       </c>
       <c r="F269" s="8" t="n">
-        <v>81013.67999999999</v>
-      </c>
-      <c r="G269" s="8" t="n">
-        <v>283.679999999993</v>
-      </c>
-      <c r="H269" s="8" t="n">
         <v>244762.3</v>
       </c>
-      <c r="I269" s="9" t="inlineStr">
+      <c r="G269" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 390.00) (scaled by 12.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -9947,15 +8327,9 @@
         <v>79570</v>
       </c>
       <c r="F270" s="4" t="n">
-        <v>81013.67999999999</v>
-      </c>
-      <c r="G270" s="4" t="n">
-        <v>1443.679999999993</v>
-      </c>
-      <c r="H270" s="4" t="n">
         <v>165192.3</v>
       </c>
-      <c r="I270" s="5" t="inlineStr">
+      <c r="G270" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 545.00) (scaled by 12.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -9982,15 +8356,9 @@
         <v>78200</v>
       </c>
       <c r="F271" s="8" t="n">
-        <v>81013.67999999999</v>
-      </c>
-      <c r="G271" s="8" t="n">
-        <v>2813.679999999993</v>
-      </c>
-      <c r="H271" s="8" t="n">
         <v>86992.29999999999</v>
       </c>
-      <c r="I271" s="9" t="inlineStr">
+      <c r="G271" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 460.00) (scaled by 12.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -10017,15 +8385,9 @@
         <v>76835.59999999999</v>
       </c>
       <c r="F272" s="4" t="n">
-        <v>81013.67999999999</v>
-      </c>
-      <c r="G272" s="4" t="n">
-        <v>4178.080000000002</v>
-      </c>
-      <c r="H272" s="4" t="n">
         <v>10156.7</v>
       </c>
-      <c r="I272" s="5" t="inlineStr">
+      <c r="G272" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 573.40) (scaled by 12.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -10052,15 +8414,9 @@
         <v>60000</v>
       </c>
       <c r="F273" s="8" t="n">
-        <v>81013.67999999999</v>
-      </c>
-      <c r="G273" s="8" t="n">
-        <v>21013.67999999999</v>
-      </c>
-      <c r="H273" s="8" t="n">
         <v>601861.2999999999</v>
       </c>
-      <c r="I273" s="9" t="inlineStr">
+      <c r="G273" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 5000.00) (scaled by 12.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -10087,15 +8443,9 @@
         <v>78498</v>
       </c>
       <c r="F274" s="4" t="n">
-        <v>81013.67999999999</v>
-      </c>
-      <c r="G274" s="4" t="n">
-        <v>2515.679999999993</v>
-      </c>
-      <c r="H274" s="4" t="n">
         <v>523363.2999999999</v>
       </c>
-      <c r="I274" s="5" t="inlineStr">
+      <c r="G274" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1602.00) (scaled by 12.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -10122,15 +8472,9 @@
         <v>61200</v>
       </c>
       <c r="F275" s="8" t="n">
-        <v>81013.67999999999</v>
-      </c>
-      <c r="G275" s="8" t="n">
-        <v>19813.67999999999</v>
-      </c>
-      <c r="H275" s="8" t="n">
         <v>462163.2999999999</v>
       </c>
-      <c r="I275" s="9" t="inlineStr">
+      <c r="G275" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 5100.00) (scaled by 12.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -10157,15 +8501,9 @@
         <v>77626.2</v>
       </c>
       <c r="F276" s="4" t="n">
-        <v>81013.67999999999</v>
-      </c>
-      <c r="G276" s="4" t="n">
-        <v>3387.479999999996</v>
-      </c>
-      <c r="H276" s="4" t="n">
         <v>445737.0999999999</v>
       </c>
-      <c r="I276" s="5" t="inlineStr">
+      <c r="G276" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 579.30) (scaled by 12.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -10192,15 +8530,9 @@
         <v>68320</v>
       </c>
       <c r="F277" s="8" t="n">
-        <v>81013.67999999999</v>
-      </c>
-      <c r="G277" s="8" t="n">
-        <v>12693.67999999999</v>
-      </c>
-      <c r="H277" s="8" t="n">
         <v>377417.0999999999</v>
       </c>
-      <c r="I277" s="9" t="inlineStr">
+      <c r="G277" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1120.00) (scaled by 12.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -10227,15 +8559,9 @@
         <v>76650</v>
       </c>
       <c r="F278" s="4" t="n">
-        <v>81013.67999999999</v>
-      </c>
-      <c r="G278" s="4" t="n">
-        <v>4363.679999999993</v>
-      </c>
-      <c r="H278" s="4" t="n">
         <v>300767.0999999999</v>
       </c>
-      <c r="I278" s="5" t="inlineStr">
+      <c r="G278" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 525.00) (scaled by 12.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -10262,15 +8588,9 @@
         <v>78540</v>
       </c>
       <c r="F279" s="8" t="n">
-        <v>81013.67999999999</v>
-      </c>
-      <c r="G279" s="8" t="n">
-        <v>2473.679999999993</v>
-      </c>
-      <c r="H279" s="8" t="n">
         <v>222227.0999999999</v>
       </c>
-      <c r="I279" s="9" t="inlineStr">
+      <c r="G279" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 462.00) (scaled by 12.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -10297,15 +8617,9 @@
         <v>79695</v>
       </c>
       <c r="F280" s="4" t="n">
-        <v>81013.67999999999</v>
-      </c>
-      <c r="G280" s="4" t="n">
-        <v>1318.679999999993</v>
-      </c>
-      <c r="H280" s="4" t="n">
         <v>142532.0999999999</v>
       </c>
-      <c r="I280" s="5" t="inlineStr">
+      <c r="G280" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 345.00) (scaled by 12.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -10332,15 +8646,9 @@
         <v>80619</v>
       </c>
       <c r="F281" s="8" t="n">
-        <v>81013.67999999999</v>
-      </c>
-      <c r="G281" s="8" t="n">
-        <v>394.679999999993</v>
-      </c>
-      <c r="H281" s="8" t="n">
         <v>61913.09999999992</v>
       </c>
-      <c r="I281" s="9" t="inlineStr">
+      <c r="G281" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 349.00) (scaled by 12.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -10367,15 +8675,9 @@
         <v>93465</v>
       </c>
       <c r="F282" s="4" t="n">
-        <v>103538.3</v>
-      </c>
-      <c r="G282" s="4" t="n">
-        <v>10073.3</v>
-      </c>
-      <c r="H282" s="4" t="n">
         <v>635723.2999999998</v>
       </c>
-      <c r="I282" s="5" t="inlineStr">
+      <c r="G282" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1005.00) (scaled by 15.53x to fit Rs. 1.5M target)</t>
         </is>
@@ -10402,15 +8704,9 @@
         <v>99448</v>
       </c>
       <c r="F283" s="8" t="n">
-        <v>103538.3</v>
-      </c>
-      <c r="G283" s="8" t="n">
-        <v>4090.300000000003</v>
-      </c>
-      <c r="H283" s="8" t="n">
         <v>536275.2999999998</v>
       </c>
-      <c r="I283" s="9" t="inlineStr">
+      <c r="G283" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 401.00) (scaled by 15.53x to fit Rs. 1.5M target)</t>
         </is>
@@ -10437,15 +8733,9 @@
         <v>101075</v>
       </c>
       <c r="F284" s="4" t="n">
-        <v>103538.3</v>
-      </c>
-      <c r="G284" s="4" t="n">
-        <v>2463.300000000003</v>
-      </c>
-      <c r="H284" s="4" t="n">
         <v>435200.2999999998</v>
       </c>
-      <c r="I284" s="5" t="inlineStr">
+      <c r="G284" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 325.00) (scaled by 15.53x to fit Rs. 1.5M target)</t>
         </is>
@@ -10472,15 +8762,9 @@
         <v>101339</v>
       </c>
       <c r="F285" s="8" t="n">
-        <v>103538.3</v>
-      </c>
-      <c r="G285" s="8" t="n">
-        <v>2199.300000000003</v>
-      </c>
-      <c r="H285" s="8" t="n">
         <v>333861.2999999998</v>
       </c>
-      <c r="I285" s="9" t="inlineStr">
+      <c r="G285" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 467.00) (scaled by 15.53x to fit Rs. 1.5M target)</t>
         </is>
@@ -10507,15 +8791,9 @@
         <v>98980</v>
       </c>
       <c r="F286" s="4" t="n">
-        <v>103538.3</v>
-      </c>
-      <c r="G286" s="4" t="n">
-        <v>4558.300000000003</v>
-      </c>
-      <c r="H286" s="4" t="n">
         <v>450858.2999999998</v>
       </c>
-      <c r="I286" s="5" t="inlineStr">
+      <c r="G286" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 490.00) (scaled by 15.53x to fit Rs. 1.5M target)</t>
         </is>
@@ -10542,15 +8820,9 @@
         <v>95940</v>
       </c>
       <c r="F287" s="8" t="n">
-        <v>103538.3</v>
-      </c>
-      <c r="G287" s="8" t="n">
-        <v>7598.300000000003</v>
-      </c>
-      <c r="H287" s="8" t="n">
         <v>354918.2999999998</v>
       </c>
-      <c r="I287" s="9" t="inlineStr">
+      <c r="G287" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1230.00) (scaled by 15.53x to fit Rs. 1.5M target)</t>
         </is>
@@ -10577,15 +8849,9 @@
         <v>96782</v>
       </c>
       <c r="F288" s="4" t="n">
-        <v>103538.3</v>
-      </c>
-      <c r="G288" s="4" t="n">
-        <v>6756.300000000003</v>
-      </c>
-      <c r="H288" s="4" t="n">
         <v>258136.2999999998</v>
       </c>
-      <c r="I288" s="5" t="inlineStr">
+      <c r="G288" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 446.00) (scaled by 15.53x to fit Rs. 1.5M target)</t>
         </is>
@@ -10612,15 +8878,9 @@
         <v>67424</v>
       </c>
       <c r="F289" s="8" t="n">
-        <v>103538.3</v>
-      </c>
-      <c r="G289" s="8" t="n">
-        <v>36114.3</v>
-      </c>
-      <c r="H289" s="8" t="n">
         <v>190712.2999999998</v>
       </c>
-      <c r="I289" s="9" t="inlineStr">
+      <c r="G289" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 4214.00) (scaled by 15.53x to fit Rs. 1.5M target)</t>
         </is>
@@ -10647,15 +8907,9 @@
         <v>66080</v>
       </c>
       <c r="F290" s="4" t="n">
-        <v>103538.3</v>
-      </c>
-      <c r="G290" s="4" t="n">
-        <v>37458.3</v>
-      </c>
-      <c r="H290" s="4" t="n">
         <v>194744.2999999998</v>
       </c>
-      <c r="I290" s="5" t="inlineStr">
+      <c r="G290" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 4130.00) (scaled by 15.53x to fit Rs. 1.5M target)</t>
         </is>
@@ -10682,15 +8936,9 @@
         <v>99000</v>
       </c>
       <c r="F291" s="8" t="n">
-        <v>103538.3</v>
-      </c>
-      <c r="G291" s="8" t="n">
-        <v>4538.300000000003</v>
-      </c>
-      <c r="H291" s="8" t="n">
         <v>95744.29999999981</v>
       </c>
-      <c r="I291" s="9" t="inlineStr">
+      <c r="G291" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 375.00) (scaled by 15.53x to fit Rs. 1.5M target)</t>
         </is>
@@ -10717,15 +8965,9 @@
         <v>67200</v>
       </c>
       <c r="F292" s="4" t="n">
-        <v>103538.3</v>
-      </c>
-      <c r="G292" s="4" t="n">
-        <v>36338.3</v>
-      </c>
-      <c r="H292" s="4" t="n">
         <v>28544.29999999981</v>
       </c>
-      <c r="I292" s="5" t="inlineStr">
+      <c r="G292" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 4200.00) (scaled by 15.53x to fit Rs. 1.5M target)</t>
         </is>
@@ -10752,15 +8994,9 @@
         <v>98735</v>
       </c>
       <c r="F293" s="8" t="n">
-        <v>103538.3</v>
-      </c>
-      <c r="G293" s="8" t="n">
-        <v>4803.300000000003</v>
-      </c>
-      <c r="H293" s="8" t="n">
         <v>-2990.700000000186</v>
       </c>
-      <c r="I293" s="9" t="inlineStr">
+      <c r="G293" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 455.00) (scaled by 15.53x to fit Rs. 1.5M target)</t>
         </is>
@@ -10787,15 +9023,9 @@
         <v>99960</v>
       </c>
       <c r="F294" s="4" t="n">
-        <v>103538.3</v>
-      </c>
-      <c r="G294" s="4" t="n">
-        <v>3578.300000000003</v>
-      </c>
-      <c r="H294" s="4" t="n">
         <v>-102950.7000000002</v>
       </c>
-      <c r="I294" s="5" t="inlineStr">
+      <c r="G294" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 357.00) (scaled by 15.53x to fit Rs. 1.5M target)</t>
         </is>
@@ -10822,15 +9052,9 @@
         <v>119642</v>
       </c>
       <c r="F295" s="8" t="n">
-        <v>121069.05</v>
-      </c>
-      <c r="G295" s="8" t="n">
-        <v>1427.050000000003</v>
-      </c>
-      <c r="H295" s="8" t="n">
         <v>101560.0999999998</v>
       </c>
-      <c r="I295" s="9" t="inlineStr">
+      <c r="G295" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 734.00) (scaled by 18.16x to fit Rs. 1.5M target)</t>
         </is>
@@ -10857,15 +9081,9 @@
         <v>108750</v>
       </c>
       <c r="F296" s="4" t="n">
-        <v>121069.05</v>
-      </c>
-      <c r="G296" s="4" t="n">
-        <v>12319.05</v>
-      </c>
-      <c r="H296" s="4" t="n">
         <v>-7189.900000000198</v>
       </c>
-      <c r="I296" s="5" t="inlineStr">
+      <c r="G296" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 750.00) (scaled by 18.16x to fit Rs. 1.5M target)</t>
         </is>
@@ -10892,15 +9110,9 @@
         <v>64170</v>
       </c>
       <c r="F297" s="8" t="n">
-        <v>121069.05</v>
-      </c>
-      <c r="G297" s="8" t="n">
-        <v>56899.05</v>
-      </c>
-      <c r="H297" s="8" t="n">
         <v>-71359.9000000002</v>
       </c>
-      <c r="I297" s="9" t="inlineStr">
+      <c r="G297" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 3565.00) (scaled by 18.16x to fit Rs. 1.5M target)</t>
         </is>
@@ -10927,15 +9139,9 @@
         <v>65178</v>
       </c>
       <c r="F298" s="4" t="n">
-        <v>121069.05</v>
-      </c>
-      <c r="G298" s="4" t="n">
-        <v>55891.05</v>
-      </c>
-      <c r="H298" s="4" t="n">
         <v>-136537.9000000002</v>
       </c>
-      <c r="I298" s="5" t="inlineStr">
+      <c r="G298" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 3621.00) (scaled by 18.16x to fit Rs. 1.5M target)</t>
         </is>
@@ -10962,15 +9168,9 @@
         <v>63036</v>
       </c>
       <c r="F299" s="8" t="n">
-        <v>121069.05</v>
-      </c>
-      <c r="G299" s="8" t="n">
-        <v>58033.05</v>
-      </c>
-      <c r="H299" s="8" t="n">
         <v>-68679.7000000002</v>
       </c>
-      <c r="I299" s="9" t="inlineStr">
+      <c r="G299" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 3502.00) (scaled by 18.16x to fit Rs. 1.5M target)</t>
         </is>
@@ -10997,15 +9197,9 @@
         <v>66780</v>
       </c>
       <c r="F300" s="4" t="n">
-        <v>121069.05</v>
-      </c>
-      <c r="G300" s="4" t="n">
-        <v>54289.05</v>
-      </c>
-      <c r="H300" s="4" t="n">
         <v>171780.2999999998</v>
       </c>
-      <c r="I300" s="5" t="inlineStr">
+      <c r="G300" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 3710.00) (scaled by 18.16x to fit Rs. 1.5M target)</t>
         </is>
@@ -11032,15 +9226,9 @@
         <v>120106</v>
       </c>
       <c r="F301" s="8" t="n">
-        <v>134300.3</v>
-      </c>
-      <c r="G301" s="8" t="n">
-        <v>14194.29999999999</v>
-      </c>
-      <c r="H301" s="8" t="n">
         <v>122648.2999999998</v>
       </c>
-      <c r="I301" s="9" t="inlineStr">
+      <c r="G301" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 746.00) (scaled by 20.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -11067,15 +9255,9 @@
         <v>120782.2</v>
       </c>
       <c r="F302" s="4" t="n">
-        <v>134300.3</v>
-      </c>
-      <c r="G302" s="4" t="n">
-        <v>13518.09999999998</v>
-      </c>
-      <c r="H302" s="4" t="n">
         <v>1866.099999999802</v>
       </c>
-      <c r="I302" s="5" t="inlineStr">
+      <c r="G302" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 750.20) (scaled by 20.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -11102,15 +9284,9 @@
         <v>123809</v>
       </c>
       <c r="F303" s="8" t="n">
-        <v>134300.3</v>
-      </c>
-      <c r="G303" s="8" t="n">
-        <v>10491.29999999999</v>
-      </c>
-      <c r="H303" s="8" t="n">
         <v>-121942.9000000002</v>
       </c>
-      <c r="I303" s="9" t="inlineStr">
+      <c r="G303" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 769.00) (scaled by 20.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -11137,15 +9313,9 @@
         <v>122682</v>
       </c>
       <c r="F304" s="4" t="n">
-        <v>134300.3</v>
-      </c>
-      <c r="G304" s="4" t="n">
-        <v>11618.29999999999</v>
-      </c>
-      <c r="H304" s="4" t="n">
         <v>131293.9999999998</v>
       </c>
-      <c r="I304" s="5" t="inlineStr">
+      <c r="G304" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 762.00) (scaled by 20.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -11172,15 +9342,9 @@
         <v>119945</v>
       </c>
       <c r="F305" s="8" t="n">
-        <v>134300.3</v>
-      </c>
-      <c r="G305" s="8" t="n">
-        <v>14355.29999999999</v>
-      </c>
-      <c r="H305" s="8" t="n">
         <v>11348.9999999998</v>
       </c>
-      <c r="I305" s="9" t="inlineStr">
+      <c r="G305" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 745.00) (scaled by 20.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -11207,15 +9371,9 @@
         <v>129720</v>
       </c>
       <c r="F306" s="4" t="n">
-        <v>134300.3</v>
-      </c>
-      <c r="G306" s="4" t="n">
-        <v>4580.299999999988</v>
-      </c>
-      <c r="H306" s="4" t="n">
         <v>677880.8999999998</v>
       </c>
-      <c r="I306" s="5" t="inlineStr">
+      <c r="G306" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 920.00) (scaled by 20.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -11242,15 +9400,9 @@
         <v>130284</v>
       </c>
       <c r="F307" s="8" t="n">
-        <v>134300.3</v>
-      </c>
-      <c r="G307" s="8" t="n">
-        <v>4016.299999999988</v>
-      </c>
-      <c r="H307" s="8" t="n">
         <v>683661.8999999998</v>
       </c>
-      <c r="I307" s="9" t="inlineStr">
+      <c r="G307" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 924.00) (scaled by 20.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -11277,15 +9429,9 @@
         <v>125934</v>
       </c>
       <c r="F308" s="4" t="n">
-        <v>134300.3</v>
-      </c>
-      <c r="G308" s="4" t="n">
-        <v>8366.299999999988</v>
-      </c>
-      <c r="H308" s="4" t="n">
         <v>557727.8999999998</v>
       </c>
-      <c r="I308" s="5" t="inlineStr">
+      <c r="G308" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 417.00) (scaled by 20.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -11312,15 +9458,9 @@
         <v>130055.8</v>
       </c>
       <c r="F309" s="8" t="n">
-        <v>134300.3</v>
-      </c>
-      <c r="G309" s="8" t="n">
-        <v>4244.5</v>
-      </c>
-      <c r="H309" s="8" t="n">
         <v>427672.0999999998</v>
       </c>
-      <c r="I309" s="9" t="inlineStr">
+      <c r="G309" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 403.90) (scaled by 20.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -11347,15 +9487,9 @@
         <v>127635</v>
       </c>
       <c r="F310" s="4" t="n">
-        <v>134300.3</v>
-      </c>
-      <c r="G310" s="4" t="n">
-        <v>6665.299999999988</v>
-      </c>
-      <c r="H310" s="4" t="n">
         <v>300037.0999999998</v>
       </c>
-      <c r="I310" s="5" t="inlineStr">
+      <c r="G310" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 635.00) (scaled by 20.15x to fit Rs. 1.5M target)</t>
         </is>
@@ -11382,15 +9516,9 @@
         <v>140342.8</v>
       </c>
       <c r="F311" s="8" t="n">
-        <v>145744.83</v>
-      </c>
-      <c r="G311" s="8" t="n">
-        <v>5402.029999999999</v>
-      </c>
-      <c r="H311" s="8" t="n">
         <v>310826.1999999998</v>
       </c>
-      <c r="I311" s="9" t="inlineStr">
+      <c r="G311" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 356.20) (scaled by 21.86x to fit Rs. 1.5M target)</t>
         </is>
@@ -11417,15 +9545,9 @@
         <v>124080</v>
       </c>
       <c r="F312" s="4" t="n">
-        <v>145744.83</v>
-      </c>
-      <c r="G312" s="4" t="n">
-        <v>21664.82999999999</v>
-      </c>
-      <c r="H312" s="4" t="n">
         <v>480431.1999999997</v>
       </c>
-      <c r="I312" s="5" t="inlineStr">
+      <c r="G312" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 5640.00) (scaled by 21.86x to fit Rs. 1.5M target)</t>
         </is>
@@ -11452,15 +9574,9 @@
         <v>140589.2</v>
       </c>
       <c r="F313" s="8" t="n">
-        <v>145744.83</v>
-      </c>
-      <c r="G313" s="8" t="n">
-        <v>5155.629999999976</v>
-      </c>
-      <c r="H313" s="8" t="n">
         <v>339841.9999999997</v>
       </c>
-      <c r="I313" s="9" t="inlineStr">
+      <c r="G313" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 1073.20) (scaled by 21.86x to fit Rs. 1.5M target)</t>
         </is>
@@ -11487,15 +9603,9 @@
         <v>130968</v>
       </c>
       <c r="F314" s="4" t="n">
-        <v>145744.83</v>
-      </c>
-      <c r="G314" s="4" t="n">
-        <v>14776.82999999999</v>
-      </c>
-      <c r="H314" s="4" t="n">
         <v>339531.9999999997</v>
       </c>
-      <c r="I314" s="5" t="inlineStr">
+      <c r="G314" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 856.00) (scaled by 21.86x to fit Rs. 1.5M target)</t>
         </is>
@@ -11522,15 +9632,9 @@
         <v>138250</v>
       </c>
       <c r="F315" s="8" t="n">
-        <v>145744.83</v>
-      </c>
-      <c r="G315" s="8" t="n">
-        <v>7494.829999999987</v>
-      </c>
-      <c r="H315" s="8" t="n">
         <v>201281.9999999997</v>
       </c>
-      <c r="I315" s="9" t="inlineStr">
+      <c r="G315" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 395.00) (scaled by 21.86x to fit Rs. 1.5M target)</t>
         </is>
@@ -11557,15 +9661,9 @@
         <v>144264</v>
       </c>
       <c r="F316" s="4" t="n">
-        <v>145744.83</v>
-      </c>
-      <c r="G316" s="4" t="n">
-        <v>1480.829999999987</v>
-      </c>
-      <c r="H316" s="4" t="n">
         <v>57017.99999999971</v>
       </c>
-      <c r="I316" s="5" t="inlineStr">
+      <c r="G316" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 601.10) (scaled by 21.86x to fit Rs. 1.5M target)</t>
         </is>
@@ -11592,15 +9690,9 @@
         <v>142104</v>
       </c>
       <c r="F317" s="8" t="n">
-        <v>145744.83</v>
-      </c>
-      <c r="G317" s="8" t="n">
-        <v>3640.829999999987</v>
-      </c>
-      <c r="H317" s="8" t="n">
         <v>353883.9999999997</v>
       </c>
-      <c r="I317" s="9" t="inlineStr">
+      <c r="G317" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 592.10) (scaled by 21.86x to fit Rs. 1.5M target)</t>
         </is>
@@ -11627,15 +9719,9 @@
         <v>130386.6</v>
       </c>
       <c r="F318" s="4" t="n">
-        <v>145744.83</v>
-      </c>
-      <c r="G318" s="4" t="n">
-        <v>15358.22999999998</v>
-      </c>
-      <c r="H318" s="4" t="n">
         <v>821481.3999999998</v>
       </c>
-      <c r="I318" s="5" t="inlineStr">
+      <c r="G318" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 852.20) (scaled by 21.86x to fit Rs. 1.5M target)</t>
         </is>
@@ -11662,15 +9748,9 @@
         <v>119614</v>
       </c>
       <c r="F319" s="8" t="n">
-        <v>145744.83</v>
-      </c>
-      <c r="G319" s="8" t="n">
-        <v>26130.82999999999</v>
-      </c>
-      <c r="H319" s="8" t="n">
         <v>701867.3999999998</v>
       </c>
-      <c r="I319" s="9" t="inlineStr">
+      <c r="G319" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 5437.00) (scaled by 21.86x to fit Rs. 1.5M target)</t>
         </is>
@@ -11697,15 +9777,9 @@
         <v>131540.22</v>
       </c>
       <c r="F320" s="4" t="n">
-        <v>145744.83</v>
-      </c>
-      <c r="G320" s="4" t="n">
-        <v>14204.60999999999</v>
-      </c>
-      <c r="H320" s="4" t="n">
         <v>1550876.98</v>
       </c>
-      <c r="I320" s="5" t="inlineStr">
+      <c r="G320" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 859.74) (scaled by 21.86x to fit Rs. 1.5M target)</t>
         </is>
@@ -11732,15 +9806,9 @@
         <v>119215.8</v>
       </c>
       <c r="F321" s="8" t="n">
-        <v>145744.83</v>
-      </c>
-      <c r="G321" s="8" t="n">
-        <v>26529.03</v>
-      </c>
-      <c r="H321" s="8" t="n">
         <v>1431661.18</v>
       </c>
-      <c r="I321" s="9" t="inlineStr">
+      <c r="G321" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 5418.90) (scaled by 21.86x to fit Rs. 1.5M target)</t>
         </is>
@@ -11767,15 +9835,9 @@
         <v>137252.5</v>
       </c>
       <c r="F322" s="4" t="n">
-        <v>145744.83</v>
-      </c>
-      <c r="G322" s="4" t="n">
-        <v>8492.329999999987</v>
-      </c>
-      <c r="H322" s="4" t="n">
         <v>1294408.68</v>
       </c>
-      <c r="I322" s="5" t="inlineStr">
+      <c r="G322" s="5" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 784.30) (scaled by 21.86x to fit Rs. 1.5M target)</t>
         </is>
@@ -11802,15 +9864,9 @@
         <v>139815.78</v>
       </c>
       <c r="F323" s="8" t="n">
-        <v>145744.83</v>
-      </c>
-      <c r="G323" s="8" t="n">
-        <v>5929.049999999988</v>
-      </c>
-      <c r="H323" s="8" t="n">
         <v>1154592.9</v>
       </c>
-      <c r="I323" s="9" t="inlineStr">
+      <c r="G323" s="9" t="inlineStr">
         <is>
           <t>BUY: Stock price is at its 3-month lowest (Rs. 320.00) (scaled by 21.86x to fit Rs. 1.5M target) (Adjusted cents to hit exact 1.5M target)</t>
         </is>
